--- a/model/Outputs/11. Interest rate/0/Output Files/0.2/Output_12_45.xlsx
+++ b/model/Outputs/11. Interest rate/0/Output Files/0.2/Output_12_45.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3800500.790464131</v>
+        <v>3801724.456090182</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13595871.02547106</v>
+        <v>13584330.56597897</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13595871.02547106</v>
+        <v>13584330.56597897</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8356.225371618373</v>
+        <v>28421.06605721018</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8356.225371618373</v>
+        <v>28421.06605721018</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>22440453.60293263</v>
+        <v>22441919.7764047</v>
       </c>
     </row>
   </sheetData>
@@ -672,7 +672,7 @@
         <v>3.343301935257443</v>
       </c>
       <c r="H2" t="n">
-        <v>5.722467174370241</v>
+        <v>3.769060713577687</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -705,13 +705,13 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>85.41253966161941</v>
+        <v>87.36594612241093</v>
       </c>
       <c r="T2" t="n">
         <v>184.8629887637397</v>
       </c>
       <c r="U2" t="n">
-        <v>249.1881709204689</v>
+        <v>249.1881709204699</v>
       </c>
       <c r="V2" t="n">
         <v>229.8510241668239</v>
@@ -781,16 +781,16 @@
         <v>144.7989632036872</v>
       </c>
       <c r="R3" t="n">
-        <v>374</v>
+        <v>133.5184388018132</v>
       </c>
       <c r="S3" t="n">
         <v>374</v>
       </c>
       <c r="T3" t="n">
-        <v>281.9814317732686</v>
+        <v>374</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1957842884886531</v>
+        <v>148.6587772599441</v>
       </c>
       <c r="V3" t="n">
         <v>14.51066719152016</v>
@@ -909,10 +909,10 @@
         <v>3.343301935257443</v>
       </c>
       <c r="H5" t="n">
-        <v>5.722467174369123</v>
+        <v>3.769060713577687</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1.953406460791434</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -970,16 +970,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>348.4381314478563</v>
+        <v>374</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1036,10 +1036,10 @@
         <v>32.37314290982852</v>
       </c>
       <c r="X6" t="n">
-        <v>19.86273944538755</v>
+        <v>310.910655012859</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
     </row>
     <row r="7">
@@ -1143,13 +1143,13 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G8" t="n">
-        <v>3.343301935257443</v>
+        <v>3.3392818347549</v>
       </c>
       <c r="H8" t="n">
-        <v>3.769060713577687</v>
+        <v>3.727889859306288</v>
       </c>
       <c r="I8" t="n">
-        <v>1.953406460791434</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1176,16 +1176,16 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.108125053756319</v>
       </c>
       <c r="S8" t="n">
-        <v>85.41253966161941</v>
+        <v>85.32093162141837</v>
       </c>
       <c r="T8" t="n">
-        <v>184.8629887637397</v>
+        <v>184.84539077379</v>
       </c>
       <c r="U8" t="n">
-        <v>249.1881709204699</v>
+        <v>249.1878493124298</v>
       </c>
       <c r="V8" t="n">
         <v>229.8510241668239</v>
@@ -1207,16 +1207,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -1252,25 +1252,25 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>144.7989632036872</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>133.5184388018132</v>
+        <v>133.3848916320019</v>
       </c>
       <c r="S9" t="n">
-        <v>62.44885845517734</v>
+        <v>163.59841185883</v>
       </c>
       <c r="T9" t="n">
-        <v>4.464774651476091</v>
+        <v>4.456104840155319</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1957842884886531</v>
+        <v>0.1956427790546513</v>
       </c>
       <c r="V9" t="n">
-        <v>374</v>
+        <v>14.51066719152016</v>
       </c>
       <c r="W9" t="n">
-        <v>369.2596284469077</v>
+        <v>32.37314290982852</v>
       </c>
       <c r="X9" t="n">
         <v>19.86273944538755</v>
@@ -1319,22 +1319,22 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>91.51638189435317</v>
+        <v>91.23370976320564</v>
       </c>
       <c r="N10" t="n">
-        <v>142.7621408454554</v>
+        <v>142.4861900257832</v>
       </c>
       <c r="O10" t="n">
-        <v>214.1923837511461</v>
+        <v>213.9374985052444</v>
       </c>
       <c r="P10" t="n">
-        <v>264.9837661807364</v>
+        <v>264.7656678200808</v>
       </c>
       <c r="Q10" t="n">
-        <v>310.286266425598</v>
+        <v>310.135266425598</v>
       </c>
       <c r="R10" t="n">
-        <v>318.2506853582003</v>
+        <v>318.1696033909872</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1416,10 +1416,10 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>142.0601778525742</v>
+        <v>142.9849209967825</v>
       </c>
       <c r="T11" t="n">
-        <v>256.6130223602093</v>
+        <v>259.5690792160011</v>
       </c>
       <c r="U11" t="n">
         <v>328.1096985586609</v>
@@ -1444,19 +1444,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>384.5565566463266</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C12" t="n">
-        <v>361.0999124455193</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D12" t="n">
-        <v>26.93768689770263</v>
+        <v>210.0969536768463</v>
       </c>
       <c r="E12" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F12" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G12" t="n">
         <v>3.993158516536777</v>
@@ -1507,13 +1507,13 @@
         <v>93.51066719152016</v>
       </c>
       <c r="W12" t="n">
-        <v>111.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X12" t="n">
         <v>98.86273944538755</v>
       </c>
       <c r="Y12" t="n">
-        <v>261.5506595452779</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="13">
@@ -1617,7 +1617,7 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G14" t="n">
-        <v>78.40634055685268</v>
+        <v>81.36239741264433</v>
       </c>
       <c r="H14" t="n">
         <v>72.7233722713666</v>
@@ -1653,7 +1653,7 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>142.0601778525742</v>
+        <v>142.9849209967825</v>
       </c>
       <c r="T14" t="n">
         <v>259.5690792160011</v>
@@ -1681,13 +1681,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>384.5565566463266</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C15" t="n">
         <v>40.09991244551929</v>
       </c>
       <c r="D15" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E15" t="n">
         <v>21.67209722191262</v>
@@ -1741,16 +1741,16 @@
         <v>79.16125598660182</v>
       </c>
       <c r="V15" t="n">
-        <v>93.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W15" t="n">
-        <v>294.5324096889722</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X15" t="n">
         <v>419.8627394453875</v>
       </c>
       <c r="Y15" t="n">
-        <v>78.39139276613435</v>
+        <v>261.5506595452779</v>
       </c>
     </row>
     <row r="16">
@@ -1854,10 +1854,10 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G17" t="n">
-        <v>81.36239741264433</v>
+        <v>81.36239741264436</v>
       </c>
       <c r="H17" t="n">
-        <v>72.7233722713666</v>
+        <v>72.72337227136661</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -1887,7 +1887,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>0.9247431442083234</v>
       </c>
       <c r="S17" t="n">
         <v>142.0601778525742</v>
@@ -1896,7 +1896,7 @@
         <v>259.5690792160011</v>
       </c>
       <c r="U17" t="n">
-        <v>328.109698558661</v>
+        <v>328.1096985586609</v>
       </c>
       <c r="V17" t="n">
         <v>308.8510241668239</v>
@@ -1908,7 +1908,7 @@
         <v>271.2818334606677</v>
       </c>
       <c r="Y17" t="n">
-        <v>187.3613758270147</v>
+        <v>190.3174326828064</v>
       </c>
     </row>
     <row r="18">
@@ -1921,7 +1921,7 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C18" t="n">
-        <v>223.2591792246631</v>
+        <v>223.2591792246629</v>
       </c>
       <c r="D18" t="n">
         <v>347.9376868977026</v>
@@ -1933,10 +1933,10 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G18" t="n">
-        <v>3.993158516536766</v>
+        <v>3.993158516536777</v>
       </c>
       <c r="H18" t="n">
-        <v>3.959653224156966</v>
+        <v>3.95965322415698</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -1972,10 +1972,10 @@
         <v>131.7003678891396</v>
       </c>
       <c r="T18" t="n">
-        <v>81.34934068921194</v>
+        <v>81.34934068921193</v>
       </c>
       <c r="U18" t="n">
-        <v>79.16125598660182</v>
+        <v>79.16125598660184</v>
       </c>
       <c r="V18" t="n">
         <v>93.51066719152016</v>
@@ -2027,7 +2027,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>9.517497010238174</v>
+        <v>9.517497010238188</v>
       </c>
       <c r="M19" t="n">
         <v>101.5443818943532</v>
@@ -2036,19 +2036,19 @@
         <v>154.4301408454554</v>
       </c>
       <c r="O19" t="n">
-        <v>231.000383751146</v>
+        <v>231.0003837511461</v>
       </c>
       <c r="P19" t="n">
         <v>290.7677661807365</v>
       </c>
       <c r="Q19" t="n">
-        <v>352.4422664255979</v>
+        <v>352.442266425598</v>
       </c>
       <c r="R19" t="n">
         <v>377.4666853582003</v>
       </c>
       <c r="S19" t="n">
-        <v>30.46857806351119</v>
+        <v>30.46857806351117</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -2127,7 +2127,7 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>142.0601778525742</v>
+        <v>142.9849209967825</v>
       </c>
       <c r="T20" t="n">
         <v>259.5690792160011</v>
@@ -2145,7 +2145,7 @@
         <v>271.2818334606677</v>
       </c>
       <c r="Y20" t="n">
-        <v>187.3613758270147</v>
+        <v>190.3174326828064</v>
       </c>
     </row>
     <row r="21">
@@ -2155,19 +2155,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>384.5565566463266</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C21" t="n">
-        <v>361.0999124455193</v>
+        <v>223.2591792246629</v>
       </c>
       <c r="D21" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E21" t="n">
-        <v>204.8313640010562</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F21" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G21" t="n">
         <v>3.993158516536766</v>
@@ -2325,7 +2325,7 @@
         <v>83.36328960686865</v>
       </c>
       <c r="F23" t="n">
-        <v>80.93357185224228</v>
+        <v>83.88962870801186</v>
       </c>
       <c r="G23" t="n">
         <v>81.36239741264433</v>
@@ -2364,7 +2364,7 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>142.0601778525742</v>
+        <v>142.9849209967825</v>
       </c>
       <c r="T23" t="n">
         <v>259.5690792160011</v>
@@ -2392,19 +2392,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>63.55655664632661</v>
+        <v>246.7158234254702</v>
       </c>
       <c r="C24" t="n">
-        <v>40.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D24" t="n">
         <v>26.93768689770263</v>
       </c>
       <c r="E24" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F24" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G24" t="n">
         <v>3.993158516536766</v>
@@ -2452,16 +2452,16 @@
         <v>79.16125598660182</v>
       </c>
       <c r="V24" t="n">
-        <v>276.669933970664</v>
+        <v>93.51066719152016</v>
       </c>
       <c r="W24" t="n">
-        <v>432.3731429098285</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X24" t="n">
-        <v>419.8627394453875</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y24" t="n">
-        <v>399.3913927661343</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="25">
@@ -2565,13 +2565,13 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G26" t="n">
-        <v>78.4063405568529</v>
+        <v>81.36239741264433</v>
       </c>
       <c r="H26" t="n">
-        <v>72.72337227136661</v>
+        <v>72.7233722713666</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>4.805543144208367</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2607,7 +2607,7 @@
         <v>259.5690792160011</v>
       </c>
       <c r="U26" t="n">
-        <v>328.1096985586609</v>
+        <v>328.109698558661</v>
       </c>
       <c r="V26" t="n">
         <v>308.8510241668239</v>
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>246.7158234254702</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C27" t="n">
         <v>361.0999124455193</v>
@@ -2638,16 +2638,16 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E27" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F27" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G27" t="n">
-        <v>3.993158516536777</v>
+        <v>187.1524252956803</v>
       </c>
       <c r="H27" t="n">
-        <v>3.95965322415698</v>
+        <v>3.959653224156966</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -2683,10 +2683,10 @@
         <v>131.7003678891396</v>
       </c>
       <c r="T27" t="n">
-        <v>81.34934068921193</v>
+        <v>81.34934068921194</v>
       </c>
       <c r="U27" t="n">
-        <v>79.16125598660184</v>
+        <v>79.16125598660182</v>
       </c>
       <c r="V27" t="n">
         <v>93.51066719152016</v>
@@ -2738,7 +2738,7 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>9.517497010238188</v>
+        <v>9.517497010238174</v>
       </c>
       <c r="M28" t="n">
         <v>101.5443818943532</v>
@@ -2747,19 +2747,19 @@
         <v>154.4301408454554</v>
       </c>
       <c r="O28" t="n">
-        <v>231.0003837511461</v>
+        <v>231.000383751146</v>
       </c>
       <c r="P28" t="n">
         <v>290.7677661807365</v>
       </c>
       <c r="Q28" t="n">
-        <v>352.442266425598</v>
+        <v>352.4422664255979</v>
       </c>
       <c r="R28" t="n">
         <v>377.4666853582003</v>
       </c>
       <c r="S28" t="n">
-        <v>30.46857806351117</v>
+        <v>30.46857806351119</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -2802,13 +2802,13 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G29" t="n">
-        <v>81.36239741264433</v>
+        <v>81.36239741264436</v>
       </c>
       <c r="H29" t="n">
-        <v>69.76731541561503</v>
+        <v>72.72337227136661</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>4.80554314420855</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2844,7 +2844,7 @@
         <v>259.5690792160011</v>
       </c>
       <c r="U29" t="n">
-        <v>328.109698558661</v>
+        <v>328.1096985586609</v>
       </c>
       <c r="V29" t="n">
         <v>308.8510241668239</v>
@@ -2881,10 +2881,10 @@
         <v>18.63624233787687</v>
       </c>
       <c r="G30" t="n">
-        <v>3.993158516536766</v>
+        <v>3.993158516536777</v>
       </c>
       <c r="H30" t="n">
-        <v>3.959653224156966</v>
+        <v>3.95965322415698</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -2920,13 +2920,13 @@
         <v>131.7003678891396</v>
       </c>
       <c r="T30" t="n">
-        <v>81.34934068921194</v>
+        <v>81.34934068921193</v>
       </c>
       <c r="U30" t="n">
-        <v>79.16125598660182</v>
+        <v>79.16125598660184</v>
       </c>
       <c r="V30" t="n">
-        <v>276.669933970664</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W30" t="n">
         <v>432.3731429098285</v>
@@ -2935,7 +2935,7 @@
         <v>419.8627394453875</v>
       </c>
       <c r="Y30" t="n">
-        <v>399.3913927661343</v>
+        <v>261.5506595452778</v>
       </c>
     </row>
     <row r="31">
@@ -2975,7 +2975,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>9.517497010238174</v>
+        <v>9.517497010238188</v>
       </c>
       <c r="M31" t="n">
         <v>101.5443818943532</v>
@@ -2984,19 +2984,19 @@
         <v>154.4301408454554</v>
       </c>
       <c r="O31" t="n">
-        <v>231.000383751146</v>
+        <v>231.0003837511461</v>
       </c>
       <c r="P31" t="n">
         <v>290.7677661807365</v>
       </c>
       <c r="Q31" t="n">
-        <v>352.4422664255979</v>
+        <v>352.442266425598</v>
       </c>
       <c r="R31" t="n">
         <v>377.4666853582003</v>
       </c>
       <c r="S31" t="n">
-        <v>30.46857806351119</v>
+        <v>30.46857806351117</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -3039,10 +3039,10 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G32" t="n">
-        <v>81.36239741264436</v>
+        <v>81.36239741264433</v>
       </c>
       <c r="H32" t="n">
-        <v>72.72337227136661</v>
+        <v>77.52891541557497</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -3081,10 +3081,10 @@
         <v>259.5690792160011</v>
       </c>
       <c r="U32" t="n">
-        <v>328.1096985586609</v>
+        <v>328.109698558661</v>
       </c>
       <c r="V32" t="n">
-        <v>305.8949673110324</v>
+        <v>308.8510241668239</v>
       </c>
       <c r="W32" t="n">
         <v>317.3734759809475</v>
@@ -3103,10 +3103,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>168.9109734293304</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C33" t="n">
-        <v>361.0999124455193</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D33" t="n">
         <v>26.93768689770263</v>
@@ -3115,13 +3115,13 @@
         <v>21.67209722191262</v>
       </c>
       <c r="F33" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G33" t="n">
-        <v>3.993158516536777</v>
+        <v>3.993158516536766</v>
       </c>
       <c r="H33" t="n">
-        <v>3.95965322415698</v>
+        <v>3.959653224156966</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
@@ -3148,7 +3148,7 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>77.80484999613995</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
         <v>179.932929367851</v>
@@ -3157,22 +3157,22 @@
         <v>131.7003678891396</v>
       </c>
       <c r="T33" t="n">
-        <v>81.34934068921193</v>
+        <v>81.34934068921194</v>
       </c>
       <c r="U33" t="n">
-        <v>79.16125598660184</v>
+        <v>79.16125598660182</v>
       </c>
       <c r="V33" t="n">
-        <v>93.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W33" t="n">
-        <v>111.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X33" t="n">
         <v>419.8627394453875</v>
       </c>
       <c r="Y33" t="n">
-        <v>78.39139276613435</v>
+        <v>261.5506595452778</v>
       </c>
     </row>
     <row r="34">
@@ -3212,7 +3212,7 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>9.517497010238188</v>
+        <v>9.517497010238174</v>
       </c>
       <c r="M34" t="n">
         <v>101.5443818943532</v>
@@ -3221,19 +3221,19 @@
         <v>154.4301408454554</v>
       </c>
       <c r="O34" t="n">
-        <v>231.0003837511461</v>
+        <v>231.000383751146</v>
       </c>
       <c r="P34" t="n">
         <v>290.7677661807365</v>
       </c>
       <c r="Q34" t="n">
-        <v>352.442266425598</v>
+        <v>352.4422664255979</v>
       </c>
       <c r="R34" t="n">
         <v>377.4666853582003</v>
       </c>
       <c r="S34" t="n">
-        <v>30.46857806351117</v>
+        <v>30.46857806351119</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -3276,7 +3276,7 @@
         <v>59.88962870801186</v>
       </c>
       <c r="G35" t="n">
-        <v>52.7767405568525</v>
+        <v>57.36239741264435</v>
       </c>
       <c r="H35" t="n">
         <v>48.72337227136661</v>
@@ -3321,7 +3321,7 @@
         <v>304.1096985586609</v>
       </c>
       <c r="V35" t="n">
-        <v>284.8510241668239</v>
+        <v>284.1461673110321</v>
       </c>
       <c r="W35" t="n">
         <v>293.3734759809475</v>
@@ -3340,22 +3340,22 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>384.5565566463266</v>
+        <v>39.55655664632661</v>
       </c>
       <c r="C36" t="n">
         <v>361.0999124455193</v>
       </c>
       <c r="D36" t="n">
-        <v>23.72038892794801</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E36" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G36" t="n">
-        <v>324.9931585165368</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -3385,10 +3385,10 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>77.80484999613995</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>155.932929367851</v>
+        <v>242.0450078876883</v>
       </c>
       <c r="S36" t="n">
         <v>107.7003678891396</v>
@@ -3513,10 +3513,10 @@
         <v>59.88962870801186</v>
       </c>
       <c r="G38" t="n">
-        <v>52.7767405568525</v>
+        <v>57.36239741264433</v>
       </c>
       <c r="H38" t="n">
-        <v>48.72337227136661</v>
+        <v>48.0185154155748</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -3555,7 +3555,7 @@
         <v>235.5690792160011</v>
       </c>
       <c r="U38" t="n">
-        <v>304.1096985586609</v>
+        <v>304.109698558661</v>
       </c>
       <c r="V38" t="n">
         <v>284.8510241668239</v>
@@ -3580,16 +3580,16 @@
         <v>39.55655664632661</v>
       </c>
       <c r="C39" t="n">
-        <v>361.0999124455193</v>
+        <v>16.09991244551929</v>
       </c>
       <c r="D39" t="n">
-        <v>347.9376868977026</v>
+        <v>2.937686897702633</v>
       </c>
       <c r="E39" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>83.94446820504487</v>
+        <v>78.42041807962657</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3631,19 +3631,19 @@
         <v>107.7003678891396</v>
       </c>
       <c r="T39" t="n">
-        <v>57.34934068921193</v>
+        <v>57.34934068921194</v>
       </c>
       <c r="U39" t="n">
-        <v>55.16125598660184</v>
+        <v>400.1612559866018</v>
       </c>
       <c r="V39" t="n">
-        <v>69.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W39" t="n">
-        <v>87.37314290982852</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X39" t="n">
-        <v>74.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y39" t="n">
         <v>54.39139276613435</v>
@@ -3689,25 +3689,25 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>77.54438189435318</v>
+        <v>77.54438189435319</v>
       </c>
       <c r="N40" t="n">
         <v>130.4301408454554</v>
       </c>
       <c r="O40" t="n">
-        <v>207.0003837511461</v>
+        <v>207.000383751146</v>
       </c>
       <c r="P40" t="n">
         <v>266.7677661807365</v>
       </c>
       <c r="Q40" t="n">
-        <v>328.442266425598</v>
+        <v>328.4422664255979</v>
       </c>
       <c r="R40" t="n">
         <v>353.4666853582003</v>
       </c>
       <c r="S40" t="n">
-        <v>6.468578063511176</v>
+        <v>6.468578063511188</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -3735,25 +3735,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>132.4136560997828</v>
+        <v>141.9993129555745</v>
       </c>
       <c r="C41" t="n">
-        <v>104.4745782429939</v>
+        <v>109.4745782429939</v>
       </c>
       <c r="D41" t="n">
-        <v>65.33915573984979</v>
+        <v>70.33915573984979</v>
       </c>
       <c r="E41" t="n">
-        <v>59.36328960686865</v>
+        <v>64.36328960686865</v>
       </c>
       <c r="F41" t="n">
-        <v>59.88962870801186</v>
+        <v>64.88962870801186</v>
       </c>
       <c r="G41" t="n">
-        <v>57.36239741264433</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>48.7233722713666</v>
+        <v>45.38091282821921</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -3786,25 +3786,25 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>118.0601778525742</v>
+        <v>123.0601778525742</v>
       </c>
       <c r="T41" t="n">
-        <v>235.5690792160011</v>
+        <v>240.5690792160011</v>
       </c>
       <c r="U41" t="n">
-        <v>304.109698558661</v>
+        <v>309.109698558661</v>
       </c>
       <c r="V41" t="n">
-        <v>284.8510241668239</v>
+        <v>289.8510241668239</v>
       </c>
       <c r="W41" t="n">
-        <v>293.3734759809475</v>
+        <v>298.3734759809475</v>
       </c>
       <c r="X41" t="n">
-        <v>247.2818334606677</v>
+        <v>252.2818334606677</v>
       </c>
       <c r="Y41" t="n">
-        <v>166.3174326828064</v>
+        <v>171.3174326828064</v>
       </c>
     </row>
     <row r="42">
@@ -3814,28 +3814,28 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>39.55655664632661</v>
+        <v>44.55655664632661</v>
       </c>
       <c r="C42" t="n">
-        <v>16.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D42" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>41.11207851983727</v>
       </c>
       <c r="I42" t="n">
-        <v>191.4287443819146</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3862,28 +3862,28 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>500.932929367851</v>
+        <v>160.932929367851</v>
       </c>
       <c r="S42" t="n">
-        <v>452.7003678891396</v>
+        <v>112.7003678891396</v>
       </c>
       <c r="T42" t="n">
-        <v>287.173404072125</v>
+        <v>62.34934068921194</v>
       </c>
       <c r="U42" t="n">
-        <v>55.16125598660182</v>
+        <v>60.16125598660182</v>
       </c>
       <c r="V42" t="n">
-        <v>69.51066719152016</v>
+        <v>74.51066719152016</v>
       </c>
       <c r="W42" t="n">
-        <v>87.37314290982852</v>
+        <v>92.37314290982852</v>
       </c>
       <c r="X42" t="n">
-        <v>74.86273944538755</v>
+        <v>79.86273944538755</v>
       </c>
       <c r="Y42" t="n">
-        <v>54.39139276613435</v>
+        <v>59.39139276613435</v>
       </c>
     </row>
     <row r="43">
@@ -3926,25 +3926,25 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>77.54438189435319</v>
+        <v>82.54438189435319</v>
       </c>
       <c r="N43" t="n">
-        <v>130.4301408454554</v>
+        <v>135.4301408454554</v>
       </c>
       <c r="O43" t="n">
-        <v>207.000383751146</v>
+        <v>212.000383751146</v>
       </c>
       <c r="P43" t="n">
-        <v>266.7677661807365</v>
+        <v>271.7677661807365</v>
       </c>
       <c r="Q43" t="n">
-        <v>328.4422664255979</v>
+        <v>333.4422664255979</v>
       </c>
       <c r="R43" t="n">
-        <v>353.4666853582003</v>
+        <v>358.4666853582003</v>
       </c>
       <c r="S43" t="n">
-        <v>6.468578063511188</v>
+        <v>11.46857806351119</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -3972,25 +3972,25 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>136.9993129555745</v>
+        <v>141.9993129555745</v>
       </c>
       <c r="C44" t="n">
-        <v>104.4745782429939</v>
+        <v>109.4745782429939</v>
       </c>
       <c r="D44" t="n">
-        <v>65.33915573984979</v>
+        <v>70.33915573984979</v>
       </c>
       <c r="E44" t="n">
-        <v>59.36328960686865</v>
+        <v>64.36328960686865</v>
       </c>
       <c r="F44" t="n">
-        <v>59.88962870801186</v>
+        <v>64.88962870801186</v>
       </c>
       <c r="G44" t="n">
-        <v>52.7767405568525</v>
+        <v>62.36239741264433</v>
       </c>
       <c r="H44" t="n">
-        <v>48.72337227136661</v>
+        <v>53.7233722713666</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -4023,25 +4023,25 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>118.0601778525742</v>
+        <v>52.35532099678267</v>
       </c>
       <c r="T44" t="n">
-        <v>235.5690792160011</v>
+        <v>240.5690792160011</v>
       </c>
       <c r="U44" t="n">
-        <v>304.1096985586609</v>
+        <v>309.109698558661</v>
       </c>
       <c r="V44" t="n">
-        <v>284.8510241668239</v>
+        <v>289.8510241668239</v>
       </c>
       <c r="W44" t="n">
-        <v>293.3734759809475</v>
+        <v>298.3734759809475</v>
       </c>
       <c r="X44" t="n">
-        <v>247.2818334606677</v>
+        <v>252.2818334606677</v>
       </c>
       <c r="Y44" t="n">
-        <v>166.3174326828064</v>
+        <v>171.3174326828064</v>
       </c>
     </row>
     <row r="45">
@@ -4051,7 +4051,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>39.55655664632661</v>
+        <v>44.55655664632661</v>
       </c>
       <c r="C45" t="n">
         <v>361.0999124455193</v>
@@ -4060,16 +4060,16 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>2.672097221912622</v>
       </c>
       <c r="F45" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G45" t="n">
-        <v>324.9931585165368</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>101.6234069104207</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -4099,28 +4099,28 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>155.932929367851</v>
+        <v>160.932929367851</v>
       </c>
       <c r="S45" t="n">
-        <v>107.7003678891396</v>
+        <v>112.7003678891396</v>
       </c>
       <c r="T45" t="n">
-        <v>57.34934068921193</v>
+        <v>62.34934068921194</v>
       </c>
       <c r="U45" t="n">
-        <v>55.16125598660184</v>
+        <v>60.16125598660182</v>
       </c>
       <c r="V45" t="n">
-        <v>69.51066719152016</v>
+        <v>115.6227457113574</v>
       </c>
       <c r="W45" t="n">
-        <v>87.37314290982852</v>
+        <v>92.37314290982852</v>
       </c>
       <c r="X45" t="n">
-        <v>74.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y45" t="n">
-        <v>54.39139276613435</v>
+        <v>59.39139276613435</v>
       </c>
     </row>
     <row r="46">
@@ -4163,25 +4163,25 @@
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>77.54438189435318</v>
+        <v>82.54438189435319</v>
       </c>
       <c r="N46" t="n">
-        <v>130.4301408454554</v>
+        <v>135.4301408454554</v>
       </c>
       <c r="O46" t="n">
-        <v>207.0003837511461</v>
+        <v>212.000383751146</v>
       </c>
       <c r="P46" t="n">
-        <v>266.7677661807365</v>
+        <v>271.7677661807365</v>
       </c>
       <c r="Q46" t="n">
-        <v>328.442266425598</v>
+        <v>333.4422664255979</v>
       </c>
       <c r="R46" t="n">
-        <v>353.4666853582003</v>
+        <v>358.4666853582003</v>
       </c>
       <c r="S46" t="n">
-        <v>6.468578063511176</v>
+        <v>11.46857806351119</v>
       </c>
       <c r="T46" t="n">
         <v>0</v>
@@ -4297,22 +4297,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>108.8416377852039</v>
+        <v>106.8684999460195</v>
       </c>
       <c r="C2" t="n">
-        <v>58.86731632763432</v>
+        <v>56.89417848844992</v>
       </c>
       <c r="D2" t="n">
-        <v>48.42372467122039</v>
+        <v>46.450586832036</v>
       </c>
       <c r="E2" t="n">
-        <v>44.01636143195913</v>
+        <v>42.04322359277474</v>
       </c>
       <c r="F2" t="n">
-        <v>39.07734253497746</v>
+        <v>37.10420469579307</v>
       </c>
       <c r="G2" t="n">
-        <v>35.70026987310126</v>
+        <v>33.72713203391686</v>
       </c>
       <c r="H2" t="n">
         <v>29.92</v>
@@ -4324,22 +4324,22 @@
         <v>30.01969029977264</v>
       </c>
       <c r="K2" t="n">
-        <v>400.2796902997726</v>
+        <v>82.16427879223495</v>
       </c>
       <c r="L2" t="n">
-        <v>696.8157936111288</v>
+        <v>385.22</v>
       </c>
       <c r="M2" t="n">
-        <v>696.8157936111288</v>
+        <v>385.22</v>
       </c>
       <c r="N2" t="n">
-        <v>1067.075793611129</v>
+        <v>755.48</v>
       </c>
       <c r="O2" t="n">
-        <v>1437.335793611129</v>
+        <v>755.48</v>
       </c>
       <c r="P2" t="n">
-        <v>1496</v>
+        <v>1125.74</v>
       </c>
       <c r="Q2" t="n">
         <v>1496</v>
@@ -4348,25 +4348,25 @@
         <v>1496</v>
       </c>
       <c r="S2" t="n">
-        <v>1409.724707412506</v>
+        <v>1407.751569573322</v>
       </c>
       <c r="T2" t="n">
-        <v>1222.994415731961</v>
+        <v>1221.021277892777</v>
       </c>
       <c r="U2" t="n">
-        <v>971.2891925799718</v>
+        <v>969.3160547407873</v>
       </c>
       <c r="V2" t="n">
-        <v>739.1164408963112</v>
+        <v>737.1433030571268</v>
       </c>
       <c r="W2" t="n">
-        <v>498.3351520266672</v>
+        <v>496.3620141874828</v>
       </c>
       <c r="X2" t="n">
-        <v>304.1110778239726</v>
+        <v>302.1379399847881</v>
       </c>
       <c r="Y2" t="n">
-        <v>191.6692266292186</v>
+        <v>189.6960887900342</v>
       </c>
     </row>
     <row r="3">
@@ -4424,13 +4424,13 @@
         <v>1349.738421006376</v>
       </c>
       <c r="R3" t="n">
-        <v>971.9606432285987</v>
+        <v>1214.871311105555</v>
       </c>
       <c r="S3" t="n">
-        <v>594.1828654508208</v>
+        <v>837.0935333277773</v>
       </c>
       <c r="T3" t="n">
-        <v>309.3531363869131</v>
+        <v>459.3157555499995</v>
       </c>
       <c r="U3" t="n">
         <v>309.1553744793488</v>
@@ -4455,34 +4455,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>203.6877435615022</v>
+        <v>666.7881941016157</v>
       </c>
       <c r="C4" t="n">
-        <v>203.6877435615022</v>
+        <v>666.7881941016157</v>
       </c>
       <c r="D4" t="n">
-        <v>203.6877435615022</v>
+        <v>666.7881941016157</v>
       </c>
       <c r="E4" t="n">
-        <v>203.6877435615022</v>
+        <v>666.7881941016157</v>
       </c>
       <c r="F4" t="n">
-        <v>328.0487161534377</v>
+        <v>791.1491666935511</v>
       </c>
       <c r="G4" t="n">
-        <v>481.6391623681918</v>
+        <v>944.7396129083053</v>
       </c>
       <c r="H4" t="n">
-        <v>652.7906108062779</v>
+        <v>944.7396129083053</v>
       </c>
       <c r="I4" t="n">
-        <v>879.4532726931805</v>
+        <v>944.7396129083053</v>
       </c>
       <c r="J4" t="n">
-        <v>1249.71327269318</v>
+        <v>1253.739110653045</v>
       </c>
       <c r="K4" t="n">
-        <v>1381.441257449721</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="L4" t="n">
         <v>1385.467095409585</v>
@@ -4509,22 +4509,22 @@
         <v>70.37478771712392</v>
       </c>
       <c r="T4" t="n">
-        <v>203.6877435615022</v>
+        <v>70.37478771712392</v>
       </c>
       <c r="U4" t="n">
-        <v>203.6877435615022</v>
+        <v>316.9360101914762</v>
       </c>
       <c r="V4" t="n">
-        <v>203.6877435615022</v>
+        <v>515.7574030774222</v>
       </c>
       <c r="W4" t="n">
-        <v>203.6877435615022</v>
+        <v>515.7574030774222</v>
       </c>
       <c r="X4" t="n">
-        <v>203.6877435615022</v>
+        <v>666.7881941016157</v>
       </c>
       <c r="Y4" t="n">
-        <v>203.6877435615022</v>
+        <v>666.7881941016157</v>
       </c>
     </row>
     <row r="5">
@@ -4552,7 +4552,7 @@
         <v>35.70026987310013</v>
       </c>
       <c r="H5" t="n">
-        <v>29.92</v>
+        <v>31.89313783918327</v>
       </c>
       <c r="I5" t="n">
         <v>29.92</v>
@@ -4573,10 +4573,10 @@
         <v>1067.075793611129</v>
       </c>
       <c r="O5" t="n">
-        <v>1067.075793611129</v>
+        <v>1437.335793611129</v>
       </c>
       <c r="P5" t="n">
-        <v>1125.74</v>
+        <v>1496</v>
       </c>
       <c r="Q5" t="n">
         <v>1496</v>
@@ -4613,13 +4613,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>727.505640524864</v>
+        <v>29.92</v>
       </c>
       <c r="C6" t="n">
-        <v>727.505640524864</v>
+        <v>29.92</v>
       </c>
       <c r="D6" t="n">
-        <v>376.0534315372855</v>
+        <v>29.92</v>
       </c>
       <c r="E6" t="n">
         <v>29.92</v>
@@ -4679,10 +4679,10 @@
         <v>1099.526722235211</v>
       </c>
       <c r="X6" t="n">
-        <v>1079.463349058052</v>
+        <v>785.4755555555557</v>
       </c>
       <c r="Y6" t="n">
-        <v>1079.463349058052</v>
+        <v>407.6977777777778</v>
       </c>
     </row>
     <row r="7">
@@ -4692,28 +4692,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>259.2361373677321</v>
+        <v>29.92</v>
       </c>
       <c r="C7" t="n">
-        <v>259.2361373677321</v>
+        <v>29.92</v>
       </c>
       <c r="D7" t="n">
-        <v>259.2361373677321</v>
+        <v>143.2391441250001</v>
       </c>
       <c r="E7" t="n">
-        <v>259.2361373677321</v>
+        <v>261.0680483364131</v>
       </c>
       <c r="F7" t="n">
-        <v>328.0487161534377</v>
+        <v>385.4290209283486</v>
       </c>
       <c r="G7" t="n">
-        <v>481.6391623681918</v>
+        <v>539.0194671431027</v>
       </c>
       <c r="H7" t="n">
-        <v>652.7906108062779</v>
+        <v>710.1709155811888</v>
       </c>
       <c r="I7" t="n">
-        <v>879.4532726931805</v>
+        <v>936.8335774680913</v>
       </c>
       <c r="J7" t="n">
         <v>1249.71327269318</v>
@@ -4743,25 +4743,25 @@
         <v>29.92</v>
       </c>
       <c r="S7" t="n">
-        <v>70.37478771712392</v>
+        <v>29.92</v>
       </c>
       <c r="T7" t="n">
-        <v>259.2361373677321</v>
+        <v>29.92</v>
       </c>
       <c r="U7" t="n">
-        <v>259.2361373677321</v>
+        <v>29.92</v>
       </c>
       <c r="V7" t="n">
-        <v>259.2361373677321</v>
+        <v>29.92</v>
       </c>
       <c r="W7" t="n">
-        <v>259.2361373677321</v>
+        <v>29.92</v>
       </c>
       <c r="X7" t="n">
-        <v>259.2361373677321</v>
+        <v>29.92</v>
       </c>
       <c r="Y7" t="n">
-        <v>259.2361373677321</v>
+        <v>29.92</v>
       </c>
     </row>
     <row r="8">
@@ -4771,46 +4771,46 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>108.8416377852028</v>
+        <v>106.822852516955</v>
       </c>
       <c r="C8" t="n">
-        <v>58.86731632763319</v>
+        <v>56.84853105938534</v>
       </c>
       <c r="D8" t="n">
-        <v>48.42372467121926</v>
+        <v>46.40493940297141</v>
       </c>
       <c r="E8" t="n">
-        <v>44.016361431958</v>
+        <v>41.99757616371015</v>
       </c>
       <c r="F8" t="n">
-        <v>39.07734253497633</v>
+        <v>37.05855726672848</v>
       </c>
       <c r="G8" t="n">
-        <v>35.70026987310013</v>
+        <v>33.6855453124306</v>
       </c>
       <c r="H8" t="n">
-        <v>31.89313783918327</v>
+        <v>29.92</v>
       </c>
       <c r="I8" t="n">
         <v>29.92</v>
       </c>
       <c r="J8" t="n">
-        <v>30.01969029977264</v>
+        <v>30.35747929474751</v>
       </c>
       <c r="K8" t="n">
-        <v>400.2796902997726</v>
+        <v>400.6174792947475</v>
       </c>
       <c r="L8" t="n">
-        <v>770.5396902997726</v>
+        <v>770.8774792947474</v>
       </c>
       <c r="M8" t="n">
-        <v>770.5396902997726</v>
+        <v>1066.30976765531</v>
       </c>
       <c r="N8" t="n">
-        <v>1067.075793611129</v>
+        <v>1066.30976765531</v>
       </c>
       <c r="O8" t="n">
-        <v>1067.075793611129</v>
+        <v>1066.503479088516</v>
       </c>
       <c r="P8" t="n">
         <v>1125.74</v>
@@ -4819,28 +4819,28 @@
         <v>1496</v>
       </c>
       <c r="R8" t="n">
-        <v>1496</v>
+        <v>1493.870580753781</v>
       </c>
       <c r="S8" t="n">
-        <v>1409.724707412506</v>
+        <v>1407.687821540228</v>
       </c>
       <c r="T8" t="n">
-        <v>1222.994415731961</v>
+        <v>1220.975305607106</v>
       </c>
       <c r="U8" t="n">
-        <v>971.2891925799706</v>
+        <v>969.2704073117228</v>
       </c>
       <c r="V8" t="n">
-        <v>739.1164408963101</v>
+        <v>737.0976556280623</v>
       </c>
       <c r="W8" t="n">
-        <v>498.3351520266661</v>
+        <v>496.3163667584182</v>
       </c>
       <c r="X8" t="n">
-        <v>304.1110778239714</v>
+        <v>302.0922925557235</v>
       </c>
       <c r="Y8" t="n">
-        <v>191.6692266292175</v>
+        <v>189.6504413609696</v>
       </c>
     </row>
     <row r="9">
@@ -4850,13 +4850,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>376.0534315372855</v>
+        <v>746.1195952961839</v>
       </c>
       <c r="C9" t="n">
-        <v>376.0534315372855</v>
+        <v>381.3722089875785</v>
       </c>
       <c r="D9" t="n">
-        <v>376.0534315372855</v>
+        <v>29.92</v>
       </c>
       <c r="E9" t="n">
         <v>29.92</v>
@@ -4874,52 +4874,52 @@
         <v>29.92</v>
       </c>
       <c r="J9" t="n">
-        <v>174.5985557413367</v>
+        <v>174.7997405526575</v>
       </c>
       <c r="K9" t="n">
-        <v>399.2086311753428</v>
+        <v>399.7536728734559</v>
       </c>
       <c r="L9" t="n">
-        <v>718.1819687139391</v>
+        <v>719.1893684309202</v>
       </c>
       <c r="M9" t="n">
-        <v>859.8361604567983</v>
+        <v>861.3831101737794</v>
       </c>
       <c r="N9" t="n">
-        <v>1050.16096421531</v>
+        <v>1052.26174421531</v>
       </c>
       <c r="O9" t="n">
-        <v>1341.388006370727</v>
+        <v>1343.995432880161</v>
       </c>
       <c r="P9" t="n">
-        <v>1495.800085368536</v>
+        <v>1496</v>
       </c>
       <c r="Q9" t="n">
-        <v>1349.538506374912</v>
+        <v>1496</v>
       </c>
       <c r="R9" t="n">
-        <v>1214.671396474091</v>
+        <v>1361.267786230301</v>
       </c>
       <c r="S9" t="n">
-        <v>1151.591741468861</v>
+        <v>1196.016865160776</v>
       </c>
       <c r="T9" t="n">
-        <v>1147.081868083532</v>
+        <v>1191.515749160619</v>
       </c>
       <c r="U9" t="n">
-        <v>1146.884106175968</v>
+        <v>1191.318130191877</v>
       </c>
       <c r="V9" t="n">
-        <v>769.1063283981898</v>
+        <v>1176.660890604483</v>
       </c>
       <c r="W9" t="n">
-        <v>396.1168047144446</v>
+        <v>1143.960746251121</v>
       </c>
       <c r="X9" t="n">
-        <v>376.0534315372855</v>
+        <v>1123.897373073962</v>
       </c>
       <c r="Y9" t="n">
-        <v>376.0534315372855</v>
+        <v>1123.897373073962</v>
       </c>
     </row>
     <row r="10">
@@ -4929,52 +4929,52 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>29.92</v>
+        <v>1021.391060366543</v>
       </c>
       <c r="C10" t="n">
-        <v>29.92</v>
+        <v>1147.393066184978</v>
       </c>
       <c r="D10" t="n">
-        <v>85.85883935008918</v>
+        <v>1260.712210309978</v>
       </c>
       <c r="E10" t="n">
-        <v>203.6877435615022</v>
+        <v>1378.541114521391</v>
       </c>
       <c r="F10" t="n">
-        <v>328.0487161534377</v>
+        <v>1384.190642354444</v>
       </c>
       <c r="G10" t="n">
-        <v>481.6391623681918</v>
+        <v>1384.190642354444</v>
       </c>
       <c r="H10" t="n">
-        <v>652.7906108062779</v>
+        <v>1384.190642354444</v>
       </c>
       <c r="I10" t="n">
-        <v>879.4532726931805</v>
+        <v>1384.190642354444</v>
       </c>
       <c r="J10" t="n">
-        <v>1249.71327269318</v>
+        <v>1384.190642354444</v>
       </c>
       <c r="K10" t="n">
-        <v>1381.441257449721</v>
+        <v>1384.190642354444</v>
       </c>
       <c r="L10" t="n">
-        <v>1385.467095409585</v>
+        <v>1384.190642354444</v>
       </c>
       <c r="M10" t="n">
-        <v>1293.026305617309</v>
+        <v>1292.035379967368</v>
       </c>
       <c r="N10" t="n">
-        <v>1148.822122945132</v>
+        <v>1148.109935496879</v>
       </c>
       <c r="O10" t="n">
-        <v>932.4661797621563</v>
+        <v>932.0114521582486</v>
       </c>
       <c r="P10" t="n">
-        <v>664.8058098826245</v>
+        <v>664.5713836531164</v>
       </c>
       <c r="Q10" t="n">
-        <v>351.3853387456568</v>
+        <v>351.3034377686739</v>
       </c>
       <c r="R10" t="n">
         <v>29.92</v>
@@ -4986,19 +4986,19 @@
         <v>29.92</v>
       </c>
       <c r="U10" t="n">
-        <v>29.92</v>
+        <v>276.4813198514014</v>
       </c>
       <c r="V10" t="n">
-        <v>29.92</v>
+        <v>475.3027127373473</v>
       </c>
       <c r="W10" t="n">
-        <v>29.92</v>
+        <v>647.1936309970248</v>
       </c>
       <c r="X10" t="n">
-        <v>29.92</v>
+        <v>798.2244220212183</v>
       </c>
       <c r="Y10" t="n">
-        <v>29.92</v>
+        <v>909.6337227002506</v>
       </c>
     </row>
     <row r="11">
@@ -5008,76 +5008,76 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>596.4384060421568</v>
+        <v>596.5184060421568</v>
       </c>
       <c r="C11" t="n">
-        <v>466.6661047866074</v>
+        <v>466.7461047866074</v>
       </c>
       <c r="D11" t="n">
-        <v>376.4245333322136</v>
+        <v>376.5045333322136</v>
       </c>
       <c r="E11" t="n">
-        <v>292.2191902949726</v>
+        <v>292.2991902949726</v>
       </c>
       <c r="F11" t="n">
-        <v>207.4821916000111</v>
+        <v>207.5621916000111</v>
       </c>
       <c r="G11" t="n">
-        <v>125.2979517892592</v>
+        <v>125.3779517892592</v>
       </c>
       <c r="H11" t="n">
-        <v>51.84</v>
+        <v>51.92</v>
       </c>
       <c r="I11" t="n">
-        <v>51.84</v>
+        <v>51.92</v>
       </c>
       <c r="J11" t="n">
-        <v>560.3618942939371</v>
+        <v>560.4418942939371</v>
       </c>
       <c r="K11" t="n">
-        <v>736.0334691180577</v>
+        <v>1202.951894293937</v>
       </c>
       <c r="L11" t="n">
-        <v>1001.294971748369</v>
+        <v>1845.461894293937</v>
       </c>
       <c r="M11" t="n">
-        <v>1642.814971748371</v>
+        <v>1845.461894293937</v>
       </c>
       <c r="N11" t="n">
-        <v>1642.814971748371</v>
+        <v>2234.549243836214</v>
       </c>
       <c r="O11" t="n">
-        <v>1805.956778005698</v>
+        <v>2397.691050093541</v>
       </c>
       <c r="P11" t="n">
-        <v>2004.265727912157</v>
+        <v>2596</v>
       </c>
       <c r="Q11" t="n">
-        <v>2592</v>
+        <v>2596</v>
       </c>
       <c r="R11" t="n">
-        <v>2592</v>
+        <v>2596</v>
       </c>
       <c r="S11" t="n">
-        <v>2448.504870855986</v>
+        <v>2451.570786871937</v>
       </c>
       <c r="T11" t="n">
-        <v>2189.299797764865</v>
+        <v>2189.379797764865</v>
       </c>
       <c r="U11" t="n">
-        <v>1857.875859826824</v>
+        <v>1857.955859826824</v>
       </c>
       <c r="V11" t="n">
-        <v>1545.905128345183</v>
+        <v>1545.985128345183</v>
       </c>
       <c r="W11" t="n">
-        <v>1225.325859677559</v>
+        <v>1225.405859677559</v>
       </c>
       <c r="X11" t="n">
-        <v>951.3038056768851</v>
+        <v>951.383805676885</v>
       </c>
       <c r="Y11" t="n">
-        <v>759.0639746841513</v>
+        <v>759.1439746841513</v>
       </c>
     </row>
     <row r="12">
@@ -5087,76 +5087,76 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>816.7882329734397</v>
+        <v>1001.877593356413</v>
       </c>
       <c r="C12" t="n">
-        <v>452.0408466648343</v>
+        <v>961.372631290232</v>
       </c>
       <c r="D12" t="n">
-        <v>424.8310619196801</v>
+        <v>749.1534861621044</v>
       </c>
       <c r="E12" t="n">
-        <v>78.69763038239458</v>
+        <v>403.0200546248188</v>
       </c>
       <c r="F12" t="n">
-        <v>59.87314317241794</v>
+        <v>59.95314317241794</v>
       </c>
       <c r="G12" t="n">
-        <v>55.83964972137069</v>
+        <v>55.91964972137069</v>
       </c>
       <c r="H12" t="n">
-        <v>51.84</v>
+        <v>51.92</v>
       </c>
       <c r="I12" t="n">
-        <v>51.84</v>
+        <v>51.92</v>
       </c>
       <c r="J12" t="n">
-        <v>245.6076497036009</v>
+        <v>245.6876497036009</v>
       </c>
       <c r="K12" t="n">
-        <v>554.1188055149654</v>
+        <v>554.1988055149654</v>
       </c>
       <c r="L12" t="n">
-        <v>985.9074996573354</v>
+        <v>985.9874996573354</v>
       </c>
       <c r="M12" t="n">
-        <v>1259.211891400195</v>
+        <v>1259.291891400195</v>
       </c>
       <c r="N12" t="n">
-        <v>1584.67128421531</v>
+        <v>1584.75128421531</v>
       </c>
       <c r="O12" t="n">
-        <v>1999.520074672614</v>
+        <v>1999.600074672614</v>
       </c>
       <c r="P12" t="n">
-        <v>2253.149505368536</v>
+        <v>2253.229505368536</v>
       </c>
       <c r="Q12" t="n">
-        <v>2253.149505368536</v>
+        <v>2253.229505368536</v>
       </c>
       <c r="R12" t="n">
-        <v>2071.399071663636</v>
+        <v>2071.479071663636</v>
       </c>
       <c r="S12" t="n">
-        <v>1938.368397028141</v>
+        <v>1938.448397028141</v>
       </c>
       <c r="T12" t="n">
-        <v>1856.197345826917</v>
+        <v>1856.277345826917</v>
       </c>
       <c r="U12" t="n">
-        <v>1776.236481193986</v>
+        <v>1776.316481193986</v>
       </c>
       <c r="V12" t="n">
-        <v>1681.781261808612</v>
+        <v>1681.861261808612</v>
       </c>
       <c r="W12" t="n">
-        <v>1569.28313765727</v>
+        <v>1245.120713414846</v>
       </c>
       <c r="X12" t="n">
-        <v>1469.421784682131</v>
+        <v>1145.259360439707</v>
       </c>
       <c r="Y12" t="n">
-        <v>1205.22919928286</v>
+        <v>1066.07613542341</v>
       </c>
     </row>
     <row r="13">
@@ -5166,76 +5166,76 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>686.5872726401018</v>
+        <v>681.5388756890411</v>
       </c>
       <c r="C13" t="n">
-        <v>734.3792784585376</v>
+        <v>729.3308815074769</v>
       </c>
       <c r="D13" t="n">
-        <v>769.4884225835376</v>
+        <v>764.4400256324769</v>
       </c>
       <c r="E13" t="n">
-        <v>809.1073267949506</v>
+        <v>804.0589298438899</v>
       </c>
       <c r="F13" t="n">
-        <v>855.2582993868861</v>
+        <v>850.2099024358254</v>
       </c>
       <c r="G13" t="n">
-        <v>931.0743456016402</v>
+        <v>926.0259486505795</v>
       </c>
       <c r="H13" t="n">
-        <v>1027.888674039726</v>
+        <v>1022.840277088666</v>
       </c>
       <c r="I13" t="n">
-        <v>1189.441015926629</v>
+        <v>1184.392618975568</v>
       </c>
       <c r="J13" t="n">
-        <v>1510.983618808348</v>
+        <v>1511.063618808347</v>
       </c>
       <c r="K13" t="n">
-        <v>1615.110403564888</v>
+        <v>1615.190403564888</v>
       </c>
       <c r="L13" t="n">
-        <v>1605.496770221213</v>
+        <v>1605.576770221213</v>
       </c>
       <c r="M13" t="n">
-        <v>1502.926687499644</v>
+        <v>1503.006687499644</v>
       </c>
       <c r="N13" t="n">
-        <v>1346.936646241608</v>
+        <v>1347.016646241608</v>
       </c>
       <c r="O13" t="n">
-        <v>1113.602925280855</v>
+        <v>1113.682925280855</v>
       </c>
       <c r="P13" t="n">
-        <v>819.8981109568782</v>
+        <v>819.9781109568783</v>
       </c>
       <c r="Q13" t="n">
-        <v>463.8958216380923</v>
+        <v>463.9758216380924</v>
       </c>
       <c r="R13" t="n">
-        <v>82.61634147829412</v>
+        <v>82.69634147829412</v>
       </c>
       <c r="S13" t="n">
-        <v>51.84</v>
+        <v>51.92</v>
       </c>
       <c r="T13" t="n">
-        <v>164.3525496506081</v>
+        <v>164.4325496506081</v>
       </c>
       <c r="U13" t="n">
-        <v>332.7275321249604</v>
+        <v>327.6791351738997</v>
       </c>
       <c r="V13" t="n">
-        <v>453.3389250109063</v>
+        <v>448.2905280598457</v>
       </c>
       <c r="W13" t="n">
-        <v>547.0198432705838</v>
+        <v>541.9714463195231</v>
       </c>
       <c r="X13" t="n">
-        <v>619.8406342947774</v>
+        <v>614.7922373437167</v>
       </c>
       <c r="Y13" t="n">
-        <v>653.0399349738096</v>
+        <v>647.991538022749</v>
       </c>
     </row>
     <row r="14">
@@ -5245,76 +5245,76 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>593.4524900262056</v>
+        <v>596.5184060421567</v>
       </c>
       <c r="C14" t="n">
-        <v>463.6801887706562</v>
+        <v>466.7461047866073</v>
       </c>
       <c r="D14" t="n">
-        <v>373.4386173162624</v>
+        <v>376.5045333322136</v>
       </c>
       <c r="E14" t="n">
-        <v>289.2332742790214</v>
+        <v>292.2991902949725</v>
       </c>
       <c r="F14" t="n">
-        <v>204.4962755840599</v>
+        <v>207.562191600011</v>
       </c>
       <c r="G14" t="n">
-        <v>125.2979517892592</v>
+        <v>125.3779517892592</v>
       </c>
       <c r="H14" t="n">
-        <v>51.84</v>
+        <v>51.92</v>
       </c>
       <c r="I14" t="n">
-        <v>51.84</v>
+        <v>51.92</v>
       </c>
       <c r="J14" t="n">
-        <v>134.360205073642</v>
+        <v>329.6380305754733</v>
       </c>
       <c r="K14" t="n">
-        <v>503.2896053995884</v>
+        <v>505.3096053995939</v>
       </c>
       <c r="L14" t="n">
-        <v>721.2257279121512</v>
+        <v>723.2457279121568</v>
       </c>
       <c r="M14" t="n">
-        <v>721.2257279121512</v>
+        <v>723.2457279121568</v>
       </c>
       <c r="N14" t="n">
-        <v>721.2257279121512</v>
+        <v>723.2457279121568</v>
       </c>
       <c r="O14" t="n">
-        <v>1362.745727912154</v>
+        <v>1365.755727912157</v>
       </c>
       <c r="P14" t="n">
-        <v>2004.265727912157</v>
+        <v>2008.265727912157</v>
       </c>
       <c r="Q14" t="n">
-        <v>2592</v>
+        <v>2596</v>
       </c>
       <c r="R14" t="n">
-        <v>2592</v>
+        <v>2596</v>
       </c>
       <c r="S14" t="n">
-        <v>2448.504870855986</v>
+        <v>2451.570786871937</v>
       </c>
       <c r="T14" t="n">
-        <v>2186.313881748914</v>
+        <v>2189.379797764865</v>
       </c>
       <c r="U14" t="n">
-        <v>1854.889943810872</v>
+        <v>1857.955859826824</v>
       </c>
       <c r="V14" t="n">
-        <v>1542.919212329232</v>
+        <v>1545.985128345183</v>
       </c>
       <c r="W14" t="n">
-        <v>1222.339943661608</v>
+        <v>1225.405859677559</v>
       </c>
       <c r="X14" t="n">
-        <v>948.3178896609338</v>
+        <v>951.383805676885</v>
       </c>
       <c r="Y14" t="n">
-        <v>756.0780586682001</v>
+        <v>759.1439746841512</v>
       </c>
     </row>
     <row r="15">
@@ -5324,76 +5324,76 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>492.5458087310154</v>
+        <v>168.383384488591</v>
       </c>
       <c r="C15" t="n">
-        <v>452.0408466648342</v>
+        <v>127.87842242241</v>
       </c>
       <c r="D15" t="n">
-        <v>100.5886376772558</v>
+        <v>100.6686376772558</v>
       </c>
       <c r="E15" t="n">
-        <v>78.69763038239455</v>
+        <v>78.77763038239453</v>
       </c>
       <c r="F15" t="n">
-        <v>59.87314317241791</v>
+        <v>59.95314317241791</v>
       </c>
       <c r="G15" t="n">
-        <v>55.83964972137068</v>
+        <v>55.91964972137067</v>
       </c>
       <c r="H15" t="n">
-        <v>51.84</v>
+        <v>51.92</v>
       </c>
       <c r="I15" t="n">
-        <v>51.84</v>
+        <v>51.92</v>
       </c>
       <c r="J15" t="n">
-        <v>245.6076497036009</v>
+        <v>245.6876497036009</v>
       </c>
       <c r="K15" t="n">
-        <v>554.1188055149654</v>
+        <v>554.1988055149654</v>
       </c>
       <c r="L15" t="n">
-        <v>985.9074996573354</v>
+        <v>985.9874996573354</v>
       </c>
       <c r="M15" t="n">
-        <v>1259.211891400195</v>
+        <v>1259.291891400195</v>
       </c>
       <c r="N15" t="n">
-        <v>1584.67128421531</v>
+        <v>1584.75128421531</v>
       </c>
       <c r="O15" t="n">
-        <v>1999.520074672614</v>
+        <v>1999.600074672614</v>
       </c>
       <c r="P15" t="n">
-        <v>2253.149505368536</v>
+        <v>2253.229505368536</v>
       </c>
       <c r="Q15" t="n">
-        <v>2253.149505368536</v>
+        <v>2253.229505368536</v>
       </c>
       <c r="R15" t="n">
-        <v>2071.399071663636</v>
+        <v>2071.479071663636</v>
       </c>
       <c r="S15" t="n">
-        <v>1938.368397028141</v>
+        <v>1938.448397028141</v>
       </c>
       <c r="T15" t="n">
-        <v>1856.197345826917</v>
+        <v>1856.277345826917</v>
       </c>
       <c r="U15" t="n">
-        <v>1776.236481193986</v>
+        <v>1776.316481193986</v>
       </c>
       <c r="V15" t="n">
-        <v>1681.781261808612</v>
+        <v>1357.618837566188</v>
       </c>
       <c r="W15" t="n">
-        <v>1384.273777274297</v>
+        <v>920.8782891724215</v>
       </c>
       <c r="X15" t="n">
-        <v>960.1700000567336</v>
+        <v>496.7745119548583</v>
       </c>
       <c r="Y15" t="n">
-        <v>880.9867750404362</v>
+        <v>232.5819265555876</v>
       </c>
     </row>
     <row r="16">
@@ -5403,76 +5403,76 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>686.5872726401018</v>
+        <v>681.5388756890411</v>
       </c>
       <c r="C16" t="n">
-        <v>734.3792784585376</v>
+        <v>729.3308815074769</v>
       </c>
       <c r="D16" t="n">
-        <v>769.4884225835376</v>
+        <v>764.4400256324769</v>
       </c>
       <c r="E16" t="n">
-        <v>809.1073267949506</v>
+        <v>804.0589298438899</v>
       </c>
       <c r="F16" t="n">
-        <v>855.2582993868861</v>
+        <v>850.2099024358254</v>
       </c>
       <c r="G16" t="n">
-        <v>931.0743456016402</v>
+        <v>926.0259486505795</v>
       </c>
       <c r="H16" t="n">
-        <v>1027.888674039726</v>
+        <v>1022.840277088666</v>
       </c>
       <c r="I16" t="n">
-        <v>1189.441015926629</v>
+        <v>1184.392618975568</v>
       </c>
       <c r="J16" t="n">
-        <v>1516.112015759408</v>
+        <v>1511.063618808347</v>
       </c>
       <c r="K16" t="n">
-        <v>1615.110403564888</v>
+        <v>1615.190403564888</v>
       </c>
       <c r="L16" t="n">
-        <v>1605.496770221213</v>
+        <v>1605.576770221213</v>
       </c>
       <c r="M16" t="n">
-        <v>1502.926687499644</v>
+        <v>1503.006687499644</v>
       </c>
       <c r="N16" t="n">
-        <v>1346.936646241608</v>
+        <v>1347.016646241608</v>
       </c>
       <c r="O16" t="n">
-        <v>1113.602925280855</v>
+        <v>1113.682925280855</v>
       </c>
       <c r="P16" t="n">
-        <v>819.8981109568782</v>
+        <v>819.9781109568783</v>
       </c>
       <c r="Q16" t="n">
-        <v>463.8958216380924</v>
+        <v>463.9758216380924</v>
       </c>
       <c r="R16" t="n">
-        <v>82.61634147829413</v>
+        <v>82.69634147829413</v>
       </c>
       <c r="S16" t="n">
-        <v>51.84</v>
+        <v>51.92</v>
       </c>
       <c r="T16" t="n">
-        <v>164.3525496506081</v>
+        <v>159.3041526995475</v>
       </c>
       <c r="U16" t="n">
-        <v>332.7275321249604</v>
+        <v>327.6791351738997</v>
       </c>
       <c r="V16" t="n">
-        <v>453.3389250109063</v>
+        <v>448.2905280598457</v>
       </c>
       <c r="W16" t="n">
-        <v>547.0198432705838</v>
+        <v>541.9714463195231</v>
       </c>
       <c r="X16" t="n">
-        <v>619.8406342947774</v>
+        <v>614.7922373437167</v>
       </c>
       <c r="Y16" t="n">
-        <v>653.0399349738096</v>
+        <v>647.991538022749</v>
       </c>
     </row>
     <row r="17">
@@ -5482,76 +5482,76 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>596.4384060421568</v>
+        <v>596.5184060421568</v>
       </c>
       <c r="C17" t="n">
-        <v>466.6661047866073</v>
+        <v>466.7461047866074</v>
       </c>
       <c r="D17" t="n">
-        <v>376.4245333322136</v>
+        <v>376.5045333322136</v>
       </c>
       <c r="E17" t="n">
-        <v>292.2191902949725</v>
+        <v>292.2991902949726</v>
       </c>
       <c r="F17" t="n">
-        <v>207.482191600011</v>
+        <v>207.5621916000111</v>
       </c>
       <c r="G17" t="n">
-        <v>125.2979517892592</v>
+        <v>125.3779517892592</v>
       </c>
       <c r="H17" t="n">
-        <v>51.84</v>
+        <v>51.92</v>
       </c>
       <c r="I17" t="n">
-        <v>51.84</v>
+        <v>51.92</v>
       </c>
       <c r="J17" t="n">
-        <v>560.3618942939371</v>
+        <v>134.440205073642</v>
       </c>
       <c r="K17" t="n">
-        <v>1201.881894293937</v>
+        <v>776.950205073642</v>
       </c>
       <c r="L17" t="n">
-        <v>1642.814971748371</v>
+        <v>1419.460205073642</v>
       </c>
       <c r="M17" t="n">
-        <v>1642.814971748371</v>
+        <v>2061.970205073642</v>
       </c>
       <c r="N17" t="n">
-        <v>1642.814971748371</v>
+        <v>2234.549243836214</v>
       </c>
       <c r="O17" t="n">
-        <v>1805.956778005698</v>
+        <v>2397.691050093541</v>
       </c>
       <c r="P17" t="n">
-        <v>2004.265727912157</v>
+        <v>2596</v>
       </c>
       <c r="Q17" t="n">
-        <v>2592</v>
+        <v>2596</v>
       </c>
       <c r="R17" t="n">
-        <v>2592</v>
+        <v>2595.065916015951</v>
       </c>
       <c r="S17" t="n">
-        <v>2448.504870855986</v>
+        <v>2451.570786871937</v>
       </c>
       <c r="T17" t="n">
-        <v>2186.313881748914</v>
+        <v>2189.379797764865</v>
       </c>
       <c r="U17" t="n">
-        <v>1854.889943810872</v>
+        <v>1857.955859826824</v>
       </c>
       <c r="V17" t="n">
-        <v>1542.919212329232</v>
+        <v>1545.985128345183</v>
       </c>
       <c r="W17" t="n">
-        <v>1222.339943661608</v>
+        <v>1225.405859677559</v>
       </c>
       <c r="X17" t="n">
-        <v>948.3178896609338</v>
+        <v>951.383805676885</v>
       </c>
       <c r="Y17" t="n">
-        <v>759.0639746841513</v>
+        <v>759.1439746841513</v>
       </c>
     </row>
     <row r="18">
@@ -5561,76 +5561,76 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1326.040017598837</v>
+        <v>1326.120017598837</v>
       </c>
       <c r="C18" t="n">
-        <v>1100.525695149683</v>
+        <v>1100.605695149683</v>
       </c>
       <c r="D18" t="n">
-        <v>749.0734861621042</v>
+        <v>749.1534861621044</v>
       </c>
       <c r="E18" t="n">
-        <v>402.9400546248188</v>
+        <v>403.0200546248188</v>
       </c>
       <c r="F18" t="n">
-        <v>59.87314317241791</v>
+        <v>59.95314317241794</v>
       </c>
       <c r="G18" t="n">
-        <v>55.83964972137068</v>
+        <v>55.91964972137069</v>
       </c>
       <c r="H18" t="n">
-        <v>51.84</v>
+        <v>51.92</v>
       </c>
       <c r="I18" t="n">
-        <v>51.84</v>
+        <v>51.92</v>
       </c>
       <c r="J18" t="n">
-        <v>245.6076497036009</v>
+        <v>245.6876497036009</v>
       </c>
       <c r="K18" t="n">
-        <v>554.1188055149654</v>
+        <v>554.1988055149654</v>
       </c>
       <c r="L18" t="n">
-        <v>985.9074996573354</v>
+        <v>985.9874996573354</v>
       </c>
       <c r="M18" t="n">
-        <v>1259.211891400195</v>
+        <v>1259.291891400195</v>
       </c>
       <c r="N18" t="n">
-        <v>1584.67128421531</v>
+        <v>1584.75128421531</v>
       </c>
       <c r="O18" t="n">
-        <v>1999.520074672614</v>
+        <v>1999.600074672614</v>
       </c>
       <c r="P18" t="n">
-        <v>2253.149505368536</v>
+        <v>2253.229505368536</v>
       </c>
       <c r="Q18" t="n">
-        <v>2253.149505368536</v>
+        <v>2253.229505368536</v>
       </c>
       <c r="R18" t="n">
-        <v>2071.399071663636</v>
+        <v>2071.479071663636</v>
       </c>
       <c r="S18" t="n">
-        <v>1938.368397028141</v>
+        <v>1938.448397028141</v>
       </c>
       <c r="T18" t="n">
-        <v>1856.197345826917</v>
+        <v>1856.277345826917</v>
       </c>
       <c r="U18" t="n">
-        <v>1776.236481193986</v>
+        <v>1776.316481193986</v>
       </c>
       <c r="V18" t="n">
-        <v>1681.781261808612</v>
+        <v>1681.861261808612</v>
       </c>
       <c r="W18" t="n">
-        <v>1569.28313765727</v>
+        <v>1569.36313765727</v>
       </c>
       <c r="X18" t="n">
-        <v>1469.421784682131</v>
+        <v>1469.501784682131</v>
       </c>
       <c r="Y18" t="n">
-        <v>1390.238559665834</v>
+        <v>1390.318559665834</v>
       </c>
     </row>
     <row r="19">
@@ -5640,76 +5640,76 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>681.4588756890412</v>
+        <v>686.6672726401017</v>
       </c>
       <c r="C19" t="n">
-        <v>729.2508815074769</v>
+        <v>734.4592784585375</v>
       </c>
       <c r="D19" t="n">
-        <v>764.360025632477</v>
+        <v>769.5684225835375</v>
       </c>
       <c r="E19" t="n">
-        <v>803.97892984389</v>
+        <v>804.0589298438899</v>
       </c>
       <c r="F19" t="n">
-        <v>850.1299024358254</v>
+        <v>850.2099024358254</v>
       </c>
       <c r="G19" t="n">
-        <v>925.9459486505796</v>
+        <v>926.0259486505795</v>
       </c>
       <c r="H19" t="n">
-        <v>1022.760277088666</v>
+        <v>1022.840277088666</v>
       </c>
       <c r="I19" t="n">
-        <v>1184.312618975568</v>
+        <v>1184.392618975568</v>
       </c>
       <c r="J19" t="n">
-        <v>1510.983618808348</v>
+        <v>1511.063618808347</v>
       </c>
       <c r="K19" t="n">
-        <v>1615.110403564888</v>
+        <v>1615.190403564888</v>
       </c>
       <c r="L19" t="n">
-        <v>1605.496770221213</v>
+        <v>1605.576770221213</v>
       </c>
       <c r="M19" t="n">
-        <v>1502.926687499644</v>
+        <v>1503.006687499644</v>
       </c>
       <c r="N19" t="n">
-        <v>1346.936646241608</v>
+        <v>1347.016646241608</v>
       </c>
       <c r="O19" t="n">
-        <v>1113.602925280855</v>
+        <v>1113.682925280855</v>
       </c>
       <c r="P19" t="n">
-        <v>819.8981109568782</v>
+        <v>819.9781109568783</v>
       </c>
       <c r="Q19" t="n">
-        <v>463.8958216380924</v>
+        <v>463.9758216380924</v>
       </c>
       <c r="R19" t="n">
-        <v>82.61634147829413</v>
+        <v>82.69634147829412</v>
       </c>
       <c r="S19" t="n">
-        <v>51.84</v>
+        <v>51.92</v>
       </c>
       <c r="T19" t="n">
-        <v>164.3525496506081</v>
+        <v>164.4325496506081</v>
       </c>
       <c r="U19" t="n">
-        <v>327.5991351738998</v>
+        <v>332.8075321249603</v>
       </c>
       <c r="V19" t="n">
-        <v>448.2105280598458</v>
+        <v>453.4189250109063</v>
       </c>
       <c r="W19" t="n">
-        <v>541.8914463195232</v>
+        <v>547.0998432705837</v>
       </c>
       <c r="X19" t="n">
-        <v>614.7122373437168</v>
+        <v>619.9206342947773</v>
       </c>
       <c r="Y19" t="n">
-        <v>647.911538022749</v>
+        <v>653.1199349738096</v>
       </c>
     </row>
     <row r="20">
@@ -5719,76 +5719,76 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>596.4384060421568</v>
+        <v>596.5184060421567</v>
       </c>
       <c r="C20" t="n">
-        <v>466.6661047866073</v>
+        <v>466.7461047866073</v>
       </c>
       <c r="D20" t="n">
-        <v>376.4245333322136</v>
+        <v>376.5045333322136</v>
       </c>
       <c r="E20" t="n">
-        <v>292.2191902949725</v>
+        <v>292.2991902949725</v>
       </c>
       <c r="F20" t="n">
-        <v>207.482191600011</v>
+        <v>207.562191600011</v>
       </c>
       <c r="G20" t="n">
-        <v>125.2979517892592</v>
+        <v>125.3779517892592</v>
       </c>
       <c r="H20" t="n">
-        <v>51.84</v>
+        <v>51.92</v>
       </c>
       <c r="I20" t="n">
-        <v>51.84</v>
+        <v>51.92</v>
       </c>
       <c r="J20" t="n">
-        <v>560.3618942939371</v>
+        <v>560.4418942939371</v>
       </c>
       <c r="K20" t="n">
-        <v>1201.881894293937</v>
+        <v>736.1134691180577</v>
       </c>
       <c r="L20" t="n">
-        <v>1642.814971748371</v>
+        <v>954.0495916306205</v>
       </c>
       <c r="M20" t="n">
-        <v>1642.814971748371</v>
+        <v>1596.559591630621</v>
       </c>
       <c r="N20" t="n">
-        <v>1642.814971748371</v>
+        <v>2234.549243836214</v>
       </c>
       <c r="O20" t="n">
-        <v>1805.956778005698</v>
+        <v>2397.691050093541</v>
       </c>
       <c r="P20" t="n">
-        <v>2004.265727912157</v>
+        <v>2596</v>
       </c>
       <c r="Q20" t="n">
-        <v>2592</v>
+        <v>2596</v>
       </c>
       <c r="R20" t="n">
-        <v>2592</v>
+        <v>2596</v>
       </c>
       <c r="S20" t="n">
-        <v>2448.504870855986</v>
+        <v>2451.570786871937</v>
       </c>
       <c r="T20" t="n">
-        <v>2186.313881748914</v>
+        <v>2189.379797764865</v>
       </c>
       <c r="U20" t="n">
-        <v>1854.889943810872</v>
+        <v>1857.955859826824</v>
       </c>
       <c r="V20" t="n">
-        <v>1542.919212329232</v>
+        <v>1545.985128345183</v>
       </c>
       <c r="W20" t="n">
-        <v>1222.339943661608</v>
+        <v>1225.405859677559</v>
       </c>
       <c r="X20" t="n">
-        <v>948.3178896609338</v>
+        <v>951.383805676885</v>
       </c>
       <c r="Y20" t="n">
-        <v>759.0639746841513</v>
+        <v>759.1439746841512</v>
       </c>
     </row>
     <row r="21">
@@ -5798,76 +5798,76 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1001.797593356413</v>
+        <v>1326.120017598837</v>
       </c>
       <c r="C21" t="n">
-        <v>637.0502070478076</v>
+        <v>1100.605695149683</v>
       </c>
       <c r="D21" t="n">
-        <v>285.5979980602291</v>
+        <v>749.1534861621044</v>
       </c>
       <c r="E21" t="n">
-        <v>78.69763038239455</v>
+        <v>403.0200546248188</v>
       </c>
       <c r="F21" t="n">
-        <v>59.87314317241791</v>
+        <v>59.95314317241791</v>
       </c>
       <c r="G21" t="n">
-        <v>55.83964972137068</v>
+        <v>55.91964972137067</v>
       </c>
       <c r="H21" t="n">
-        <v>51.84</v>
+        <v>51.92</v>
       </c>
       <c r="I21" t="n">
-        <v>51.84</v>
+        <v>51.92</v>
       </c>
       <c r="J21" t="n">
-        <v>245.6076497036009</v>
+        <v>245.6876497036009</v>
       </c>
       <c r="K21" t="n">
-        <v>554.1188055149654</v>
+        <v>554.1988055149654</v>
       </c>
       <c r="L21" t="n">
-        <v>985.9074996573354</v>
+        <v>985.9874996573354</v>
       </c>
       <c r="M21" t="n">
-        <v>1259.211891400195</v>
+        <v>1259.291891400195</v>
       </c>
       <c r="N21" t="n">
-        <v>1584.67128421531</v>
+        <v>1584.75128421531</v>
       </c>
       <c r="O21" t="n">
-        <v>1999.520074672614</v>
+        <v>1999.600074672614</v>
       </c>
       <c r="P21" t="n">
-        <v>2253.149505368536</v>
+        <v>2253.229505368536</v>
       </c>
       <c r="Q21" t="n">
-        <v>2253.149505368536</v>
+        <v>2253.229505368536</v>
       </c>
       <c r="R21" t="n">
-        <v>2071.399071663636</v>
+        <v>2071.479071663636</v>
       </c>
       <c r="S21" t="n">
-        <v>1938.368397028141</v>
+        <v>1938.448397028141</v>
       </c>
       <c r="T21" t="n">
-        <v>1856.197345826917</v>
+        <v>1856.277345826917</v>
       </c>
       <c r="U21" t="n">
-        <v>1776.236481193986</v>
+        <v>1776.316481193986</v>
       </c>
       <c r="V21" t="n">
-        <v>1681.781261808612</v>
+        <v>1681.861261808612</v>
       </c>
       <c r="W21" t="n">
-        <v>1569.28313765727</v>
+        <v>1569.36313765727</v>
       </c>
       <c r="X21" t="n">
-        <v>1469.421784682131</v>
+        <v>1469.501784682131</v>
       </c>
       <c r="Y21" t="n">
-        <v>1390.238559665834</v>
+        <v>1390.318559665834</v>
       </c>
     </row>
     <row r="22">
@@ -5877,76 +5877,76 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>681.4588756890412</v>
+        <v>686.6672726401017</v>
       </c>
       <c r="C22" t="n">
-        <v>729.2508815074769</v>
+        <v>734.4592784585375</v>
       </c>
       <c r="D22" t="n">
-        <v>764.360025632477</v>
+        <v>764.4400256324769</v>
       </c>
       <c r="E22" t="n">
-        <v>803.97892984389</v>
+        <v>804.0589298438899</v>
       </c>
       <c r="F22" t="n">
-        <v>850.1299024358254</v>
+        <v>850.2099024358254</v>
       </c>
       <c r="G22" t="n">
-        <v>925.9459486505796</v>
+        <v>926.0259486505795</v>
       </c>
       <c r="H22" t="n">
-        <v>1022.760277088666</v>
+        <v>1022.840277088666</v>
       </c>
       <c r="I22" t="n">
-        <v>1184.312618975568</v>
+        <v>1184.392618975568</v>
       </c>
       <c r="J22" t="n">
-        <v>1510.983618808348</v>
+        <v>1511.063618808347</v>
       </c>
       <c r="K22" t="n">
-        <v>1615.110403564888</v>
+        <v>1615.190403564888</v>
       </c>
       <c r="L22" t="n">
-        <v>1605.496770221213</v>
+        <v>1605.576770221213</v>
       </c>
       <c r="M22" t="n">
-        <v>1502.926687499644</v>
+        <v>1503.006687499644</v>
       </c>
       <c r="N22" t="n">
-        <v>1346.936646241608</v>
+        <v>1347.016646241608</v>
       </c>
       <c r="O22" t="n">
-        <v>1113.602925280855</v>
+        <v>1113.682925280855</v>
       </c>
       <c r="P22" t="n">
-        <v>819.8981109568782</v>
+        <v>819.9781109568783</v>
       </c>
       <c r="Q22" t="n">
-        <v>463.8958216380924</v>
+        <v>463.9758216380924</v>
       </c>
       <c r="R22" t="n">
-        <v>82.61634147829413</v>
+        <v>82.69634147829413</v>
       </c>
       <c r="S22" t="n">
-        <v>51.84</v>
+        <v>51.92</v>
       </c>
       <c r="T22" t="n">
-        <v>159.2241526995476</v>
+        <v>164.4325496506081</v>
       </c>
       <c r="U22" t="n">
-        <v>327.5991351738998</v>
+        <v>332.8075321249603</v>
       </c>
       <c r="V22" t="n">
-        <v>448.2105280598458</v>
+        <v>453.4189250109063</v>
       </c>
       <c r="W22" t="n">
-        <v>541.8914463195232</v>
+        <v>547.0998432705837</v>
       </c>
       <c r="X22" t="n">
-        <v>614.7122373437168</v>
+        <v>619.9206342947773</v>
       </c>
       <c r="Y22" t="n">
-        <v>647.911538022749</v>
+        <v>653.1199349738096</v>
       </c>
     </row>
     <row r="23">
@@ -5956,76 +5956,76 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>593.4524900262279</v>
+        <v>596.5184060421567</v>
       </c>
       <c r="C23" t="n">
-        <v>463.6801887706785</v>
+        <v>466.7461047866073</v>
       </c>
       <c r="D23" t="n">
-        <v>373.4386173162847</v>
+        <v>376.5045333322136</v>
       </c>
       <c r="E23" t="n">
-        <v>289.2332742790437</v>
+        <v>292.2991902949725</v>
       </c>
       <c r="F23" t="n">
-        <v>207.482191600011</v>
+        <v>207.562191600011</v>
       </c>
       <c r="G23" t="n">
-        <v>125.2979517892592</v>
+        <v>125.3779517892592</v>
       </c>
       <c r="H23" t="n">
-        <v>51.84</v>
+        <v>51.92</v>
       </c>
       <c r="I23" t="n">
-        <v>51.84</v>
+        <v>51.92</v>
       </c>
       <c r="J23" t="n">
-        <v>560.3618942939371</v>
+        <v>134.440205073642</v>
       </c>
       <c r="K23" t="n">
-        <v>1201.881894293937</v>
+        <v>310.1117798977626</v>
       </c>
       <c r="L23" t="n">
-        <v>1843.401894293937</v>
+        <v>528.0479024103255</v>
       </c>
       <c r="M23" t="n">
-        <v>2230.549243836214</v>
+        <v>1170.557902410325</v>
       </c>
       <c r="N23" t="n">
-        <v>2230.549243836214</v>
+        <v>1813.067902410325</v>
       </c>
       <c r="O23" t="n">
-        <v>2393.691050093541</v>
+        <v>1976.209708667652</v>
       </c>
       <c r="P23" t="n">
-        <v>2592</v>
+        <v>2174.518658574111</v>
       </c>
       <c r="Q23" t="n">
-        <v>2592</v>
+        <v>2596</v>
       </c>
       <c r="R23" t="n">
-        <v>2592.000000000022</v>
+        <v>2596</v>
       </c>
       <c r="S23" t="n">
-        <v>2448.504870856008</v>
+        <v>2451.570786871937</v>
       </c>
       <c r="T23" t="n">
-        <v>2186.313881748936</v>
+        <v>2189.379797764865</v>
       </c>
       <c r="U23" t="n">
-        <v>1854.889943810895</v>
+        <v>1857.955859826824</v>
       </c>
       <c r="V23" t="n">
-        <v>1542.919212329254</v>
+        <v>1545.985128345183</v>
       </c>
       <c r="W23" t="n">
-        <v>1222.339943661631</v>
+        <v>1225.405859677559</v>
       </c>
       <c r="X23" t="n">
-        <v>948.3178896609561</v>
+        <v>951.383805676885</v>
       </c>
       <c r="Y23" t="n">
-        <v>756.0780586682224</v>
+        <v>759.1439746841512</v>
       </c>
     </row>
     <row r="24">
@@ -6035,76 +6035,76 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>168.3033844885911</v>
+        <v>1141.110657215864</v>
       </c>
       <c r="C24" t="n">
-        <v>127.79842242241</v>
+        <v>776.3632709072585</v>
       </c>
       <c r="D24" t="n">
-        <v>100.5886376772558</v>
+        <v>749.1534861621044</v>
       </c>
       <c r="E24" t="n">
-        <v>78.69763038239455</v>
+        <v>403.0200546248188</v>
       </c>
       <c r="F24" t="n">
-        <v>59.87314317241791</v>
+        <v>59.95314317241791</v>
       </c>
       <c r="G24" t="n">
-        <v>55.83964972137068</v>
+        <v>55.91964972137067</v>
       </c>
       <c r="H24" t="n">
-        <v>51.84</v>
+        <v>51.92</v>
       </c>
       <c r="I24" t="n">
-        <v>51.84</v>
+        <v>51.92</v>
       </c>
       <c r="J24" t="n">
-        <v>245.6076497036009</v>
+        <v>245.6876497036009</v>
       </c>
       <c r="K24" t="n">
-        <v>554.1188055149654</v>
+        <v>554.1988055149654</v>
       </c>
       <c r="L24" t="n">
-        <v>985.9074996573354</v>
+        <v>985.9874996573354</v>
       </c>
       <c r="M24" t="n">
-        <v>1259.211891400195</v>
+        <v>1259.291891400195</v>
       </c>
       <c r="N24" t="n">
-        <v>1584.67128421531</v>
+        <v>1584.75128421531</v>
       </c>
       <c r="O24" t="n">
-        <v>1999.520074672614</v>
+        <v>1999.600074672614</v>
       </c>
       <c r="P24" t="n">
-        <v>2253.149505368536</v>
+        <v>2253.229505368536</v>
       </c>
       <c r="Q24" t="n">
-        <v>2253.149505368536</v>
+        <v>2253.229505368536</v>
       </c>
       <c r="R24" t="n">
-        <v>2071.399071663636</v>
+        <v>2071.479071663636</v>
       </c>
       <c r="S24" t="n">
-        <v>1938.368397028141</v>
+        <v>1938.448397028141</v>
       </c>
       <c r="T24" t="n">
-        <v>1856.197345826917</v>
+        <v>1856.277345826917</v>
       </c>
       <c r="U24" t="n">
-        <v>1776.236481193986</v>
+        <v>1776.316481193986</v>
       </c>
       <c r="V24" t="n">
-        <v>1496.771901425639</v>
+        <v>1681.861261808612</v>
       </c>
       <c r="W24" t="n">
-        <v>1060.031353031872</v>
+        <v>1569.36313765727</v>
       </c>
       <c r="X24" t="n">
-        <v>635.9275758143092</v>
+        <v>1469.501784682131</v>
       </c>
       <c r="Y24" t="n">
-        <v>232.5019265555877</v>
+        <v>1390.318559665834</v>
       </c>
     </row>
     <row r="25">
@@ -6114,76 +6114,76 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>681.4588756890412</v>
+        <v>681.5388756890411</v>
       </c>
       <c r="C25" t="n">
-        <v>729.2508815074769</v>
+        <v>729.3308815074769</v>
       </c>
       <c r="D25" t="n">
-        <v>764.360025632477</v>
+        <v>764.4400256324769</v>
       </c>
       <c r="E25" t="n">
-        <v>803.97892984389</v>
+        <v>804.0589298438899</v>
       </c>
       <c r="F25" t="n">
-        <v>850.1299024358254</v>
+        <v>850.2099024358254</v>
       </c>
       <c r="G25" t="n">
-        <v>925.9459486505796</v>
+        <v>926.0259486505795</v>
       </c>
       <c r="H25" t="n">
-        <v>1022.760277088666</v>
+        <v>1022.840277088666</v>
       </c>
       <c r="I25" t="n">
-        <v>1184.312618975568</v>
+        <v>1184.392618975568</v>
       </c>
       <c r="J25" t="n">
-        <v>1510.983618808348</v>
+        <v>1511.063618808347</v>
       </c>
       <c r="K25" t="n">
-        <v>1615.110403564888</v>
+        <v>1615.190403564888</v>
       </c>
       <c r="L25" t="n">
-        <v>1605.496770221213</v>
+        <v>1605.576770221213</v>
       </c>
       <c r="M25" t="n">
-        <v>1502.926687499644</v>
+        <v>1503.006687499644</v>
       </c>
       <c r="N25" t="n">
-        <v>1346.936646241608</v>
+        <v>1347.016646241608</v>
       </c>
       <c r="O25" t="n">
-        <v>1113.602925280855</v>
+        <v>1113.682925280855</v>
       </c>
       <c r="P25" t="n">
-        <v>819.8981109568782</v>
+        <v>819.9781109568783</v>
       </c>
       <c r="Q25" t="n">
-        <v>463.8958216380924</v>
+        <v>463.9758216380924</v>
       </c>
       <c r="R25" t="n">
-        <v>82.61634147829413</v>
+        <v>82.69634147829413</v>
       </c>
       <c r="S25" t="n">
-        <v>51.84</v>
+        <v>51.92</v>
       </c>
       <c r="T25" t="n">
-        <v>164.3525496506081</v>
+        <v>159.3041526995475</v>
       </c>
       <c r="U25" t="n">
-        <v>327.5991351738998</v>
+        <v>327.6791351738997</v>
       </c>
       <c r="V25" t="n">
-        <v>448.2105280598458</v>
+        <v>448.2905280598457</v>
       </c>
       <c r="W25" t="n">
-        <v>541.8914463195232</v>
+        <v>541.9714463195231</v>
       </c>
       <c r="X25" t="n">
-        <v>614.7122373437168</v>
+        <v>614.7922373437167</v>
       </c>
       <c r="Y25" t="n">
-        <v>647.911538022749</v>
+        <v>647.991538022749</v>
       </c>
     </row>
     <row r="26">
@@ -6193,76 +6193,76 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>593.4524900262059</v>
+        <v>601.4524900262056</v>
       </c>
       <c r="C26" t="n">
-        <v>463.6801887706564</v>
+        <v>471.6801887706562</v>
       </c>
       <c r="D26" t="n">
-        <v>373.4386173162627</v>
+        <v>381.4386173162624</v>
       </c>
       <c r="E26" t="n">
-        <v>289.2332742790216</v>
+        <v>297.2332742790214</v>
       </c>
       <c r="F26" t="n">
-        <v>204.4962755840601</v>
+        <v>212.4962755840599</v>
       </c>
       <c r="G26" t="n">
-        <v>125.2979517892592</v>
+        <v>130.3120357733081</v>
       </c>
       <c r="H26" t="n">
-        <v>51.84</v>
+        <v>56.85408398404886</v>
       </c>
       <c r="I26" t="n">
-        <v>51.84</v>
+        <v>52</v>
       </c>
       <c r="J26" t="n">
-        <v>134.360205073642</v>
+        <v>560.5218942939371</v>
       </c>
       <c r="K26" t="n">
-        <v>775.8802050736419</v>
+        <v>1204.021894293937</v>
       </c>
       <c r="L26" t="n">
-        <v>1417.400205073642</v>
+        <v>1847.521894293937</v>
       </c>
       <c r="M26" t="n">
-        <v>2058.920205073645</v>
+        <v>2238.549243836214</v>
       </c>
       <c r="N26" t="n">
-        <v>2230.549243836214</v>
+        <v>2238.549243836214</v>
       </c>
       <c r="O26" t="n">
-        <v>2393.691050093541</v>
+        <v>2401.691050093541</v>
       </c>
       <c r="P26" t="n">
-        <v>2592</v>
+        <v>2600</v>
       </c>
       <c r="Q26" t="n">
-        <v>2592</v>
+        <v>2600</v>
       </c>
       <c r="R26" t="n">
-        <v>2592</v>
+        <v>2600</v>
       </c>
       <c r="S26" t="n">
-        <v>2448.504870855986</v>
+        <v>2456.504870855986</v>
       </c>
       <c r="T26" t="n">
-        <v>2186.313881748914</v>
+        <v>2194.313881748914</v>
       </c>
       <c r="U26" t="n">
-        <v>1854.889943810873</v>
+        <v>1862.889943810872</v>
       </c>
       <c r="V26" t="n">
-        <v>1542.919212329232</v>
+        <v>1550.919212329232</v>
       </c>
       <c r="W26" t="n">
-        <v>1222.339943661608</v>
+        <v>1230.339943661608</v>
       </c>
       <c r="X26" t="n">
-        <v>948.317889660934</v>
+        <v>956.3178896609338</v>
       </c>
       <c r="Y26" t="n">
-        <v>756.0780586682004</v>
+        <v>764.0780586682001</v>
       </c>
     </row>
     <row r="27">
@@ -6272,76 +6272,76 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1141.030657215864</v>
+        <v>1326.200017598837</v>
       </c>
       <c r="C27" t="n">
-        <v>776.2832709072586</v>
+        <v>961.4526312902317</v>
       </c>
       <c r="D27" t="n">
-        <v>424.8310619196801</v>
+        <v>610.0004223026533</v>
       </c>
       <c r="E27" t="n">
-        <v>78.69763038239458</v>
+        <v>588.1094150077921</v>
       </c>
       <c r="F27" t="n">
-        <v>59.87314317241794</v>
+        <v>245.0425035553912</v>
       </c>
       <c r="G27" t="n">
-        <v>55.83964972137069</v>
+        <v>55.99964972137067</v>
       </c>
       <c r="H27" t="n">
-        <v>51.84</v>
+        <v>52</v>
       </c>
       <c r="I27" t="n">
-        <v>51.84</v>
+        <v>52</v>
       </c>
       <c r="J27" t="n">
-        <v>245.6076497036009</v>
+        <v>245.7676497036009</v>
       </c>
       <c r="K27" t="n">
-        <v>554.1188055149654</v>
+        <v>554.2788055149654</v>
       </c>
       <c r="L27" t="n">
-        <v>985.9074996573354</v>
+        <v>986.0674996573354</v>
       </c>
       <c r="M27" t="n">
-        <v>1259.211891400195</v>
+        <v>1259.371891400194</v>
       </c>
       <c r="N27" t="n">
-        <v>1584.67128421531</v>
+        <v>1584.83128421531</v>
       </c>
       <c r="O27" t="n">
-        <v>1999.520074672614</v>
+        <v>1999.680074672614</v>
       </c>
       <c r="P27" t="n">
-        <v>2253.149505368536</v>
+        <v>2253.309505368536</v>
       </c>
       <c r="Q27" t="n">
-        <v>2253.149505368536</v>
+        <v>2253.309505368536</v>
       </c>
       <c r="R27" t="n">
-        <v>2071.399071663636</v>
+        <v>2071.559071663636</v>
       </c>
       <c r="S27" t="n">
-        <v>1938.368397028141</v>
+        <v>1938.528397028141</v>
       </c>
       <c r="T27" t="n">
-        <v>1856.197345826917</v>
+        <v>1856.357345826917</v>
       </c>
       <c r="U27" t="n">
-        <v>1776.236481193986</v>
+        <v>1776.396481193986</v>
       </c>
       <c r="V27" t="n">
-        <v>1681.781261808612</v>
+        <v>1681.941261808612</v>
       </c>
       <c r="W27" t="n">
-        <v>1569.28313765727</v>
+        <v>1569.44313765727</v>
       </c>
       <c r="X27" t="n">
-        <v>1469.421784682131</v>
+        <v>1469.581784682131</v>
       </c>
       <c r="Y27" t="n">
-        <v>1390.238559665834</v>
+        <v>1390.398559665834</v>
       </c>
     </row>
     <row r="28">
@@ -6351,76 +6351,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>681.4588756890412</v>
+        <v>681.618875689041</v>
       </c>
       <c r="C28" t="n">
-        <v>729.2508815074769</v>
+        <v>729.4108815074768</v>
       </c>
       <c r="D28" t="n">
-        <v>764.360025632477</v>
+        <v>764.5200256324769</v>
       </c>
       <c r="E28" t="n">
-        <v>803.97892984389</v>
+        <v>804.1389298438899</v>
       </c>
       <c r="F28" t="n">
-        <v>850.1299024358254</v>
+        <v>850.2899024358253</v>
       </c>
       <c r="G28" t="n">
-        <v>925.9459486505796</v>
+        <v>926.1059486505794</v>
       </c>
       <c r="H28" t="n">
-        <v>1022.760277088666</v>
+        <v>1022.920277088666</v>
       </c>
       <c r="I28" t="n">
-        <v>1184.312618975568</v>
+        <v>1184.472618975568</v>
       </c>
       <c r="J28" t="n">
-        <v>1510.983618808348</v>
+        <v>1511.143618808347</v>
       </c>
       <c r="K28" t="n">
-        <v>1615.110403564888</v>
+        <v>1615.270403564888</v>
       </c>
       <c r="L28" t="n">
-        <v>1605.496770221213</v>
+        <v>1605.656770221213</v>
       </c>
       <c r="M28" t="n">
-        <v>1502.926687499644</v>
+        <v>1503.086687499644</v>
       </c>
       <c r="N28" t="n">
-        <v>1346.936646241608</v>
+        <v>1347.096646241608</v>
       </c>
       <c r="O28" t="n">
-        <v>1113.602925280855</v>
+        <v>1113.762925280854</v>
       </c>
       <c r="P28" t="n">
-        <v>819.8981109568782</v>
+        <v>820.0581109568782</v>
       </c>
       <c r="Q28" t="n">
-        <v>463.8958216380923</v>
+        <v>464.0558216380924</v>
       </c>
       <c r="R28" t="n">
-        <v>82.61634147829412</v>
+        <v>82.77634147829413</v>
       </c>
       <c r="S28" t="n">
-        <v>51.84</v>
+        <v>52</v>
       </c>
       <c r="T28" t="n">
-        <v>164.3525496506081</v>
+        <v>159.3841526995475</v>
       </c>
       <c r="U28" t="n">
-        <v>332.7275321249604</v>
+        <v>327.7591351738997</v>
       </c>
       <c r="V28" t="n">
-        <v>453.3389250109063</v>
+        <v>448.3705280598456</v>
       </c>
       <c r="W28" t="n">
-        <v>547.0198432705838</v>
+        <v>542.0514463195231</v>
       </c>
       <c r="X28" t="n">
-        <v>619.8406342947774</v>
+        <v>614.8722373437166</v>
       </c>
       <c r="Y28" t="n">
-        <v>647.911538022749</v>
+        <v>648.0715380227489</v>
       </c>
     </row>
     <row r="29">
@@ -6430,76 +6430,76 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>593.4524900262461</v>
+        <v>601.4524900262059</v>
       </c>
       <c r="C29" t="n">
-        <v>463.6801887706966</v>
+        <v>471.6801887706564</v>
       </c>
       <c r="D29" t="n">
-        <v>373.4386173163029</v>
+        <v>381.4386173162627</v>
       </c>
       <c r="E29" t="n">
-        <v>289.2332742790618</v>
+        <v>297.2332742790216</v>
       </c>
       <c r="F29" t="n">
-        <v>204.4962755841004</v>
+        <v>212.4962755840601</v>
       </c>
       <c r="G29" t="n">
-        <v>122.3120357733485</v>
+        <v>130.3120357733083</v>
       </c>
       <c r="H29" t="n">
-        <v>51.84</v>
+        <v>56.85408398404904</v>
       </c>
       <c r="I29" t="n">
-        <v>51.84</v>
+        <v>52</v>
       </c>
       <c r="J29" t="n">
-        <v>134.360205073642</v>
+        <v>134.520205073642</v>
       </c>
       <c r="K29" t="n">
-        <v>775.8802050736419</v>
+        <v>310.1917798977626</v>
       </c>
       <c r="L29" t="n">
-        <v>1417.400205073642</v>
+        <v>528.1279024103255</v>
       </c>
       <c r="M29" t="n">
-        <v>1589.02924383621</v>
+        <v>1007.314971748371</v>
       </c>
       <c r="N29" t="n">
-        <v>2230.549243836214</v>
+        <v>1650.814971748371</v>
       </c>
       <c r="O29" t="n">
-        <v>2393.691050093541</v>
+        <v>1813.956778005698</v>
       </c>
       <c r="P29" t="n">
-        <v>2592</v>
+        <v>2012.265727912157</v>
       </c>
       <c r="Q29" t="n">
-        <v>2592</v>
+        <v>2600</v>
       </c>
       <c r="R29" t="n">
-        <v>2592.00000000004</v>
+        <v>2600</v>
       </c>
       <c r="S29" t="n">
-        <v>2448.504870856026</v>
+        <v>2456.504870855986</v>
       </c>
       <c r="T29" t="n">
-        <v>2186.313881748954</v>
+        <v>2194.313881748914</v>
       </c>
       <c r="U29" t="n">
-        <v>1854.889943810913</v>
+        <v>1862.889943810873</v>
       </c>
       <c r="V29" t="n">
-        <v>1542.919212329273</v>
+        <v>1550.919212329232</v>
       </c>
       <c r="W29" t="n">
-        <v>1222.339943661649</v>
+        <v>1230.339943661608</v>
       </c>
       <c r="X29" t="n">
-        <v>948.3178896609743</v>
+        <v>956.317889660934</v>
       </c>
       <c r="Y29" t="n">
-        <v>756.0780586682406</v>
+        <v>764.0780586682004</v>
       </c>
     </row>
     <row r="30">
@@ -6509,76 +6509,76 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>168.3033844885911</v>
+        <v>168.4633844885911</v>
       </c>
       <c r="C30" t="n">
-        <v>127.79842242241</v>
+        <v>127.95842242241</v>
       </c>
       <c r="D30" t="n">
-        <v>100.5886376772558</v>
+        <v>100.7486376772558</v>
       </c>
       <c r="E30" t="n">
-        <v>78.69763038239455</v>
+        <v>78.85763038239458</v>
       </c>
       <c r="F30" t="n">
-        <v>59.87314317241791</v>
+        <v>60.03314317241794</v>
       </c>
       <c r="G30" t="n">
-        <v>55.83964972137068</v>
+        <v>55.99964972137069</v>
       </c>
       <c r="H30" t="n">
-        <v>51.84</v>
+        <v>52</v>
       </c>
       <c r="I30" t="n">
-        <v>51.84</v>
+        <v>52</v>
       </c>
       <c r="J30" t="n">
-        <v>245.6076497036009</v>
+        <v>245.7676497036009</v>
       </c>
       <c r="K30" t="n">
-        <v>554.1188055149654</v>
+        <v>554.2788055149654</v>
       </c>
       <c r="L30" t="n">
-        <v>985.9074996573354</v>
+        <v>986.0674996573354</v>
       </c>
       <c r="M30" t="n">
-        <v>1259.211891400195</v>
+        <v>1259.371891400194</v>
       </c>
       <c r="N30" t="n">
-        <v>1584.67128421531</v>
+        <v>1584.83128421531</v>
       </c>
       <c r="O30" t="n">
-        <v>1999.520074672614</v>
+        <v>1999.680074672614</v>
       </c>
       <c r="P30" t="n">
-        <v>2253.149505368536</v>
+        <v>2253.309505368536</v>
       </c>
       <c r="Q30" t="n">
-        <v>2253.149505368536</v>
+        <v>2253.309505368536</v>
       </c>
       <c r="R30" t="n">
-        <v>2071.399071663636</v>
+        <v>2071.559071663636</v>
       </c>
       <c r="S30" t="n">
-        <v>1938.368397028141</v>
+        <v>1938.528397028141</v>
       </c>
       <c r="T30" t="n">
-        <v>1856.197345826917</v>
+        <v>1856.357345826917</v>
       </c>
       <c r="U30" t="n">
-        <v>1776.236481193986</v>
+        <v>1776.396481193986</v>
       </c>
       <c r="V30" t="n">
-        <v>1496.771901425639</v>
+        <v>1357.698837566188</v>
       </c>
       <c r="W30" t="n">
-        <v>1060.031353031872</v>
+        <v>920.9582891724215</v>
       </c>
       <c r="X30" t="n">
-        <v>635.9275758143092</v>
+        <v>496.8545119548583</v>
       </c>
       <c r="Y30" t="n">
-        <v>232.5019265555877</v>
+        <v>232.6619265555877</v>
       </c>
     </row>
     <row r="31">
@@ -6588,76 +6588,76 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>681.4588756890412</v>
+        <v>681.618875689041</v>
       </c>
       <c r="C31" t="n">
-        <v>729.2508815074769</v>
+        <v>729.4108815074768</v>
       </c>
       <c r="D31" t="n">
-        <v>764.360025632477</v>
+        <v>764.5200256324769</v>
       </c>
       <c r="E31" t="n">
-        <v>803.97892984389</v>
+        <v>804.1389298438899</v>
       </c>
       <c r="F31" t="n">
-        <v>850.1299024358254</v>
+        <v>850.2899024358253</v>
       </c>
       <c r="G31" t="n">
-        <v>925.9459486505796</v>
+        <v>926.1059486505794</v>
       </c>
       <c r="H31" t="n">
-        <v>1022.760277088666</v>
+        <v>1022.920277088666</v>
       </c>
       <c r="I31" t="n">
-        <v>1184.312618975568</v>
+        <v>1184.472618975568</v>
       </c>
       <c r="J31" t="n">
-        <v>1510.983618808348</v>
+        <v>1511.143618808347</v>
       </c>
       <c r="K31" t="n">
-        <v>1615.110403564888</v>
+        <v>1615.270403564888</v>
       </c>
       <c r="L31" t="n">
-        <v>1605.496770221213</v>
+        <v>1605.656770221213</v>
       </c>
       <c r="M31" t="n">
-        <v>1502.926687499644</v>
+        <v>1503.086687499644</v>
       </c>
       <c r="N31" t="n">
-        <v>1346.936646241608</v>
+        <v>1347.096646241608</v>
       </c>
       <c r="O31" t="n">
-        <v>1113.602925280855</v>
+        <v>1113.762925280854</v>
       </c>
       <c r="P31" t="n">
-        <v>819.8981109568782</v>
+        <v>820.0581109568782</v>
       </c>
       <c r="Q31" t="n">
-        <v>463.8958216380924</v>
+        <v>464.0558216380924</v>
       </c>
       <c r="R31" t="n">
-        <v>82.61634147829413</v>
+        <v>82.77634147829411</v>
       </c>
       <c r="S31" t="n">
-        <v>51.84</v>
+        <v>52</v>
       </c>
       <c r="T31" t="n">
-        <v>159.2241526995476</v>
+        <v>159.3841526995475</v>
       </c>
       <c r="U31" t="n">
-        <v>327.5991351738998</v>
+        <v>327.7591351738997</v>
       </c>
       <c r="V31" t="n">
-        <v>448.2105280598458</v>
+        <v>448.3705280598456</v>
       </c>
       <c r="W31" t="n">
-        <v>541.8914463195232</v>
+        <v>542.0514463195231</v>
       </c>
       <c r="X31" t="n">
-        <v>614.7122373437168</v>
+        <v>614.8722373437166</v>
       </c>
       <c r="Y31" t="n">
-        <v>647.911538022749</v>
+        <v>648.0715380227489</v>
       </c>
     </row>
     <row r="32">
@@ -6667,76 +6667,76 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>596.4384060421568</v>
+        <v>601.4524900262056</v>
       </c>
       <c r="C32" t="n">
-        <v>466.6661047866074</v>
+        <v>471.6801887706562</v>
       </c>
       <c r="D32" t="n">
-        <v>376.4245333322136</v>
+        <v>381.4386173162624</v>
       </c>
       <c r="E32" t="n">
-        <v>292.2191902949726</v>
+        <v>297.2332742790214</v>
       </c>
       <c r="F32" t="n">
-        <v>207.4821916000111</v>
+        <v>212.4962755840599</v>
       </c>
       <c r="G32" t="n">
-        <v>125.2979517892592</v>
+        <v>130.3120357733081</v>
       </c>
       <c r="H32" t="n">
-        <v>51.84</v>
+        <v>52</v>
       </c>
       <c r="I32" t="n">
-        <v>51.84</v>
+        <v>52</v>
       </c>
       <c r="J32" t="n">
-        <v>134.360205073642</v>
+        <v>134.520205073642</v>
       </c>
       <c r="K32" t="n">
-        <v>775.8802050736419</v>
+        <v>363.8149717483709</v>
       </c>
       <c r="L32" t="n">
-        <v>1001.294971748368</v>
+        <v>1007.314971748371</v>
       </c>
       <c r="M32" t="n">
-        <v>1001.294971748368</v>
+        <v>1650.814971748371</v>
       </c>
       <c r="N32" t="n">
-        <v>1642.814971748371</v>
+        <v>1650.814971748371</v>
       </c>
       <c r="O32" t="n">
-        <v>1805.956778005698</v>
+        <v>1813.956778005698</v>
       </c>
       <c r="P32" t="n">
-        <v>2004.265727912157</v>
+        <v>2012.265727912157</v>
       </c>
       <c r="Q32" t="n">
-        <v>2592</v>
+        <v>2600</v>
       </c>
       <c r="R32" t="n">
-        <v>2592</v>
+        <v>2600</v>
       </c>
       <c r="S32" t="n">
-        <v>2448.504870855986</v>
+        <v>2456.504870855986</v>
       </c>
       <c r="T32" t="n">
-        <v>2186.313881748914</v>
+        <v>2194.313881748914</v>
       </c>
       <c r="U32" t="n">
-        <v>1854.889943810873</v>
+        <v>1862.889943810872</v>
       </c>
       <c r="V32" t="n">
-        <v>1545.905128345183</v>
+        <v>1550.919212329232</v>
       </c>
       <c r="W32" t="n">
-        <v>1225.325859677559</v>
+        <v>1230.339943661608</v>
       </c>
       <c r="X32" t="n">
-        <v>951.3038056768851</v>
+        <v>956.3178896609338</v>
       </c>
       <c r="Y32" t="n">
-        <v>759.0639746841513</v>
+        <v>764.0780586682001</v>
       </c>
     </row>
     <row r="33">
@@ -6746,76 +6746,76 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>816.7882329734397</v>
+        <v>168.4633844885911</v>
       </c>
       <c r="C33" t="n">
-        <v>452.0408466648343</v>
+        <v>127.95842242241</v>
       </c>
       <c r="D33" t="n">
-        <v>424.8310619196801</v>
+        <v>100.7486376772558</v>
       </c>
       <c r="E33" t="n">
-        <v>402.9400546248189</v>
+        <v>78.85763038239455</v>
       </c>
       <c r="F33" t="n">
-        <v>59.87314317241794</v>
+        <v>60.03314317241791</v>
       </c>
       <c r="G33" t="n">
-        <v>55.83964972137069</v>
+        <v>55.99964972137067</v>
       </c>
       <c r="H33" t="n">
-        <v>51.84</v>
+        <v>52</v>
       </c>
       <c r="I33" t="n">
-        <v>51.84</v>
+        <v>52</v>
       </c>
       <c r="J33" t="n">
-        <v>245.6076497036009</v>
+        <v>245.7676497036009</v>
       </c>
       <c r="K33" t="n">
-        <v>554.1188055149654</v>
+        <v>554.2788055149654</v>
       </c>
       <c r="L33" t="n">
-        <v>985.9074996573354</v>
+        <v>986.0674996573354</v>
       </c>
       <c r="M33" t="n">
-        <v>1259.211891400195</v>
+        <v>1259.371891400194</v>
       </c>
       <c r="N33" t="n">
-        <v>1584.67128421531</v>
+        <v>1584.83128421531</v>
       </c>
       <c r="O33" t="n">
-        <v>1999.520074672614</v>
+        <v>1999.680074672614</v>
       </c>
       <c r="P33" t="n">
-        <v>2253.149505368536</v>
+        <v>2253.309505368536</v>
       </c>
       <c r="Q33" t="n">
-        <v>2174.558747796677</v>
+        <v>2253.309505368536</v>
       </c>
       <c r="R33" t="n">
-        <v>1992.808314091777</v>
+        <v>2071.559071663636</v>
       </c>
       <c r="S33" t="n">
-        <v>1859.777639456283</v>
+        <v>1938.528397028141</v>
       </c>
       <c r="T33" t="n">
-        <v>1777.606588255059</v>
+        <v>1856.357345826917</v>
       </c>
       <c r="U33" t="n">
-        <v>1697.645723622128</v>
+        <v>1776.396481193986</v>
       </c>
       <c r="V33" t="n">
-        <v>1603.190504236754</v>
+        <v>1357.698837566188</v>
       </c>
       <c r="W33" t="n">
-        <v>1490.692380085412</v>
+        <v>920.9582891724215</v>
       </c>
       <c r="X33" t="n">
-        <v>1066.588602867849</v>
+        <v>496.8545119548583</v>
       </c>
       <c r="Y33" t="n">
-        <v>987.4053778515512</v>
+        <v>232.6619265555877</v>
       </c>
     </row>
     <row r="34">
@@ -6825,76 +6825,76 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>681.4588756890412</v>
+        <v>686.7472726401016</v>
       </c>
       <c r="C34" t="n">
-        <v>729.2508815074769</v>
+        <v>734.5392784585374</v>
       </c>
       <c r="D34" t="n">
-        <v>764.360025632477</v>
+        <v>764.5200256324769</v>
       </c>
       <c r="E34" t="n">
-        <v>803.97892984389</v>
+        <v>804.1389298438899</v>
       </c>
       <c r="F34" t="n">
-        <v>850.1299024358254</v>
+        <v>850.2899024358253</v>
       </c>
       <c r="G34" t="n">
-        <v>925.9459486505796</v>
+        <v>926.1059486505794</v>
       </c>
       <c r="H34" t="n">
-        <v>1022.760277088666</v>
+        <v>1022.920277088666</v>
       </c>
       <c r="I34" t="n">
-        <v>1184.312618975568</v>
+        <v>1184.472618975568</v>
       </c>
       <c r="J34" t="n">
-        <v>1510.983618808348</v>
+        <v>1511.143618808347</v>
       </c>
       <c r="K34" t="n">
-        <v>1615.110403564888</v>
+        <v>1615.270403564888</v>
       </c>
       <c r="L34" t="n">
-        <v>1605.496770221213</v>
+        <v>1605.656770221213</v>
       </c>
       <c r="M34" t="n">
-        <v>1502.926687499644</v>
+        <v>1503.086687499644</v>
       </c>
       <c r="N34" t="n">
-        <v>1346.936646241608</v>
+        <v>1347.096646241608</v>
       </c>
       <c r="O34" t="n">
-        <v>1113.602925280855</v>
+        <v>1113.762925280854</v>
       </c>
       <c r="P34" t="n">
-        <v>819.8981109568782</v>
+        <v>820.0581109568782</v>
       </c>
       <c r="Q34" t="n">
-        <v>463.8958216380923</v>
+        <v>464.0558216380924</v>
       </c>
       <c r="R34" t="n">
-        <v>82.61634147829412</v>
+        <v>82.77634147829413</v>
       </c>
       <c r="S34" t="n">
-        <v>51.84</v>
+        <v>52</v>
       </c>
       <c r="T34" t="n">
-        <v>159.2241526995476</v>
+        <v>164.5125496506082</v>
       </c>
       <c r="U34" t="n">
-        <v>327.5991351738998</v>
+        <v>332.8875321249603</v>
       </c>
       <c r="V34" t="n">
-        <v>448.2105280598458</v>
+        <v>453.4989250109063</v>
       </c>
       <c r="W34" t="n">
-        <v>541.8914463195232</v>
+        <v>547.1798432705837</v>
       </c>
       <c r="X34" t="n">
-        <v>614.7122373437168</v>
+        <v>620.0006342947772</v>
       </c>
       <c r="Y34" t="n">
-        <v>647.911538022749</v>
+        <v>653.1999349738095</v>
       </c>
     </row>
     <row r="35">
@@ -6904,76 +6904,76 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>439.3918839655994</v>
+        <v>444.1038605876113</v>
       </c>
       <c r="C35" t="n">
-        <v>333.8620069524742</v>
+        <v>338.5739835744861</v>
       </c>
       <c r="D35" t="n">
-        <v>267.8628597405047</v>
+        <v>272.5748363625166</v>
       </c>
       <c r="E35" t="n">
-        <v>207.8999409456879</v>
+        <v>212.6119175676998</v>
       </c>
       <c r="F35" t="n">
-        <v>147.4053664931506</v>
+        <v>152.1173431151626</v>
       </c>
       <c r="G35" t="n">
-        <v>94.09552754683497</v>
+        <v>94.17552754683497</v>
       </c>
       <c r="H35" t="n">
-        <v>44.88</v>
+        <v>44.96</v>
       </c>
       <c r="I35" t="n">
-        <v>44.88</v>
+        <v>44.96</v>
       </c>
       <c r="J35" t="n">
-        <v>127.400205073642</v>
+        <v>127.480205073642</v>
       </c>
       <c r="K35" t="n">
-        <v>682.790205073642</v>
+        <v>303.1517798977626</v>
       </c>
       <c r="L35" t="n">
-        <v>1238.180205073642</v>
+        <v>521.0879024103255</v>
       </c>
       <c r="M35" t="n">
-        <v>1327.159243836214</v>
+        <v>936.9310500935409</v>
       </c>
       <c r="N35" t="n">
-        <v>1882.549243836214</v>
+        <v>1493.311050093541</v>
       </c>
       <c r="O35" t="n">
-        <v>2045.691050093541</v>
+        <v>2049.691050093541</v>
       </c>
       <c r="P35" t="n">
-        <v>2244</v>
+        <v>2248</v>
       </c>
       <c r="Q35" t="n">
-        <v>2244</v>
+        <v>2248</v>
       </c>
       <c r="R35" t="n">
-        <v>2244</v>
+        <v>2248</v>
       </c>
       <c r="S35" t="n">
-        <v>2124.74729509841</v>
+        <v>2128.74729509841</v>
       </c>
       <c r="T35" t="n">
-        <v>1886.798730233762</v>
+        <v>1890.798730233762</v>
       </c>
       <c r="U35" t="n">
-        <v>1579.617216538145</v>
+        <v>1583.617216538145</v>
       </c>
       <c r="V35" t="n">
-        <v>1291.888909298929</v>
+        <v>1296.600885920941</v>
       </c>
       <c r="W35" t="n">
-        <v>995.5520648737293</v>
+        <v>1000.264041495741</v>
       </c>
       <c r="X35" t="n">
-        <v>745.7724351154791</v>
+        <v>750.484411737491</v>
       </c>
       <c r="Y35" t="n">
-        <v>577.7750283651696</v>
+        <v>582.4870049871815</v>
       </c>
     </row>
     <row r="36">
@@ -6983,76 +6983,76 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1107.996724355472</v>
+        <v>1450.35993828587</v>
       </c>
       <c r="C36" t="n">
-        <v>743.2493380468661</v>
+        <v>1085.612551977265</v>
       </c>
       <c r="D36" t="n">
-        <v>719.289349230757</v>
+        <v>734.1603429896863</v>
       </c>
       <c r="E36" t="n">
-        <v>373.1559176934715</v>
+        <v>388.0269114524009</v>
       </c>
       <c r="F36" t="n">
-        <v>373.1559176934715</v>
+        <v>44.96</v>
       </c>
       <c r="G36" t="n">
-        <v>44.88</v>
+        <v>44.96</v>
       </c>
       <c r="H36" t="n">
-        <v>44.88</v>
+        <v>44.96</v>
       </c>
       <c r="I36" t="n">
-        <v>44.88</v>
+        <v>44.96</v>
       </c>
       <c r="J36" t="n">
-        <v>236.4581443351238</v>
+        <v>238.7276497036009</v>
       </c>
       <c r="K36" t="n">
-        <v>544.9693001464883</v>
+        <v>547.2388055149654</v>
       </c>
       <c r="L36" t="n">
-        <v>976.7579942888583</v>
+        <v>979.0274996573354</v>
       </c>
       <c r="M36" t="n">
-        <v>1250.062386031718</v>
+        <v>1252.331891400195</v>
       </c>
       <c r="N36" t="n">
-        <v>1575.521778846833</v>
+        <v>1577.79128421531</v>
       </c>
       <c r="O36" t="n">
-        <v>1990.370569304137</v>
+        <v>1992.640074672614</v>
       </c>
       <c r="P36" t="n">
-        <v>2244.000000000059</v>
+        <v>2246.269505368536</v>
       </c>
       <c r="Q36" t="n">
-        <v>2165.4092424282</v>
+        <v>2246.269505368536</v>
       </c>
       <c r="R36" t="n">
-        <v>2007.901232965725</v>
+        <v>2001.779598411275</v>
       </c>
       <c r="S36" t="n">
-        <v>1899.112982572654</v>
+        <v>1892.991348018204</v>
       </c>
       <c r="T36" t="n">
-        <v>1841.184355613854</v>
+        <v>1835.062721059405</v>
       </c>
       <c r="U36" t="n">
-        <v>1785.465915223348</v>
+        <v>1779.344280668898</v>
       </c>
       <c r="V36" t="n">
-        <v>1715.253120080398</v>
+        <v>1709.131485525948</v>
       </c>
       <c r="W36" t="n">
-        <v>1626.99742017148</v>
+        <v>1620.87578561703</v>
       </c>
       <c r="X36" t="n">
-        <v>1551.378491438765</v>
+        <v>1545.256856884316</v>
       </c>
       <c r="Y36" t="n">
-        <v>1496.437690664892</v>
+        <v>1490.316056110443</v>
       </c>
     </row>
     <row r="37">
@@ -7062,76 +7062,76 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>731.6806342947774</v>
+        <v>267.0905946885322</v>
       </c>
       <c r="C37" t="n">
-        <v>731.6806342947774</v>
+        <v>338.6426005069679</v>
       </c>
       <c r="D37" t="n">
-        <v>731.6806342947774</v>
+        <v>397.511744631968</v>
       </c>
       <c r="E37" t="n">
-        <v>795.0595385061904</v>
+        <v>460.890648843381</v>
       </c>
       <c r="F37" t="n">
-        <v>795.0595385061904</v>
+        <v>530.8016214353165</v>
       </c>
       <c r="G37" t="n">
-        <v>894.6355847209445</v>
+        <v>630.3776676500706</v>
       </c>
       <c r="H37" t="n">
-        <v>1015.209913159031</v>
+        <v>750.9519960881568</v>
       </c>
       <c r="I37" t="n">
-        <v>1015.209913159031</v>
+        <v>936.2643379750593</v>
       </c>
       <c r="J37" t="n">
-        <v>1300.953015767703</v>
+        <v>1286.695337807839</v>
       </c>
       <c r="K37" t="n">
-        <v>1428.839800524243</v>
+        <v>1414.582122564379</v>
       </c>
       <c r="L37" t="n">
-        <v>1428.839800524243</v>
+        <v>1428.919800524243</v>
       </c>
       <c r="M37" t="n">
-        <v>1350.512142045098</v>
+        <v>1350.592142045098</v>
       </c>
       <c r="N37" t="n">
-        <v>1218.764525029487</v>
+        <v>1218.844525029487</v>
       </c>
       <c r="O37" t="n">
-        <v>1009.673228311158</v>
+        <v>1009.753228311157</v>
       </c>
       <c r="P37" t="n">
-        <v>740.2108382296055</v>
+        <v>740.2908382296055</v>
       </c>
       <c r="Q37" t="n">
-        <v>408.4509731532439</v>
+        <v>408.5309731532438</v>
       </c>
       <c r="R37" t="n">
-        <v>51.41391723586987</v>
+        <v>51.49391723586987</v>
       </c>
       <c r="S37" t="n">
-        <v>44.88</v>
+        <v>44.96</v>
       </c>
       <c r="T37" t="n">
-        <v>181.1525496506081</v>
+        <v>44.96</v>
       </c>
       <c r="U37" t="n">
-        <v>373.2875321249604</v>
+        <v>44.96</v>
       </c>
       <c r="V37" t="n">
-        <v>517.6589250109064</v>
+        <v>44.96</v>
       </c>
       <c r="W37" t="n">
-        <v>635.0998432705838</v>
+        <v>56.24316531901427</v>
       </c>
       <c r="X37" t="n">
-        <v>731.6806342947774</v>
+        <v>152.8239563432078</v>
       </c>
       <c r="Y37" t="n">
-        <v>731.6806342947774</v>
+        <v>209.78325702224</v>
       </c>
     </row>
     <row r="38">
@@ -7141,76 +7141,76 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>439.3918839655994</v>
+        <v>443.3918839655994</v>
       </c>
       <c r="C38" t="n">
-        <v>333.8620069524742</v>
+        <v>337.8620069524742</v>
       </c>
       <c r="D38" t="n">
-        <v>267.8628597405047</v>
+        <v>271.8628597405047</v>
       </c>
       <c r="E38" t="n">
-        <v>207.8999409456879</v>
+        <v>211.8999409456879</v>
       </c>
       <c r="F38" t="n">
-        <v>147.4053664931506</v>
+        <v>151.4053664931506</v>
       </c>
       <c r="G38" t="n">
-        <v>94.09552754683497</v>
+        <v>93.46355092482304</v>
       </c>
       <c r="H38" t="n">
-        <v>44.88</v>
+        <v>44.96</v>
       </c>
       <c r="I38" t="n">
-        <v>44.88</v>
+        <v>44.96</v>
       </c>
       <c r="J38" t="n">
-        <v>127.400205073642</v>
+        <v>553.4818942939371</v>
       </c>
       <c r="K38" t="n">
-        <v>682.790205073642</v>
+        <v>729.1534691180577</v>
       </c>
       <c r="L38" t="n">
-        <v>1238.180205073642</v>
+        <v>947.0895916306206</v>
       </c>
       <c r="M38" t="n">
-        <v>1793.570205073646</v>
+        <v>947.0895916306206</v>
       </c>
       <c r="N38" t="n">
-        <v>1882.549243836214</v>
+        <v>1330.169243836214</v>
       </c>
       <c r="O38" t="n">
-        <v>2045.691050093541</v>
+        <v>1493.311050093541</v>
       </c>
       <c r="P38" t="n">
-        <v>2244</v>
+        <v>1691.62</v>
       </c>
       <c r="Q38" t="n">
-        <v>2244</v>
+        <v>2248</v>
       </c>
       <c r="R38" t="n">
-        <v>2244</v>
+        <v>2248</v>
       </c>
       <c r="S38" t="n">
-        <v>2124.74729509841</v>
+        <v>2128.74729509841</v>
       </c>
       <c r="T38" t="n">
-        <v>1886.798730233762</v>
+        <v>1890.798730233762</v>
       </c>
       <c r="U38" t="n">
-        <v>1579.617216538145</v>
+        <v>1583.617216538145</v>
       </c>
       <c r="V38" t="n">
-        <v>1291.888909298929</v>
+        <v>1295.888909298929</v>
       </c>
       <c r="W38" t="n">
-        <v>995.5520648737293</v>
+        <v>999.5520648737293</v>
       </c>
       <c r="X38" t="n">
-        <v>745.7724351154791</v>
+        <v>749.7724351154791</v>
       </c>
       <c r="Y38" t="n">
-        <v>577.7750283651696</v>
+        <v>581.7750283651696</v>
       </c>
     </row>
     <row r="39">
@@ -7220,76 +7220,76 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1535.072330412178</v>
+        <v>143.4024418412611</v>
       </c>
       <c r="C39" t="n">
-        <v>1170.324944103573</v>
+        <v>127.1399040175043</v>
       </c>
       <c r="D39" t="n">
-        <v>818.8727351159944</v>
+        <v>124.1725435147743</v>
       </c>
       <c r="E39" t="n">
-        <v>472.7393035787089</v>
+        <v>124.1725435147743</v>
       </c>
       <c r="F39" t="n">
-        <v>129.672392126308</v>
+        <v>124.1725435147743</v>
       </c>
       <c r="G39" t="n">
-        <v>129.672392126308</v>
+        <v>124.1725435147743</v>
       </c>
       <c r="H39" t="n">
-        <v>129.672392126308</v>
+        <v>124.1725435147743</v>
       </c>
       <c r="I39" t="n">
-        <v>44.88</v>
+        <v>44.96</v>
       </c>
       <c r="J39" t="n">
-        <v>236.4581443351238</v>
+        <v>238.7276497036009</v>
       </c>
       <c r="K39" t="n">
-        <v>544.9693001464883</v>
+        <v>547.2388055149654</v>
       </c>
       <c r="L39" t="n">
-        <v>976.7579942888583</v>
+        <v>979.0274996573354</v>
       </c>
       <c r="M39" t="n">
-        <v>1250.062386031718</v>
+        <v>1252.331891400195</v>
       </c>
       <c r="N39" t="n">
-        <v>1575.521778846833</v>
+        <v>1577.79128421531</v>
       </c>
       <c r="O39" t="n">
-        <v>1990.370569304137</v>
+        <v>1992.640074672614</v>
       </c>
       <c r="P39" t="n">
-        <v>2244.000000000059</v>
+        <v>2246.269505368536</v>
       </c>
       <c r="Q39" t="n">
-        <v>2244.000000000059</v>
+        <v>2246.269505368536</v>
       </c>
       <c r="R39" t="n">
-        <v>2086.491990537583</v>
+        <v>2088.76149590606</v>
       </c>
       <c r="S39" t="n">
-        <v>1977.703740144512</v>
+        <v>1979.973245512989</v>
       </c>
       <c r="T39" t="n">
-        <v>1919.775113185713</v>
+        <v>1922.04461855419</v>
       </c>
       <c r="U39" t="n">
-        <v>1864.056672795206</v>
+        <v>1517.841329678834</v>
       </c>
       <c r="V39" t="n">
-        <v>1793.843877652256</v>
+        <v>1099.143686051036</v>
       </c>
       <c r="W39" t="n">
-        <v>1705.588177743338</v>
+        <v>662.4031376572698</v>
       </c>
       <c r="X39" t="n">
-        <v>1629.969249010624</v>
+        <v>238.2993604397066</v>
       </c>
       <c r="Y39" t="n">
-        <v>1575.028448236751</v>
+        <v>183.3585596658335</v>
       </c>
     </row>
     <row r="40">
@@ -7299,76 +7299,76 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>845.9472726401018</v>
+        <v>460.890648843381</v>
       </c>
       <c r="C40" t="n">
-        <v>917.4992784585376</v>
+        <v>460.890648843381</v>
       </c>
       <c r="D40" t="n">
-        <v>976.3684225835376</v>
+        <v>460.890648843381</v>
       </c>
       <c r="E40" t="n">
-        <v>1039.747326794951</v>
+        <v>460.890648843381</v>
       </c>
       <c r="F40" t="n">
-        <v>1109.658299386886</v>
+        <v>530.8016214353165</v>
       </c>
       <c r="G40" t="n">
-        <v>1209.23434560164</v>
+        <v>630.3776676500706</v>
       </c>
       <c r="H40" t="n">
-        <v>1329.808674039726</v>
+        <v>750.9519960881568</v>
       </c>
       <c r="I40" t="n">
-        <v>1419.958800691464</v>
+        <v>936.2643379750593</v>
       </c>
       <c r="J40" t="n">
-        <v>1428.839800524243</v>
+        <v>1286.695337807839</v>
       </c>
       <c r="K40" t="n">
-        <v>1428.839800524243</v>
+        <v>1414.582122564379</v>
       </c>
       <c r="L40" t="n">
-        <v>1428.839800524243</v>
+        <v>1428.919800524243</v>
       </c>
       <c r="M40" t="n">
-        <v>1350.512142045098</v>
+        <v>1350.592142045098</v>
       </c>
       <c r="N40" t="n">
-        <v>1218.764525029487</v>
+        <v>1218.844525029487</v>
       </c>
       <c r="O40" t="n">
-        <v>1009.673228311158</v>
+        <v>1009.753228311157</v>
       </c>
       <c r="P40" t="n">
-        <v>740.2108382296055</v>
+        <v>740.2908382296055</v>
       </c>
       <c r="Q40" t="n">
-        <v>408.4509731532439</v>
+        <v>408.5309731532439</v>
       </c>
       <c r="R40" t="n">
-        <v>51.41391723586987</v>
+        <v>51.49391723586989</v>
       </c>
       <c r="S40" t="n">
-        <v>44.88</v>
+        <v>44.96</v>
       </c>
       <c r="T40" t="n">
-        <v>181.1525496506081</v>
+        <v>44.96</v>
       </c>
       <c r="U40" t="n">
-        <v>373.2875321249604</v>
+        <v>237.0949824743522</v>
       </c>
       <c r="V40" t="n">
-        <v>517.6589250109064</v>
+        <v>343.4497305837036</v>
       </c>
       <c r="W40" t="n">
-        <v>635.0998432705838</v>
+        <v>460.890648843381</v>
       </c>
       <c r="X40" t="n">
-        <v>731.6806342947774</v>
+        <v>460.890648843381</v>
       </c>
       <c r="Y40" t="n">
-        <v>788.6399349738097</v>
+        <v>460.890648843381</v>
       </c>
     </row>
     <row r="41">
@@ -7378,76 +7378,76 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>444.0238605876112</v>
+        <v>402.987843561559</v>
       </c>
       <c r="C41" t="n">
-        <v>338.4939835744861</v>
+        <v>292.4074614979288</v>
       </c>
       <c r="D41" t="n">
-        <v>272.4948363625166</v>
+        <v>221.3578092354543</v>
       </c>
       <c r="E41" t="n">
-        <v>212.5319175676998</v>
+        <v>156.3443853901324</v>
       </c>
       <c r="F41" t="n">
-        <v>152.0373431151626</v>
+        <v>90.79930588709011</v>
       </c>
       <c r="G41" t="n">
-        <v>94.09552754683496</v>
+        <v>90.79930588709011</v>
       </c>
       <c r="H41" t="n">
-        <v>44.88</v>
+        <v>44.96</v>
       </c>
       <c r="I41" t="n">
-        <v>44.88</v>
+        <v>44.96</v>
       </c>
       <c r="J41" t="n">
-        <v>127.400205073642</v>
+        <v>127.480205073642</v>
       </c>
       <c r="K41" t="n">
-        <v>303.0717798977627</v>
+        <v>555.8531213236513</v>
       </c>
       <c r="L41" t="n">
-        <v>521.0079024103255</v>
+        <v>773.789243836214</v>
       </c>
       <c r="M41" t="n">
-        <v>771.7692438362103</v>
+        <v>1330.169243836214</v>
       </c>
       <c r="N41" t="n">
-        <v>1327.159243836212</v>
+        <v>1330.169243836214</v>
       </c>
       <c r="O41" t="n">
-        <v>1490.301050093539</v>
+        <v>1493.311050093541</v>
       </c>
       <c r="P41" t="n">
-        <v>1688.609999999998</v>
+        <v>1691.62</v>
       </c>
       <c r="Q41" t="n">
-        <v>2244</v>
+        <v>2248</v>
       </c>
       <c r="R41" t="n">
-        <v>2244</v>
+        <v>2248</v>
       </c>
       <c r="S41" t="n">
-        <v>2124.74729509841</v>
+        <v>2123.696790047905</v>
       </c>
       <c r="T41" t="n">
-        <v>1886.798730233762</v>
+        <v>1880.697720132752</v>
       </c>
       <c r="U41" t="n">
-        <v>1579.617216538145</v>
+        <v>1568.46570138663</v>
       </c>
       <c r="V41" t="n">
-        <v>1291.888909298929</v>
+        <v>1275.686889096909</v>
       </c>
       <c r="W41" t="n">
-        <v>995.5520648737293</v>
+        <v>974.2995396212041</v>
       </c>
       <c r="X41" t="n">
-        <v>745.7724351154791</v>
+        <v>719.4694048124488</v>
       </c>
       <c r="Y41" t="n">
-        <v>577.7750283651696</v>
+        <v>546.4214930116343</v>
       </c>
     </row>
     <row r="42">
@@ -7457,76 +7457,76 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>605.9571148738752</v>
+        <v>1491.88729032611</v>
       </c>
       <c r="C42" t="n">
-        <v>589.6945770501184</v>
+        <v>1127.139904017504</v>
       </c>
       <c r="D42" t="n">
-        <v>238.24236806254</v>
+        <v>775.6876950299261</v>
       </c>
       <c r="E42" t="n">
-        <v>238.24236806254</v>
+        <v>429.5542634926406</v>
       </c>
       <c r="F42" t="n">
-        <v>238.24236806254</v>
+        <v>86.48735204023967</v>
       </c>
       <c r="G42" t="n">
-        <v>238.24236806254</v>
+        <v>86.48735204023967</v>
       </c>
       <c r="H42" t="n">
-        <v>238.24236806254</v>
+        <v>44.96</v>
       </c>
       <c r="I42" t="n">
-        <v>44.88</v>
+        <v>44.96</v>
       </c>
       <c r="J42" t="n">
-        <v>236.4581443351165</v>
+        <v>238.7276497036009</v>
       </c>
       <c r="K42" t="n">
-        <v>544.969300146481</v>
+        <v>547.2388055149654</v>
       </c>
       <c r="L42" t="n">
-        <v>976.757994288851</v>
+        <v>979.0274996573354</v>
       </c>
       <c r="M42" t="n">
-        <v>1250.06238603171</v>
+        <v>1252.331891400195</v>
       </c>
       <c r="N42" t="n">
-        <v>1575.521778846826</v>
+        <v>1577.79128421531</v>
       </c>
       <c r="O42" t="n">
-        <v>1990.37056930413</v>
+        <v>1992.640074672614</v>
       </c>
       <c r="P42" t="n">
-        <v>2244.000000000051</v>
+        <v>2246.269505368536</v>
       </c>
       <c r="Q42" t="n">
-        <v>2244.000000000051</v>
+        <v>2246.269505368536</v>
       </c>
       <c r="R42" t="n">
-        <v>1738.007142052727</v>
+        <v>2083.710990855555</v>
       </c>
       <c r="S42" t="n">
-        <v>1280.734043174808</v>
+        <v>1969.87223541198</v>
       </c>
       <c r="T42" t="n">
-        <v>990.6598976474095</v>
+        <v>1906.893103402675</v>
       </c>
       <c r="U42" t="n">
-        <v>934.9414572569026</v>
+        <v>1846.124157961663</v>
       </c>
       <c r="V42" t="n">
-        <v>864.728662113953</v>
+        <v>1770.860857768208</v>
       </c>
       <c r="W42" t="n">
-        <v>776.4729622050353</v>
+        <v>1677.554652808785</v>
       </c>
       <c r="X42" t="n">
-        <v>700.8540334723206</v>
+        <v>1596.885219025565</v>
       </c>
       <c r="Y42" t="n">
-        <v>645.9132326984475</v>
+        <v>1536.893913201187</v>
       </c>
     </row>
     <row r="43">
@@ -7536,76 +7536,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>716.0339633222192</v>
+        <v>657.3184783269205</v>
       </c>
       <c r="C43" t="n">
-        <v>716.0339633222192</v>
+        <v>723.9204841453563</v>
       </c>
       <c r="D43" t="n">
-        <v>716.0339633222192</v>
+        <v>777.8396282703565</v>
       </c>
       <c r="E43" t="n">
-        <v>716.0339633222192</v>
+        <v>836.2685324817695</v>
       </c>
       <c r="F43" t="n">
-        <v>716.0339633222192</v>
+        <v>901.229505073705</v>
       </c>
       <c r="G43" t="n">
-        <v>815.6100095369733</v>
+        <v>995.8555512884591</v>
       </c>
       <c r="H43" t="n">
-        <v>936.1843379750594</v>
+        <v>995.8555512884591</v>
       </c>
       <c r="I43" t="n">
-        <v>936.1843379750594</v>
+        <v>995.8555512884591</v>
       </c>
       <c r="J43" t="n">
-        <v>1286.615337807839</v>
+        <v>1341.336551121238</v>
       </c>
       <c r="K43" t="n">
-        <v>1414.502122564379</v>
+        <v>1464.273335877779</v>
       </c>
       <c r="L43" t="n">
-        <v>1428.839800524243</v>
+        <v>1464.273335877779</v>
       </c>
       <c r="M43" t="n">
-        <v>1350.512142045098</v>
+        <v>1380.895172348129</v>
       </c>
       <c r="N43" t="n">
-        <v>1218.764525029487</v>
+        <v>1244.097050282012</v>
       </c>
       <c r="O43" t="n">
-        <v>1009.673228311158</v>
+        <v>1029.955248513178</v>
       </c>
       <c r="P43" t="n">
-        <v>740.2108382296055</v>
+        <v>755.4423533811207</v>
       </c>
       <c r="Q43" t="n">
-        <v>408.4509731532439</v>
+        <v>418.631983254254</v>
       </c>
       <c r="R43" t="n">
-        <v>51.41391723586989</v>
+        <v>56.54442228637494</v>
       </c>
       <c r="S43" t="n">
-        <v>44.88</v>
+        <v>44.96</v>
       </c>
       <c r="T43" t="n">
-        <v>181.1525496506081</v>
+        <v>44.96</v>
       </c>
       <c r="U43" t="n">
-        <v>373.2875321249604</v>
+        <v>232.1449824743522</v>
       </c>
       <c r="V43" t="n">
-        <v>517.6589250109064</v>
+        <v>371.5663753602982</v>
       </c>
       <c r="W43" t="n">
-        <v>635.0998432705838</v>
+        <v>484.0572936199756</v>
       </c>
       <c r="X43" t="n">
-        <v>716.0339633222192</v>
+        <v>575.6880846441692</v>
       </c>
       <c r="Y43" t="n">
-        <v>716.0339633222192</v>
+        <v>627.6973853232014</v>
       </c>
     </row>
     <row r="44">
@@ -7615,76 +7615,76 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>439.3918839655994</v>
+        <v>474.4068908906416</v>
       </c>
       <c r="C44" t="n">
-        <v>333.8620069524742</v>
+        <v>363.8265088270114</v>
       </c>
       <c r="D44" t="n">
-        <v>267.8628597405047</v>
+        <v>292.7768565645368</v>
       </c>
       <c r="E44" t="n">
-        <v>207.8999409456879</v>
+        <v>227.763432719215</v>
       </c>
       <c r="F44" t="n">
-        <v>147.4053664931506</v>
+        <v>162.2183532161727</v>
       </c>
       <c r="G44" t="n">
-        <v>94.09552754683497</v>
+        <v>99.22603259734001</v>
       </c>
       <c r="H44" t="n">
-        <v>44.88</v>
+        <v>44.96</v>
       </c>
       <c r="I44" t="n">
-        <v>44.88</v>
+        <v>44.96</v>
       </c>
       <c r="J44" t="n">
-        <v>127.400205073642</v>
+        <v>127.480205073642</v>
       </c>
       <c r="K44" t="n">
-        <v>682.790205073642</v>
+        <v>683.860205073642</v>
       </c>
       <c r="L44" t="n">
-        <v>1238.180205073642</v>
+        <v>1240.240205073642</v>
       </c>
       <c r="M44" t="n">
-        <v>1793.570205073642</v>
+        <v>1330.169243836214</v>
       </c>
       <c r="N44" t="n">
-        <v>1882.549243836214</v>
+        <v>1330.169243836214</v>
       </c>
       <c r="O44" t="n">
-        <v>2045.691050093541</v>
+        <v>1493.311050093541</v>
       </c>
       <c r="P44" t="n">
-        <v>2244</v>
+        <v>1691.62</v>
       </c>
       <c r="Q44" t="n">
-        <v>2244</v>
+        <v>2248</v>
       </c>
       <c r="R44" t="n">
-        <v>2244</v>
+        <v>2248</v>
       </c>
       <c r="S44" t="n">
-        <v>2124.74729509841</v>
+        <v>2195.115837376987</v>
       </c>
       <c r="T44" t="n">
-        <v>1886.798730233762</v>
+        <v>1952.116767461835</v>
       </c>
       <c r="U44" t="n">
-        <v>1579.617216538145</v>
+        <v>1639.884748715712</v>
       </c>
       <c r="V44" t="n">
-        <v>1291.888909298929</v>
+        <v>1347.105936425991</v>
       </c>
       <c r="W44" t="n">
-        <v>995.5520648737293</v>
+        <v>1045.718586950287</v>
       </c>
       <c r="X44" t="n">
-        <v>745.7724351154791</v>
+        <v>790.8884521415314</v>
       </c>
       <c r="Y44" t="n">
-        <v>577.7750283651696</v>
+        <v>617.8405403407169</v>
       </c>
     </row>
     <row r="45">
@@ -7694,76 +7694,76 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1535.072330412178</v>
+        <v>1106.925594851527</v>
       </c>
       <c r="C45" t="n">
-        <v>1170.324944103573</v>
+        <v>742.1782085429213</v>
       </c>
       <c r="D45" t="n">
-        <v>818.8727351159944</v>
+        <v>390.7259995553429</v>
       </c>
       <c r="E45" t="n">
-        <v>818.8727351159944</v>
+        <v>388.0269114524009</v>
       </c>
       <c r="F45" t="n">
-        <v>475.8058236635935</v>
+        <v>44.96</v>
       </c>
       <c r="G45" t="n">
-        <v>147.5299059701219</v>
+        <v>44.96</v>
       </c>
       <c r="H45" t="n">
-        <v>44.88</v>
+        <v>44.96</v>
       </c>
       <c r="I45" t="n">
-        <v>44.88</v>
+        <v>44.96</v>
       </c>
       <c r="J45" t="n">
-        <v>238.6476497036008</v>
+        <v>238.7276497036009</v>
       </c>
       <c r="K45" t="n">
-        <v>547.1588055149654</v>
+        <v>547.2388055149654</v>
       </c>
       <c r="L45" t="n">
-        <v>978.9474996573354</v>
+        <v>979.0274996573354</v>
       </c>
       <c r="M45" t="n">
-        <v>1252.251891400195</v>
+        <v>1252.331891400195</v>
       </c>
       <c r="N45" t="n">
-        <v>1577.71128421531</v>
+        <v>1577.79128421531</v>
       </c>
       <c r="O45" t="n">
-        <v>1992.560074672614</v>
+        <v>1992.640074672614</v>
       </c>
       <c r="P45" t="n">
-        <v>2244.000000000059</v>
+        <v>2246.269505368536</v>
       </c>
       <c r="Q45" t="n">
-        <v>2244.000000000059</v>
+        <v>2246.269505368536</v>
       </c>
       <c r="R45" t="n">
-        <v>2086.491990537583</v>
+        <v>2083.710990855555</v>
       </c>
       <c r="S45" t="n">
-        <v>1977.703740144512</v>
+        <v>1969.87223541198</v>
       </c>
       <c r="T45" t="n">
-        <v>1919.775113185713</v>
+        <v>1906.893103402675</v>
       </c>
       <c r="U45" t="n">
-        <v>1864.056672795206</v>
+        <v>1846.124157961663</v>
       </c>
       <c r="V45" t="n">
-        <v>1793.843877652256</v>
+        <v>1729.333505727968</v>
       </c>
       <c r="W45" t="n">
-        <v>1705.588177743338</v>
+        <v>1636.027300768546</v>
       </c>
       <c r="X45" t="n">
-        <v>1629.969249010624</v>
+        <v>1211.923523550982</v>
       </c>
       <c r="Y45" t="n">
-        <v>1575.028448236751</v>
+        <v>1151.932217726604</v>
       </c>
     </row>
     <row r="46">
@@ -7773,76 +7773,76 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>800.7196156168809</v>
+        <v>351.9441300420675</v>
       </c>
       <c r="C46" t="n">
-        <v>872.2716214353167</v>
+        <v>418.5461358605033</v>
       </c>
       <c r="D46" t="n">
-        <v>872.2716214353167</v>
+        <v>472.4652799855033</v>
       </c>
       <c r="E46" t="n">
-        <v>872.2716214353167</v>
+        <v>530.8941841969164</v>
       </c>
       <c r="F46" t="n">
-        <v>872.2716214353167</v>
+        <v>595.8551567888519</v>
       </c>
       <c r="G46" t="n">
-        <v>971.8476676500708</v>
+        <v>690.4812030036061</v>
       </c>
       <c r="H46" t="n">
-        <v>1092.421996088157</v>
+        <v>806.1055314416922</v>
       </c>
       <c r="I46" t="n">
-        <v>1277.734337975059</v>
+        <v>986.4678733285948</v>
       </c>
       <c r="J46" t="n">
-        <v>1286.615337807839</v>
+        <v>1331.948873161374</v>
       </c>
       <c r="K46" t="n">
-        <v>1414.502122564379</v>
+        <v>1454.885657917914</v>
       </c>
       <c r="L46" t="n">
-        <v>1428.839800524243</v>
+        <v>1464.273335877779</v>
       </c>
       <c r="M46" t="n">
-        <v>1350.512142045098</v>
+        <v>1380.895172348129</v>
       </c>
       <c r="N46" t="n">
-        <v>1218.764525029487</v>
+        <v>1244.097050282012</v>
       </c>
       <c r="O46" t="n">
-        <v>1009.673228311158</v>
+        <v>1029.955248513178</v>
       </c>
       <c r="P46" t="n">
-        <v>740.2108382296055</v>
+        <v>755.4423533811207</v>
       </c>
       <c r="Q46" t="n">
-        <v>408.4509731532439</v>
+        <v>418.631983254254</v>
       </c>
       <c r="R46" t="n">
-        <v>51.41391723586987</v>
+        <v>56.54442228637494</v>
       </c>
       <c r="S46" t="n">
-        <v>44.88</v>
+        <v>44.96</v>
       </c>
       <c r="T46" t="n">
-        <v>181.1525496506081</v>
+        <v>176.2825496506081</v>
       </c>
       <c r="U46" t="n">
-        <v>373.2875321249604</v>
+        <v>176.2825496506081</v>
       </c>
       <c r="V46" t="n">
-        <v>517.6589250109064</v>
+        <v>176.2825496506081</v>
       </c>
       <c r="W46" t="n">
-        <v>589.8721862473629</v>
+        <v>176.2825496506081</v>
       </c>
       <c r="X46" t="n">
-        <v>686.4529772715565</v>
+        <v>247.5774916967432</v>
       </c>
       <c r="Y46" t="n">
-        <v>743.4122779505888</v>
+        <v>299.5867923757754</v>
       </c>
     </row>
   </sheetData>
@@ -7967,10 +7967,10 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>321.3286984924623</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>234.1880104510425</v>
+        <v>240.7734830736778</v>
       </c>
       <c r="M2" t="n">
         <v>471.5549969890509</v>
@@ -7979,13 +7979,13 @@
         <v>777.3653500296342</v>
       </c>
       <c r="O2" t="n">
-        <v>374.4816735941929</v>
+        <v>0.4816735941929551</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>314.7432258698271</v>
       </c>
       <c r="Q2" t="n">
-        <v>128.1077446289929</v>
+        <v>502.1077446289929</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8216,13 +8216,13 @@
         <v>403.3653500296342</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4816735941929551</v>
+        <v>374.4816735941929</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>502.1077446289929</v>
+        <v>128.1077446289929</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8441,25 +8441,25 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>321.3286984924623</v>
+        <v>320.8173266331659</v>
       </c>
       <c r="L8" t="n">
-        <v>308.6565929648241</v>
+        <v>308.0221909547739</v>
       </c>
       <c r="M8" t="n">
-        <v>471.5549969890509</v>
+        <v>769.2655554061457</v>
       </c>
       <c r="N8" t="n">
-        <v>702.8967675158526</v>
+        <v>402.6480334467196</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4816735941929551</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>502.1077446289929</v>
+        <v>501.6736190008522</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8535,7 +8535,7 @@
         <v>382.6817988009037</v>
       </c>
       <c r="P9" t="n">
-        <v>219.1507118405495</v>
+        <v>216.3081458117257</v>
       </c>
       <c r="Q9" t="n">
         <v>17.27519534353338</v>
@@ -8678,16 +8678,16 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>471.5539648241206</v>
       </c>
       <c r="L11" t="n">
-        <v>47.80341426035193</v>
+        <v>428.8625025125627</v>
       </c>
       <c r="M11" t="n">
-        <v>947.3167457327716</v>
+        <v>299.3167457327696</v>
       </c>
       <c r="N11" t="n">
-        <v>228.3401037984784</v>
+        <v>621.357628588657</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -8696,7 +8696,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>615.8520732695737</v>
+        <v>22.18109136266131</v>
       </c>
       <c r="R11" t="n">
         <v>294.54111633436</v>
@@ -8912,10 +8912,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>197.1695207089205</v>
       </c>
       <c r="K14" t="n">
-        <v>195.209924749319</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -8927,10 +8927,10 @@
         <v>228.3401037984784</v>
       </c>
       <c r="O14" t="n">
-        <v>483.2102967097736</v>
+        <v>484.2102967097708</v>
       </c>
       <c r="P14" t="n">
-        <v>447.687929387418</v>
+        <v>448.6879293874151</v>
       </c>
       <c r="Q14" t="n">
         <v>615.8520732695737</v>
@@ -9149,19 +9149,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J17" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>470.5539648241206</v>
+        <v>471.5539648241206</v>
       </c>
       <c r="L17" t="n">
-        <v>225.2494494362334</v>
+        <v>428.8625025125627</v>
       </c>
       <c r="M17" t="n">
-        <v>299.3167457327696</v>
+        <v>948.3167457327697</v>
       </c>
       <c r="N17" t="n">
-        <v>228.3401037984784</v>
+        <v>402.6623651748134</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -9170,7 +9170,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>615.8520732695737</v>
+        <v>22.18109136266131</v>
       </c>
       <c r="R17" t="n">
         <v>294.54111633436</v>
@@ -9389,16 +9389,16 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K20" t="n">
-        <v>470.5539648241206</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>225.2494494362334</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>299.3167457327696</v>
+        <v>948.3167457327697</v>
       </c>
       <c r="N20" t="n">
-        <v>228.3401037984784</v>
+        <v>872.7740959253404</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -9407,7 +9407,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>615.8520732695737</v>
+        <v>22.18109136266131</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9623,19 +9623,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J23" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>470.5539648241206</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>427.8625025125627</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>690.3746745633521</v>
+        <v>948.3167457327697</v>
       </c>
       <c r="N23" t="n">
-        <v>228.3401037984784</v>
+        <v>877.3401037984784</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -9644,7 +9644,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>22.18109136266131</v>
+        <v>447.9198200756803</v>
       </c>
       <c r="R23" t="n">
         <v>294.54111633436</v>
@@ -9860,19 +9860,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K26" t="n">
-        <v>470.5539648241206</v>
+        <v>472.5539648241206</v>
       </c>
       <c r="L26" t="n">
-        <v>427.8625025125627</v>
+        <v>429.8625025125627</v>
       </c>
       <c r="M26" t="n">
-        <v>947.3167457327725</v>
+        <v>694.2938664825442</v>
       </c>
       <c r="N26" t="n">
-        <v>401.7027692152149</v>
+        <v>228.3401037984784</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -10100,16 +10100,16 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>470.5539648241206</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>427.8625025125627</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>472.6794111495053</v>
+        <v>783.344088498472</v>
       </c>
       <c r="N29" t="n">
-        <v>876.340103798482</v>
+        <v>878.3401037984784</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -10118,7 +10118,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>22.18109136266131</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10337,16 +10337,16 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>470.5539648241206</v>
+        <v>54.16484025313969</v>
       </c>
       <c r="L32" t="n">
-        <v>7.554186022386602</v>
+        <v>429.8625025125629</v>
       </c>
       <c r="M32" t="n">
-        <v>299.3167457327696</v>
+        <v>949.3167457327697</v>
       </c>
       <c r="N32" t="n">
-        <v>876.3401037984816</v>
+        <v>228.3401037984784</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -10574,19 +10574,19 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>383.5539648241206</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>340.8625025125627</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>389.1945626646604</v>
+        <v>719.360329251169</v>
       </c>
       <c r="N35" t="n">
-        <v>789.3401037984784</v>
+        <v>790.3401037984784</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>397.2102967097708</v>
       </c>
       <c r="P35" t="n">
         <v>0</v>
@@ -10650,7 +10650,7 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J36" t="n">
-        <v>225.2531203434682</v>
+        <v>227.4647419277884</v>
       </c>
       <c r="K36" t="n">
         <v>295.8802408630135</v>
@@ -10808,19 +10808,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K38" t="n">
-        <v>383.5539648241206</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>340.8625025125627</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>860.3167457327734</v>
+        <v>299.3167457327696</v>
       </c>
       <c r="N38" t="n">
-        <v>318.2179207303656</v>
+        <v>615.2892474404921</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -10829,7 +10829,7 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>22.18109136266131</v>
+        <v>584.1810913626613</v>
       </c>
       <c r="R38" t="n">
         <v>294.54111633436</v>
@@ -10887,7 +10887,7 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J39" t="n">
-        <v>225.2531203434682</v>
+        <v>227.4647419277884</v>
       </c>
       <c r="K39" t="n">
         <v>295.8802408630135</v>
@@ -11048,16 +11048,16 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>255.2538802281705</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>552.6110300013401</v>
+        <v>861.3167457327697</v>
       </c>
       <c r="N41" t="n">
-        <v>789.3401037984802</v>
+        <v>228.3401037984784</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -11066,7 +11066,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>583.1810913626632</v>
+        <v>584.1810913626613</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -11124,7 +11124,7 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J42" t="n">
-        <v>225.2531203434608</v>
+        <v>227.4647419277884</v>
       </c>
       <c r="K42" t="n">
         <v>295.8802408630135</v>
@@ -11285,16 +11285,16 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>383.5539648241206</v>
+        <v>384.5539648241206</v>
       </c>
       <c r="L44" t="n">
-        <v>340.8625025125627</v>
+        <v>341.862502512563</v>
       </c>
       <c r="M44" t="n">
-        <v>860.3167457327697</v>
+        <v>390.1541586242564</v>
       </c>
       <c r="N44" t="n">
-        <v>318.2179207303693</v>
+        <v>228.3401037984784</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -11303,7 +11303,7 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>22.18109136266131</v>
+        <v>584.1810913626613</v>
       </c>
       <c r="R44" t="n">
         <v>294.54111633436</v>
@@ -11379,7 +11379,7 @@
         <v>382.6817988009037</v>
       </c>
       <c r="P45" t="n">
-        <v>216.9390902562291</v>
+        <v>219.1507118405495</v>
       </c>
       <c r="Q45" t="n">
         <v>17.27519534353338</v>
@@ -22569,7 +22569,7 @@
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>1.051603248924948e-12</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -23277,7 +23277,7 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.956056855791701</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -23475,7 +23475,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>2.95605685579163</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -23766,7 +23766,7 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.956056855791672</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -24003,7 +24003,7 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.956056855791672</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -24183,7 +24183,7 @@
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>2.956056855769575</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -24423,7 +24423,7 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>2.956056855791442</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -24663,7 +24663,7 @@
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>2.956056855751569</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -24942,7 +24942,7 @@
         <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>2.95605685579153</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
         <v>0</v>
@@ -25134,7 +25134,7 @@
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>4.585656855791843</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -25179,7 +25179,7 @@
         <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>0.7048568557917747</v>
       </c>
       <c r="W35" t="n">
         <v>0</v>
@@ -25371,10 +25371,10 @@
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>4.585656855791843</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>0.7048568557917889</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -25593,7 +25593,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4.585656855791683</v>
+        <v>0</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
@@ -25608,10 +25608,10 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>62.36239741264433</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>8.342459443147391</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -25845,7 +25845,7 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>4.585656855791843</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -25881,7 +25881,7 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>70.70485685579149</v>
       </c>
       <c r="T44" t="n">
         <v>0</v>
@@ -26102,7 +26102,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2459333.915074921</v>
+        <v>2459187.915635035</v>
       </c>
     </row>
     <row r="5">
@@ -26110,7 +26110,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3245404.164969369</v>
+        <v>3245645.78394946</v>
       </c>
     </row>
     <row r="6">
@@ -26118,7 +26118,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>4032367.751348666</v>
+        <v>4032756.434157332</v>
       </c>
     </row>
     <row r="7">
@@ -26126,7 +26126,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4819331.337727963</v>
+        <v>4819867.084365204</v>
       </c>
     </row>
     <row r="8">
@@ -26134,7 +26134,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5606294.924107256</v>
+        <v>5606977.734573073</v>
       </c>
     </row>
     <row r="9">
@@ -26142,7 +26142,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6393258.51048655</v>
+        <v>6394088.384780941</v>
       </c>
     </row>
     <row r="10">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7180222.096865843</v>
+        <v>7181293.590140325</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7967185.683245138</v>
+        <v>7968404.240348194</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>8754149.269624436</v>
+        <v>8755514.890556067</v>
       </c>
     </row>
     <row r="13">
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9532777.353395367</v>
+        <v>9534269.620802036</v>
       </c>
     </row>
     <row r="14">
@@ -26182,7 +26182,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>10319659.86717467</v>
+        <v>10321345.20438134</v>
       </c>
     </row>
     <row r="15">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>11106542.38095397</v>
+        <v>11104938.28796064</v>
       </c>
     </row>
     <row r="16">
@@ -26198,7 +26198,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11893424.89473327</v>
+        <v>11888531.37153994</v>
       </c>
     </row>
   </sheetData>
@@ -26275,43 +26275,43 @@
         <v>1416799.170374169</v>
       </c>
       <c r="D2" t="n">
+        <v>1416799.17037417</v>
+      </c>
+      <c r="E2" t="n">
         <v>1416799.170374169</v>
       </c>
-      <c r="E2" t="n">
-        <v>1416534.455482733</v>
-      </c>
       <c r="F2" t="n">
-        <v>1416534.455482734</v>
+        <v>1416799.170374169</v>
       </c>
       <c r="G2" t="n">
-        <v>1416534.455482733</v>
+        <v>1416799.17037417</v>
       </c>
       <c r="H2" t="n">
-        <v>1416534.455482733</v>
+        <v>1416799.17037417</v>
       </c>
       <c r="I2" t="n">
-        <v>1416534.455482735</v>
+        <v>1416799.170374169</v>
       </c>
       <c r="J2" t="n">
-        <v>1416534.455482734</v>
+        <v>1416799.17037417</v>
       </c>
       <c r="K2" t="n">
-        <v>1416534.455482737</v>
+        <v>1416799.170374169</v>
       </c>
       <c r="L2" t="n">
-        <v>1416534.455482733</v>
+        <v>1416799.170374169</v>
       </c>
       <c r="M2" t="n">
-        <v>1416388.524802734</v>
+        <v>1416736.050442733</v>
       </c>
       <c r="N2" t="n">
-        <v>1416388.524802733</v>
+        <v>1416736.050442734</v>
       </c>
       <c r="O2" t="n">
-        <v>1416388.524802734</v>
+        <v>1410467.550442734</v>
       </c>
       <c r="P2" t="n">
-        <v>1416388.524802733</v>
+        <v>1410467.550442734</v>
       </c>
     </row>
     <row r="3">
@@ -26327,10 +26327,10 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>975</v>
       </c>
       <c r="E3" t="n">
-        <v>591148</v>
+        <v>590525</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -26345,7 +26345,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>388448</v>
+        <v>388800</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -26360,7 +26360,7 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>256800</v>
+        <v>252800</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>602166.8573620638</v>
+        <v>601967.7658514546</v>
       </c>
       <c r="C4" t="n">
-        <v>600158.4933044576</v>
+        <v>599959.4017938484</v>
       </c>
       <c r="D4" t="n">
-        <v>598147.4047756541</v>
+        <v>597727.0650659911</v>
       </c>
       <c r="E4" t="n">
-        <v>513949.0290844531</v>
+        <v>513807.9040017775</v>
       </c>
       <c r="F4" t="n">
-        <v>512264.4313324891</v>
+        <v>512123.4760862632</v>
       </c>
       <c r="G4" t="n">
-        <v>510577.5088988312</v>
+        <v>510436.7237234231</v>
       </c>
       <c r="H4" t="n">
-        <v>508888.2451130981</v>
+        <v>508747.6302445563</v>
       </c>
       <c r="I4" t="n">
-        <v>507196.6230877028</v>
+        <v>507056.1787637775</v>
       </c>
       <c r="J4" t="n">
-        <v>505502.6257137285</v>
+        <v>505288.8894845269</v>
       </c>
       <c r="K4" t="n">
-        <v>503806.2356567245</v>
+        <v>503593.3881819232</v>
       </c>
       <c r="L4" t="n">
-        <v>502107.4353523577</v>
+        <v>501895.4778947112</v>
       </c>
       <c r="M4" t="n">
-        <v>506489.4162279235</v>
+        <v>506385.5103073897</v>
       </c>
       <c r="N4" t="n">
-        <v>504723.3213042059</v>
+        <v>504619.6298376815</v>
       </c>
       <c r="O4" t="n">
-        <v>502954.6717247892</v>
+        <v>499837.1975574076</v>
       </c>
       <c r="P4" t="n">
-        <v>501183.4482814742</v>
+        <v>498079.1886758039</v>
       </c>
     </row>
     <row r="5">
@@ -26431,43 +26431,43 @@
         <v>58612.2</v>
       </c>
       <c r="D5" t="n">
-        <v>58612.2</v>
+        <v>58634</v>
       </c>
       <c r="E5" t="n">
-        <v>73949.149</v>
+        <v>74009.94899999999</v>
       </c>
       <c r="F5" t="n">
-        <v>73949.149</v>
+        <v>74009.94899999999</v>
       </c>
       <c r="G5" t="n">
-        <v>73949.149</v>
+        <v>74009.94899999999</v>
       </c>
       <c r="H5" t="n">
-        <v>73949.149</v>
+        <v>74009.94899999999</v>
       </c>
       <c r="I5" t="n">
-        <v>73949.149</v>
+        <v>74009.94899999999</v>
       </c>
       <c r="J5" t="n">
-        <v>73949.149</v>
+        <v>74070.74900000001</v>
       </c>
       <c r="K5" t="n">
-        <v>73949.149</v>
+        <v>74070.74900000001</v>
       </c>
       <c r="L5" t="n">
-        <v>73949.149</v>
+        <v>74070.74900000001</v>
       </c>
       <c r="M5" t="n">
-        <v>70677.20499999999</v>
+        <v>70738.005</v>
       </c>
       <c r="N5" t="n">
-        <v>70677.20499999999</v>
+        <v>70738.005</v>
       </c>
       <c r="O5" t="n">
-        <v>70677.20499999999</v>
+        <v>70317.66</v>
       </c>
       <c r="P5" t="n">
-        <v>70677.20499999999</v>
+        <v>70317.66</v>
       </c>
     </row>
     <row r="6">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>523947.1130121049</v>
+        <v>524146.2045227147</v>
       </c>
       <c r="C6" t="n">
-        <v>758028.4770697114</v>
+        <v>758227.5685803209</v>
       </c>
       <c r="D6" t="n">
-        <v>760039.565598515</v>
+        <v>759463.1053081788</v>
       </c>
       <c r="E6" t="n">
-        <v>237488.2773982798</v>
+        <v>238456.3173723918</v>
       </c>
       <c r="F6" t="n">
-        <v>830320.8751502446</v>
+        <v>830665.745287906</v>
       </c>
       <c r="G6" t="n">
-        <v>832007.7975839023</v>
+        <v>832352.4976507466</v>
       </c>
       <c r="H6" t="n">
-        <v>833697.0613696349</v>
+        <v>834041.5911296133</v>
       </c>
       <c r="I6" t="n">
-        <v>835388.6833950325</v>
+        <v>835733.0426103917</v>
       </c>
       <c r="J6" t="n">
-        <v>448634.6807690054</v>
+        <v>448639.5318896428</v>
       </c>
       <c r="K6" t="n">
-        <v>838779.0708260126</v>
+        <v>839135.033192246</v>
       </c>
       <c r="L6" t="n">
-        <v>840477.8711303757</v>
+        <v>840832.9434794581</v>
       </c>
       <c r="M6" t="n">
-        <v>754197.9035748102</v>
+        <v>754588.5351353432</v>
       </c>
       <c r="N6" t="n">
-        <v>840987.9984985273</v>
+        <v>841378.4156050525</v>
       </c>
       <c r="O6" t="n">
-        <v>585956.6480779448</v>
+        <v>587512.6928853261</v>
       </c>
       <c r="P6" t="n">
-        <v>844527.8715212593</v>
+        <v>842070.7017669298</v>
       </c>
     </row>
   </sheetData>
@@ -26794,10 +26794,10 @@
         <v>345</v>
       </c>
       <c r="O2" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="P2" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
     </row>
     <row r="3">
@@ -26813,7 +26813,7 @@
         <v>103</v>
       </c>
       <c r="D3" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E3" t="n">
         <v>347</v>
@@ -26868,40 +26868,40 @@
         <v>374</v>
       </c>
       <c r="E4" t="n">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="F4" t="n">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="G4" t="n">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H4" t="n">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="I4" t="n">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="J4" t="n">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="K4" t="n">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="L4" t="n">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="M4" t="n">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="N4" t="n">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="O4" t="n">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="P4" t="n">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
   </sheetData>
@@ -26987,7 +26987,7 @@
         <v>-0</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>-0</v>
@@ -27002,16 +27002,16 @@
         <v>-0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M2" t="n">
         <v>24</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O2" t="n">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="P2" t="n">
         <v>-0</v>
@@ -27030,10 +27030,10 @@
         <v>-0</v>
       </c>
       <c r="D3" t="n">
-        <v>-0</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F3" t="n">
         <v>-0</v>
@@ -27085,10 +27085,10 @@
         <v>-0</v>
       </c>
       <c r="E4" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
         <v>-0</v>
@@ -27100,10 +27100,10 @@
         <v>-0</v>
       </c>
       <c r="J4" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="K4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>-0</v>
@@ -27326,7 +27326,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -27451,7 +27451,7 @@
         <v>400</v>
       </c>
       <c r="H2" t="n">
-        <v>398.0465935392074</v>
+        <v>400</v>
       </c>
       <c r="I2" t="n">
         <v>134.1177124465037</v>
@@ -27484,7 +27484,7 @@
         <v>224.8682520946261</v>
       </c>
       <c r="S2" t="n">
-        <v>400</v>
+        <v>398.0465935392085</v>
       </c>
       <c r="T2" t="n">
         <v>400</v>
@@ -27560,16 +27560,16 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>159.5184388018133</v>
+        <v>400</v>
       </c>
       <c r="S3" t="n">
         <v>88.44885845517734</v>
       </c>
       <c r="T3" t="n">
-        <v>122.4833428782075</v>
+        <v>30.46477465147608</v>
       </c>
       <c r="U3" t="n">
-        <v>400</v>
+        <v>251.5370070285445</v>
       </c>
       <c r="V3" t="n">
         <v>400</v>
@@ -27609,19 +27609,19 @@
         <v>400</v>
       </c>
       <c r="H4" t="n">
-        <v>400</v>
+        <v>227.1197490524383</v>
       </c>
       <c r="I4" t="n">
-        <v>400</v>
+        <v>171.047816275856</v>
       </c>
       <c r="J4" t="n">
-        <v>396.1372930982029</v>
+        <v>334.257997890869</v>
       </c>
       <c r="K4" t="n">
         <v>400</v>
       </c>
       <c r="L4" t="n">
-        <v>400</v>
+        <v>395.9334970102382</v>
       </c>
       <c r="M4" t="n">
         <v>400</v>
@@ -27645,19 +27645,19 @@
         <v>400</v>
       </c>
       <c r="T4" t="n">
-        <v>343.8905113068386</v>
+        <v>209.2309599488807</v>
       </c>
       <c r="U4" t="n">
-        <v>150.9482601269169</v>
+        <v>400</v>
       </c>
       <c r="V4" t="n">
-        <v>199.1703102162162</v>
+        <v>400</v>
       </c>
       <c r="W4" t="n">
         <v>226.3728098387097</v>
       </c>
       <c r="X4" t="n">
-        <v>247.4436454301076</v>
+        <v>400</v>
       </c>
       <c r="Y4" t="n">
         <v>287.4653528494624</v>
@@ -27688,10 +27688,10 @@
         <v>400</v>
       </c>
       <c r="H5" t="n">
-        <v>398.0465935392086</v>
+        <v>400</v>
       </c>
       <c r="I5" t="n">
-        <v>134.1177124465037</v>
+        <v>132.1643059857123</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -27749,16 +27749,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36.11842519847028</v>
+        <v>10.55655664632661</v>
       </c>
       <c r="C6" t="n">
         <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
         <v>339.6362423378769</v>
@@ -27815,10 +27815,10 @@
         <v>400</v>
       </c>
       <c r="X6" t="n">
-        <v>400</v>
+        <v>108.9520844325285</v>
       </c>
       <c r="Y6" t="n">
-        <v>399.3913927661343</v>
+        <v>25.39139276613435</v>
       </c>
     </row>
     <row r="7">
@@ -27834,13 +27834,13 @@
         <v>272.7252466480447</v>
       </c>
       <c r="D7" t="n">
-        <v>285.5362180555555</v>
+        <v>400</v>
       </c>
       <c r="E7" t="n">
-        <v>280.9809048369565</v>
+        <v>400</v>
       </c>
       <c r="F7" t="n">
-        <v>343.8905113068386</v>
+        <v>400</v>
       </c>
       <c r="G7" t="n">
         <v>400</v>
@@ -27852,7 +27852,7 @@
         <v>400</v>
       </c>
       <c r="J7" t="n">
-        <v>396.1372930982029</v>
+        <v>338.1773892851616</v>
       </c>
       <c r="K7" t="n">
         <v>400</v>
@@ -27879,10 +27879,10 @@
         <v>400</v>
       </c>
       <c r="S7" t="n">
-        <v>400</v>
+        <v>359.1365780635112</v>
       </c>
       <c r="T7" t="n">
-        <v>400</v>
+        <v>209.2309599488807</v>
       </c>
       <c r="U7" t="n">
         <v>150.9482601269169</v>
@@ -27928,7 +27928,7 @@
         <v>400</v>
       </c>
       <c r="I8" t="n">
-        <v>132.1643059857123</v>
+        <v>133.9627275218806</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -27955,7 +27955,7 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>224.8682520946261</v>
+        <v>222.5075994026788</v>
       </c>
       <c r="S8" t="n">
         <v>400</v>
@@ -27986,28 +27986,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>384.5565566463266</v>
+        <v>10.55655664632661</v>
       </c>
       <c r="C9" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F9" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G9" t="n">
-        <v>325.517988705216</v>
+        <v>325.5158377618198</v>
       </c>
       <c r="H9" t="n">
-        <v>330.0284079411381</v>
+        <v>330.0076343562325</v>
       </c>
       <c r="I9" t="n">
-        <v>209.4985557026693</v>
+        <v>209.4244990988957</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -28031,13 +28031,13 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>144.5243971659513</v>
       </c>
       <c r="R9" t="n">
         <v>400</v>
       </c>
       <c r="S9" t="n">
-        <v>400</v>
+        <v>298.8104937661587</v>
       </c>
       <c r="T9" t="n">
         <v>400</v>
@@ -28046,10 +28046,10 @@
         <v>400</v>
       </c>
       <c r="V9" t="n">
-        <v>40.51066719152016</v>
+        <v>400</v>
       </c>
       <c r="W9" t="n">
-        <v>63.11351446292082</v>
+        <v>400</v>
       </c>
       <c r="X9" t="n">
         <v>400</v>
@@ -28065,37 +28065,37 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>287.1138003370787</v>
+        <v>400</v>
       </c>
       <c r="C10" t="n">
-        <v>272.7252466480447</v>
+        <v>400</v>
       </c>
       <c r="D10" t="n">
-        <v>342.0400961869587</v>
+        <v>400</v>
       </c>
       <c r="E10" t="n">
         <v>400</v>
       </c>
       <c r="F10" t="n">
-        <v>400</v>
+        <v>280.0894497385021</v>
       </c>
       <c r="G10" t="n">
-        <v>400</v>
+        <v>244.8563318579235</v>
       </c>
       <c r="H10" t="n">
-        <v>400</v>
+        <v>227.103716265553</v>
       </c>
       <c r="I10" t="n">
-        <v>400</v>
+        <v>170.9935867676593</v>
       </c>
       <c r="J10" t="n">
-        <v>396.1372930982029</v>
+        <v>22.00980129492416</v>
       </c>
       <c r="K10" t="n">
-        <v>400</v>
+        <v>266.7319213421267</v>
       </c>
       <c r="L10" t="n">
-        <v>400</v>
+        <v>395.6653986495825</v>
       </c>
       <c r="M10" t="n">
         <v>400</v>
@@ -28116,25 +28116,25 @@
         <v>400</v>
       </c>
       <c r="S10" t="n">
-        <v>359.1365780635112</v>
+        <v>359.105151834003</v>
       </c>
       <c r="T10" t="n">
-        <v>209.2309599488807</v>
+        <v>209.2232550308479</v>
       </c>
       <c r="U10" t="n">
-        <v>150.9482601269169</v>
+        <v>400</v>
       </c>
       <c r="V10" t="n">
-        <v>199.1703102162162</v>
+        <v>400</v>
       </c>
       <c r="W10" t="n">
-        <v>226.3728098387097</v>
+        <v>400</v>
       </c>
       <c r="X10" t="n">
-        <v>247.4436454301076</v>
+        <v>400</v>
       </c>
       <c r="Y10" t="n">
-        <v>287.4653528494624</v>
+        <v>400</v>
       </c>
     </row>
     <row r="11">
@@ -28195,7 +28195,7 @@
         <v>163.2515083760331</v>
       </c>
       <c r="S11" t="n">
-        <v>321</v>
+        <v>320.0752568557917</v>
       </c>
       <c r="T11" t="n">
         <v>321</v>
@@ -28223,19 +28223,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="D12" t="n">
-        <v>321</v>
+        <v>137.8407332208563</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
         <v>321</v>
@@ -28286,13 +28286,13 @@
         <v>321</v>
       </c>
       <c r="W12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
         <v>321</v>
       </c>
       <c r="Y12" t="n">
-        <v>137.8407332208564</v>
+        <v>321</v>
       </c>
     </row>
     <row r="13">
@@ -28326,40 +28326,40 @@
         <v>321</v>
       </c>
       <c r="J13" t="n">
+        <v>321</v>
+      </c>
+      <c r="K13" t="n">
+        <v>321</v>
+      </c>
+      <c r="L13" t="n">
+        <v>321</v>
+      </c>
+      <c r="M13" t="n">
+        <v>321</v>
+      </c>
+      <c r="N13" t="n">
+        <v>321</v>
+      </c>
+      <c r="O13" t="n">
+        <v>321</v>
+      </c>
+      <c r="P13" t="n">
+        <v>321</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>321</v>
+      </c>
+      <c r="R13" t="n">
+        <v>321</v>
+      </c>
+      <c r="S13" t="n">
+        <v>321</v>
+      </c>
+      <c r="T13" t="n">
+        <v>321</v>
+      </c>
+      <c r="U13" t="n">
         <v>315.8198010595347</v>
-      </c>
-      <c r="K13" t="n">
-        <v>321</v>
-      </c>
-      <c r="L13" t="n">
-        <v>321</v>
-      </c>
-      <c r="M13" t="n">
-        <v>321</v>
-      </c>
-      <c r="N13" t="n">
-        <v>321</v>
-      </c>
-      <c r="O13" t="n">
-        <v>321</v>
-      </c>
-      <c r="P13" t="n">
-        <v>321</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>321</v>
-      </c>
-      <c r="R13" t="n">
-        <v>321</v>
-      </c>
-      <c r="S13" t="n">
-        <v>321</v>
-      </c>
-      <c r="T13" t="n">
-        <v>321</v>
-      </c>
-      <c r="U13" t="n">
-        <v>321</v>
       </c>
       <c r="V13" t="n">
         <v>321</v>
@@ -28432,7 +28432,7 @@
         <v>163.2515083760331</v>
       </c>
       <c r="S14" t="n">
-        <v>321</v>
+        <v>320.0752568557917</v>
       </c>
       <c r="T14" t="n">
         <v>321</v>
@@ -28460,13 +28460,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="C15" t="n">
         <v>321</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E15" t="n">
         <v>321</v>
@@ -28520,16 +28520,16 @@
         <v>321</v>
       </c>
       <c r="V15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>137.8407332208563</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>321</v>
+        <v>137.8407332208564</v>
       </c>
     </row>
     <row r="16">
@@ -28566,7 +28566,7 @@
         <v>321</v>
       </c>
       <c r="K16" t="n">
-        <v>315.8198010595346</v>
+        <v>321</v>
       </c>
       <c r="L16" t="n">
         <v>321</v>
@@ -28593,7 +28593,7 @@
         <v>321</v>
       </c>
       <c r="T16" t="n">
-        <v>321</v>
+        <v>315.8198010595347</v>
       </c>
       <c r="U16" t="n">
         <v>321</v>
@@ -28666,7 +28666,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>163.2515083760331</v>
+        <v>162.3267652318248</v>
       </c>
       <c r="S17" t="n">
         <v>321</v>
@@ -28700,7 +28700,7 @@
         <v>321</v>
       </c>
       <c r="C18" t="n">
-        <v>137.8407332208562</v>
+        <v>137.8407332208564</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -28785,7 +28785,7 @@
         <v>321</v>
       </c>
       <c r="E19" t="n">
-        <v>321</v>
+        <v>315.8198010595347</v>
       </c>
       <c r="F19" t="n">
         <v>321</v>
@@ -28833,7 +28833,7 @@
         <v>321</v>
       </c>
       <c r="U19" t="n">
-        <v>315.8198010595348</v>
+        <v>321</v>
       </c>
       <c r="V19" t="n">
         <v>321</v>
@@ -28906,7 +28906,7 @@
         <v>163.2515083760331</v>
       </c>
       <c r="S20" t="n">
-        <v>321</v>
+        <v>320.0752568557917</v>
       </c>
       <c r="T20" t="n">
         <v>321</v>
@@ -28934,19 +28934,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>137.8407332208564</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>137.8407332208564</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
         <v>321</v>
@@ -29019,7 +29019,7 @@
         <v>321</v>
       </c>
       <c r="D22" t="n">
-        <v>321</v>
+        <v>315.8198010595347</v>
       </c>
       <c r="E22" t="n">
         <v>321</v>
@@ -29067,7 +29067,7 @@
         <v>321</v>
       </c>
       <c r="T22" t="n">
-        <v>315.8198010595348</v>
+        <v>321</v>
       </c>
       <c r="U22" t="n">
         <v>321</v>
@@ -29140,10 +29140,10 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>163.2515083760557</v>
+        <v>163.2515083760331</v>
       </c>
       <c r="S23" t="n">
-        <v>321</v>
+        <v>320.0752568557917</v>
       </c>
       <c r="T23" t="n">
         <v>321</v>
@@ -29171,19 +29171,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>321</v>
+        <v>137.8407332208564</v>
       </c>
       <c r="C24" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
         <v>321</v>
       </c>
       <c r="E24" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
         <v>321</v>
@@ -29231,16 +29231,16 @@
         <v>321</v>
       </c>
       <c r="V24" t="n">
-        <v>137.8407332208562</v>
+        <v>321</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
     </row>
     <row r="25">
@@ -29304,10 +29304,10 @@
         <v>321</v>
       </c>
       <c r="T25" t="n">
-        <v>321</v>
+        <v>315.8198010595347</v>
       </c>
       <c r="U25" t="n">
-        <v>315.8198010595348</v>
+        <v>321</v>
       </c>
       <c r="V25" t="n">
         <v>321</v>
@@ -29350,7 +29350,7 @@
         <v>321</v>
       </c>
       <c r="I26" t="n">
-        <v>96.3013908384635</v>
+        <v>91.49584769425513</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -29408,7 +29408,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>137.8407332208564</v>
+        <v>321</v>
       </c>
       <c r="C27" t="n">
         <v>0</v>
@@ -29417,13 +29417,13 @@
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F27" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>321</v>
+        <v>137.8407332208565</v>
       </c>
       <c r="H27" t="n">
         <v>321</v>
@@ -29541,7 +29541,7 @@
         <v>321</v>
       </c>
       <c r="T28" t="n">
-        <v>321</v>
+        <v>315.8198010595347</v>
       </c>
       <c r="U28" t="n">
         <v>321</v>
@@ -29556,7 +29556,7 @@
         <v>321</v>
       </c>
       <c r="Y28" t="n">
-        <v>315.8198010595348</v>
+        <v>321</v>
       </c>
     </row>
     <row r="29">
@@ -29587,7 +29587,7 @@
         <v>321</v>
       </c>
       <c r="I29" t="n">
-        <v>96.3013908384635</v>
+        <v>91.49584769425496</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -29614,7 +29614,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>163.2515083760741</v>
+        <v>163.2515083760331</v>
       </c>
       <c r="S29" t="n">
         <v>321</v>
@@ -29705,7 +29705,7 @@
         <v>321</v>
       </c>
       <c r="V30" t="n">
-        <v>137.8407332208562</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
         <v>0</v>
@@ -29714,7 +29714,7 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>137.8407332208565</v>
       </c>
     </row>
     <row r="31">
@@ -29778,7 +29778,7 @@
         <v>321</v>
       </c>
       <c r="T31" t="n">
-        <v>315.8198010595348</v>
+        <v>315.8198010595347</v>
       </c>
       <c r="U31" t="n">
         <v>321</v>
@@ -29821,7 +29821,7 @@
         <v>321</v>
       </c>
       <c r="H32" t="n">
-        <v>321</v>
+        <v>316.1944568557916</v>
       </c>
       <c r="I32" t="n">
         <v>96.3013908384635</v>
@@ -29882,10 +29882,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>215.6455832169962</v>
+        <v>321</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="D33" t="n">
         <v>321</v>
@@ -29894,7 +29894,7 @@
         <v>321</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G33" t="n">
         <v>321</v>
@@ -29927,7 +29927,7 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>77.80484999613995</v>
       </c>
       <c r="R33" t="n">
         <v>321</v>
@@ -29942,16 +29942,16 @@
         <v>321</v>
       </c>
       <c r="V33" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>321</v>
+        <v>137.8407332208565</v>
       </c>
     </row>
     <row r="34">
@@ -29967,7 +29967,7 @@
         <v>321</v>
       </c>
       <c r="D34" t="n">
-        <v>321</v>
+        <v>315.8198010595347</v>
       </c>
       <c r="E34" t="n">
         <v>321</v>
@@ -30015,7 +30015,7 @@
         <v>321</v>
       </c>
       <c r="T34" t="n">
-        <v>315.8198010595348</v>
+        <v>321</v>
       </c>
       <c r="U34" t="n">
         <v>321</v>
@@ -30119,22 +30119,22 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="C36" t="n">
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>324.2172979697546</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>324.9931585165368</v>
       </c>
       <c r="H36" t="n">
         <v>324.959653224157</v>
@@ -30164,10 +30164,10 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>77.80484999613995</v>
       </c>
       <c r="R36" t="n">
-        <v>345</v>
+        <v>258.8879214801627</v>
       </c>
       <c r="S36" t="n">
         <v>345</v>
@@ -30198,19 +30198,19 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>287.1138003370787</v>
+        <v>345</v>
       </c>
       <c r="C37" t="n">
-        <v>272.7252466480447</v>
+        <v>345</v>
       </c>
       <c r="D37" t="n">
-        <v>285.5362180555555</v>
+        <v>345</v>
       </c>
       <c r="E37" t="n">
         <v>345</v>
       </c>
       <c r="F37" t="n">
-        <v>274.3828559677419</v>
+        <v>345</v>
       </c>
       <c r="G37" t="n">
         <v>345</v>
@@ -30219,16 +30219,16 @@
         <v>345</v>
       </c>
       <c r="I37" t="n">
-        <v>157.815816275856</v>
+        <v>345</v>
       </c>
       <c r="J37" t="n">
-        <v>279.6586896726191</v>
+        <v>345</v>
       </c>
       <c r="K37" t="n">
         <v>345</v>
       </c>
       <c r="L37" t="n">
-        <v>330.5174970102382</v>
+        <v>345</v>
       </c>
       <c r="M37" t="n">
         <v>345</v>
@@ -30252,22 +30252,22 @@
         <v>345</v>
       </c>
       <c r="T37" t="n">
-        <v>345</v>
+        <v>207.3509599488807</v>
       </c>
       <c r="U37" t="n">
-        <v>345</v>
+        <v>150.9242601269169</v>
       </c>
       <c r="V37" t="n">
-        <v>345</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W37" t="n">
-        <v>345</v>
+        <v>237.7699465245827</v>
       </c>
       <c r="X37" t="n">
         <v>345</v>
       </c>
       <c r="Y37" t="n">
-        <v>287.4653528494624</v>
+        <v>345</v>
       </c>
     </row>
     <row r="38">
@@ -30359,16 +30359,16 @@
         <v>345</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G39" t="n">
         <v>324.9931585165368</v>
@@ -30377,7 +30377,7 @@
         <v>324.959653224157</v>
       </c>
       <c r="I39" t="n">
-        <v>107.4842761768697</v>
+        <v>113.008326302288</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -30413,16 +30413,16 @@
         <v>345</v>
       </c>
       <c r="U39" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
         <v>345</v>
@@ -30435,16 +30435,16 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>345</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C40" t="n">
-        <v>345</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D40" t="n">
-        <v>345</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E40" t="n">
-        <v>345</v>
+        <v>280.9809048369565</v>
       </c>
       <c r="F40" t="n">
         <v>345</v>
@@ -30456,16 +30456,16 @@
         <v>345</v>
       </c>
       <c r="I40" t="n">
-        <v>248.8765502675103</v>
+        <v>345</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="K40" t="n">
-        <v>215.821429538848</v>
+        <v>345</v>
       </c>
       <c r="L40" t="n">
-        <v>330.5174970102382</v>
+        <v>345</v>
       </c>
       <c r="M40" t="n">
         <v>345</v>
@@ -30489,22 +30489,22 @@
         <v>345</v>
       </c>
       <c r="T40" t="n">
-        <v>345</v>
+        <v>207.3509599488807</v>
       </c>
       <c r="U40" t="n">
         <v>345</v>
       </c>
       <c r="V40" t="n">
-        <v>345</v>
+        <v>306.5993487105105</v>
       </c>
       <c r="W40" t="n">
         <v>345</v>
       </c>
       <c r="X40" t="n">
-        <v>345</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y40" t="n">
-        <v>345</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="41">
@@ -30514,25 +30514,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="C41" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="D41" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="E41" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="F41" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="G41" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="H41" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="I41" t="n">
         <v>96.3013908384635</v>
@@ -30565,25 +30565,25 @@
         <v>163.2515083760331</v>
       </c>
       <c r="S41" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="T41" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="U41" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="V41" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="W41" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="X41" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="Y41" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
     </row>
     <row r="42">
@@ -30593,28 +30593,28 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="C42" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
         <v>324.9931585165368</v>
       </c>
       <c r="H42" t="n">
-        <v>324.959653224157</v>
+        <v>283.8475747043197</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>191.4287443819146</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -30641,28 +30641,28 @@
         <v>77.80484999613995</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>340</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>340</v>
       </c>
       <c r="T42" t="n">
-        <v>115.175936617087</v>
+        <v>340</v>
       </c>
       <c r="U42" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="V42" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="W42" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="X42" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="Y42" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
     </row>
     <row r="43">
@@ -30672,76 +30672,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>287.1138003370787</v>
+        <v>317.0340963004313</v>
       </c>
       <c r="C43" t="n">
-        <v>272.7252466480447</v>
+        <v>340</v>
       </c>
       <c r="D43" t="n">
-        <v>285.5362180555555</v>
+        <v>340</v>
       </c>
       <c r="E43" t="n">
-        <v>280.9809048369565</v>
+        <v>340</v>
       </c>
       <c r="F43" t="n">
-        <v>274.3828559677419</v>
+        <v>340</v>
       </c>
       <c r="G43" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="H43" t="n">
-        <v>345</v>
+        <v>223.2077490524383</v>
       </c>
       <c r="I43" t="n">
         <v>157.815816275856</v>
       </c>
       <c r="J43" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="K43" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="L43" t="n">
-        <v>345</v>
+        <v>330.5174970102382</v>
       </c>
       <c r="M43" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="N43" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="O43" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="P43" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="Q43" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="R43" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="S43" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="T43" t="n">
-        <v>345</v>
+        <v>207.3509599488807</v>
       </c>
       <c r="U43" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="V43" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="W43" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="X43" t="n">
-        <v>329.1952818459008</v>
+        <v>340</v>
       </c>
       <c r="Y43" t="n">
-        <v>287.4653528494624</v>
+        <v>340</v>
       </c>
     </row>
     <row r="44">
@@ -30751,25 +30751,25 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="C44" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="D44" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="E44" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="F44" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="G44" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="H44" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="I44" t="n">
         <v>96.3013908384635</v>
@@ -30802,25 +30802,25 @@
         <v>163.2515083760331</v>
       </c>
       <c r="S44" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="T44" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="U44" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="V44" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="W44" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="X44" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="Y44" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
     </row>
     <row r="45">
@@ -30830,7 +30830,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="C45" t="n">
         <v>0</v>
@@ -30839,16 +30839,16 @@
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>342.6720972219126</v>
+        <v>340</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>324.9931585165368</v>
       </c>
       <c r="H45" t="n">
-        <v>223.3362463137362</v>
+        <v>324.959653224157</v>
       </c>
       <c r="I45" t="n">
         <v>191.4287443819146</v>
@@ -30878,28 +30878,28 @@
         <v>77.80484999613995</v>
       </c>
       <c r="R45" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="S45" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="T45" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="U45" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="V45" t="n">
-        <v>345</v>
+        <v>298.8879214801627</v>
       </c>
       <c r="W45" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="X45" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
     </row>
     <row r="46">
@@ -30909,76 +30909,76 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="C46" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="D46" t="n">
-        <v>285.5362180555555</v>
+        <v>340</v>
       </c>
       <c r="E46" t="n">
-        <v>280.9809048369565</v>
+        <v>340</v>
       </c>
       <c r="F46" t="n">
-        <v>274.3828559677419</v>
+        <v>340</v>
       </c>
       <c r="G46" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="H46" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="I46" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>340</v>
       </c>
       <c r="K46" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="L46" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="M46" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="N46" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="O46" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="P46" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="Q46" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="R46" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="S46" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="T46" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="U46" t="n">
-        <v>345</v>
+        <v>150.9242601269169</v>
       </c>
       <c r="V46" t="n">
-        <v>345</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W46" t="n">
-        <v>299.3154979563426</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X46" t="n">
-        <v>345</v>
+        <v>319.4587384060015</v>
       </c>
       <c r="Y46" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
     </row>
   </sheetData>
@@ -31565,49 +31565,49 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4140703517587936</v>
+        <v>0.4180904522613062</v>
       </c>
       <c r="H8" t="n">
-        <v>4.240597989949746</v>
+        <v>4.281768844221103</v>
       </c>
       <c r="I8" t="n">
-        <v>15.96344723618091</v>
+        <v>16.11843216080402</v>
       </c>
       <c r="J8" t="n">
-        <v>35.14370351758794</v>
+        <v>35.48490452261307</v>
       </c>
       <c r="K8" t="n">
-        <v>52.67130150753769</v>
+        <v>53.18267336683417</v>
       </c>
       <c r="L8" t="n">
-        <v>65.34340703517589</v>
+        <v>65.97780904522614</v>
       </c>
       <c r="M8" t="n">
-        <v>72.70713065326633</v>
+        <v>73.41302512562814</v>
       </c>
       <c r="N8" t="n">
-        <v>73.88360804020101</v>
+        <v>74.60092462311559</v>
       </c>
       <c r="O8" t="n">
-        <v>69.76619597989949</v>
+        <v>70.44353768844221</v>
       </c>
       <c r="P8" t="n">
-        <v>59.54383417085427</v>
+        <v>60.12192964824121</v>
       </c>
       <c r="Q8" t="n">
-        <v>44.71493969849246</v>
+        <v>45.14906532663316</v>
       </c>
       <c r="R8" t="n">
-        <v>26.01034673366835</v>
+        <v>26.2628743718593</v>
       </c>
       <c r="S8" t="n">
-        <v>9.435628140703519</v>
+        <v>9.527236180904525</v>
       </c>
       <c r="T8" t="n">
-        <v>1.81259296482412</v>
+        <v>1.830190954773869</v>
       </c>
       <c r="U8" t="n">
-        <v>0.03312562814070349</v>
+        <v>0.03344723618090449</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -31644,49 +31644,49 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2215471698113208</v>
+        <v>0.2236981132075472</v>
       </c>
       <c r="H9" t="n">
-        <v>2.139679245283019</v>
+        <v>2.16045283018868</v>
       </c>
       <c r="I9" t="n">
-        <v>7.627830188679247</v>
+        <v>7.701886792452831</v>
       </c>
       <c r="J9" t="n">
-        <v>20.93134905660378</v>
+        <v>21.13456603773585</v>
       </c>
       <c r="K9" t="n">
-        <v>35.77500943396227</v>
+        <v>36.12233962264151</v>
       </c>
       <c r="L9" t="n">
-        <v>48.10391509433963</v>
+        <v>48.57094339622642</v>
       </c>
       <c r="M9" t="n">
-        <v>56.13499999999999</v>
+        <v>56.67999999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>57.62072641509435</v>
+        <v>58.18015094339623</v>
       </c>
       <c r="O9" t="n">
-        <v>52.71170754716981</v>
+        <v>53.22347169811321</v>
       </c>
       <c r="P9" t="n">
-        <v>42.3057924528302</v>
+        <v>42.7165283018868</v>
       </c>
       <c r="Q9" t="n">
-        <v>28.28030188679246</v>
+        <v>28.55486792452831</v>
       </c>
       <c r="R9" t="n">
-        <v>13.75535849056604</v>
+        <v>13.88890566037736</v>
       </c>
       <c r="S9" t="n">
-        <v>4.115141509433959</v>
+        <v>4.155094339622639</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8929905660377355</v>
+        <v>0.9016603773584903</v>
       </c>
       <c r="U9" t="n">
-        <v>0.01457547169811321</v>
+        <v>0.01471698113207548</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -31723,49 +31723,49 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1857377049180328</v>
+        <v>0.1875409836065574</v>
       </c>
       <c r="H10" t="n">
-        <v>1.651377049180329</v>
+        <v>1.667409836065575</v>
       </c>
       <c r="I10" t="n">
-        <v>5.585639344262296</v>
+        <v>5.639868852459018</v>
       </c>
       <c r="J10" t="n">
-        <v>13.13165573770492</v>
+        <v>13.25914754098361</v>
       </c>
       <c r="K10" t="n">
-        <v>21.57934426229507</v>
+        <v>21.78885245901639</v>
       </c>
       <c r="L10" t="n">
-        <v>27.61413114754098</v>
+        <v>27.88222950819672</v>
       </c>
       <c r="M10" t="n">
-        <v>29.11522950819672</v>
+        <v>29.39790163934425</v>
       </c>
       <c r="N10" t="n">
-        <v>28.42293442622952</v>
+        <v>28.69888524590166</v>
       </c>
       <c r="O10" t="n">
-        <v>26.25318032786886</v>
+        <v>26.5080655737705</v>
       </c>
       <c r="P10" t="n">
-        <v>22.46413114754097</v>
+        <v>22.68222950819671</v>
       </c>
       <c r="Q10" t="n">
-        <v>15.553</v>
+        <v>15.704</v>
       </c>
       <c r="R10" t="n">
-        <v>8.351442622950817</v>
+        <v>8.432524590163931</v>
       </c>
       <c r="S10" t="n">
-        <v>3.236901639344261</v>
+        <v>3.268327868852458</v>
       </c>
       <c r="T10" t="n">
-        <v>0.7936065573770489</v>
+        <v>0.8013114754098358</v>
       </c>
       <c r="U10" t="n">
-        <v>0.01013114754098362</v>
+        <v>0.01022950819672132</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -34746,10 +34746,10 @@
         <v>0.1006972724976123</v>
       </c>
       <c r="K2" t="n">
-        <v>374</v>
+        <v>52.67130150753769</v>
       </c>
       <c r="L2" t="n">
-        <v>299.5314174862184</v>
+        <v>306.1168901088536</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -34758,13 +34758,13 @@
         <v>374</v>
       </c>
       <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
         <v>374</v>
       </c>
-      <c r="P2" t="n">
-        <v>59.25677413017286</v>
-      </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -34895,19 +34895,19 @@
         <v>155.141864863388</v>
       </c>
       <c r="H4" t="n">
-        <v>172.8802509475617</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>228.952183724144</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>374</v>
+        <v>312.1207047926661</v>
       </c>
       <c r="K4" t="n">
         <v>133.058570461152</v>
       </c>
       <c r="L4" t="n">
-        <v>4.06650298976183</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -34931,19 +34931,19 @@
         <v>40.86342193648881</v>
       </c>
       <c r="T4" t="n">
-        <v>134.6595513579579</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>249.0517398730831</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>200.8296897837838</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
@@ -34995,13 +34995,13 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="P5" t="n">
         <v>59.25677413017286</v>
       </c>
       <c r="Q5" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -35120,13 +35120,13 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>119.0190951630435</v>
       </c>
       <c r="F7" t="n">
-        <v>69.50765533909659</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G7" t="n">
         <v>155.141864863388</v>
@@ -35138,7 +35138,7 @@
         <v>228.952183724144</v>
       </c>
       <c r="J7" t="n">
-        <v>374</v>
+        <v>316.0400961869587</v>
       </c>
       <c r="K7" t="n">
         <v>133.058570461152</v>
@@ -35165,10 +35165,10 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>40.86342193648881</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>190.7690400511193</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -35217,7 +35217,7 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1006972724976123</v>
+        <v>0.4418982775227391</v>
       </c>
       <c r="K8" t="n">
         <v>374</v>
@@ -35226,16 +35226,16 @@
         <v>374</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>298.4164528894565</v>
       </c>
       <c r="N8" t="n">
-        <v>299.5314174862184</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>0.1956681143497576</v>
       </c>
       <c r="P8" t="n">
-        <v>59.25677413017286</v>
+        <v>59.8348696075598</v>
       </c>
       <c r="Q8" t="n">
         <v>374</v>
@@ -35296,25 +35296,25 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>146.1399552942795</v>
+        <v>146.3431722754116</v>
       </c>
       <c r="K9" t="n">
-        <v>226.8788640747536</v>
+        <v>227.2261942634328</v>
       </c>
       <c r="L9" t="n">
-        <v>322.1952904430266</v>
+        <v>322.6623187449134</v>
       </c>
       <c r="M9" t="n">
-        <v>143.0850421645043</v>
+        <v>143.6300421645043</v>
       </c>
       <c r="N9" t="n">
-        <v>192.2472765237492</v>
+        <v>192.8067010520511</v>
       </c>
       <c r="O9" t="n">
-        <v>294.1687294499162</v>
+        <v>294.6804936008596</v>
       </c>
       <c r="P9" t="n">
-        <v>155.9717969674834</v>
+        <v>153.5399667877162</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -35351,37 +35351,37 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>127.2747533519553</v>
       </c>
       <c r="D10" t="n">
-        <v>56.50387813140321</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E10" t="n">
         <v>119.0190951630435</v>
       </c>
       <c r="F10" t="n">
-        <v>125.6171440322581</v>
+        <v>5.706593770760218</v>
       </c>
       <c r="G10" t="n">
-        <v>155.141864863388</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>172.8802509475617</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>228.952183724144</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>133.058570461152</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>4.06650298976183</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -35408,19 +35408,19 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>249.0518382337388</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>200.8296897837838</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="11">
@@ -35457,16 +35457,16 @@
         <v>513.658479084785</v>
       </c>
       <c r="K11" t="n">
-        <v>177.4460351758794</v>
+        <v>649</v>
       </c>
       <c r="L11" t="n">
-        <v>267.9409117477892</v>
+        <v>649</v>
       </c>
       <c r="M11" t="n">
-        <v>648.0000000000019</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>393.0175247901786</v>
       </c>
       <c r="O11" t="n">
         <v>164.7897032902292</v>
@@ -35475,7 +35475,7 @@
         <v>200.3120706125849</v>
       </c>
       <c r="Q11" t="n">
-        <v>593.6709819069124</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -35612,7 +35612,7 @@
         <v>163.184183724144</v>
       </c>
       <c r="J13" t="n">
-        <v>324.7905079613318</v>
+        <v>329.9707069017971</v>
       </c>
       <c r="K13" t="n">
         <v>105.178570461152</v>
@@ -35645,7 +35645,7 @@
         <v>113.6490400511193</v>
       </c>
       <c r="U13" t="n">
-        <v>170.0757398730831</v>
+        <v>164.8955409326178</v>
       </c>
       <c r="V13" t="n">
         <v>121.8296897837838</v>
@@ -35691,10 +35691,10 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>83.35374249862829</v>
+        <v>280.5232632075488</v>
       </c>
       <c r="K14" t="n">
-        <v>372.6559599251984</v>
+        <v>177.4460351758794</v>
       </c>
       <c r="L14" t="n">
         <v>220.1374974874372</v>
@@ -35706,10 +35706,10 @@
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>648.0000000000028</v>
+        <v>649</v>
       </c>
       <c r="P14" t="n">
-        <v>648.0000000000028</v>
+        <v>649</v>
       </c>
       <c r="Q14" t="n">
         <v>593.6709819069124</v>
@@ -35852,7 +35852,7 @@
         <v>329.9707069017971</v>
       </c>
       <c r="K16" t="n">
-        <v>99.99837152068662</v>
+        <v>105.178570461152</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -35879,7 +35879,7 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>113.6490400511193</v>
+        <v>108.4688411106541</v>
       </c>
       <c r="U16" t="n">
         <v>170.0757398730831</v>
@@ -35928,19 +35928,19 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>513.658479084785</v>
+        <v>83.35374249862829</v>
       </c>
       <c r="K17" t="n">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="L17" t="n">
-        <v>445.3869469236706</v>
+        <v>649</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>649</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>174.322261376335</v>
       </c>
       <c r="O17" t="n">
         <v>164.7897032902292</v>
@@ -35949,7 +35949,7 @@
         <v>200.3120706125849</v>
       </c>
       <c r="Q17" t="n">
-        <v>593.6709819069124</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -36071,7 +36071,7 @@
         <v>35.46378194444452</v>
       </c>
       <c r="E19" t="n">
-        <v>40.01909516304346</v>
+        <v>34.83889622257817</v>
       </c>
       <c r="F19" t="n">
         <v>46.61714403225807</v>
@@ -36119,7 +36119,7 @@
         <v>113.6490400511193</v>
       </c>
       <c r="U19" t="n">
-        <v>164.8955409326179</v>
+        <v>170.0757398730831</v>
       </c>
       <c r="V19" t="n">
         <v>121.8296897837838</v>
@@ -36168,16 +36168,16 @@
         <v>513.658479084785</v>
       </c>
       <c r="K20" t="n">
-        <v>648</v>
+        <v>177.4460351758794</v>
       </c>
       <c r="L20" t="n">
-        <v>445.3869469236706</v>
+        <v>220.1374974874373</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>649</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>644.4339921268619</v>
       </c>
       <c r="O20" t="n">
         <v>164.7897032902292</v>
@@ -36186,7 +36186,7 @@
         <v>200.3120706125849</v>
       </c>
       <c r="Q20" t="n">
-        <v>593.6709819069124</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -36305,7 +36305,7 @@
         <v>48.27475335195533</v>
       </c>
       <c r="D22" t="n">
-        <v>35.46378194444452</v>
+        <v>30.28358300397924</v>
       </c>
       <c r="E22" t="n">
         <v>40.01909516304346</v>
@@ -36353,7 +36353,7 @@
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>108.4688411106541</v>
+        <v>113.6490400511193</v>
       </c>
       <c r="U22" t="n">
         <v>170.0757398730831</v>
@@ -36402,19 +36402,19 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>513.658479084785</v>
+        <v>83.35374249862829</v>
       </c>
       <c r="K23" t="n">
-        <v>648</v>
+        <v>177.4460351758794</v>
       </c>
       <c r="L23" t="n">
-        <v>648</v>
+        <v>220.1374974874373</v>
       </c>
       <c r="M23" t="n">
-        <v>391.0579288305826</v>
+        <v>649</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>649</v>
       </c>
       <c r="O23" t="n">
         <v>164.7897032902292</v>
@@ -36423,10 +36423,10 @@
         <v>200.3120706125849</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>425.738728713019</v>
       </c>
       <c r="R23" t="n">
-        <v>2.250769716508762e-11</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -36590,10 +36590,10 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>113.6490400511193</v>
+        <v>108.4688411106541</v>
       </c>
       <c r="U25" t="n">
-        <v>164.8955409326179</v>
+        <v>170.0757398730831</v>
       </c>
       <c r="V25" t="n">
         <v>121.8296897837838</v>
@@ -36639,19 +36639,19 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>83.35374249862829</v>
+        <v>513.658479084785</v>
       </c>
       <c r="K26" t="n">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="L26" t="n">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="M26" t="n">
-        <v>648.0000000000028</v>
+        <v>394.9771207497746</v>
       </c>
       <c r="N26" t="n">
-        <v>173.3626654167364</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>164.7897032902292</v>
@@ -36827,7 +36827,7 @@
         <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>113.6490400511193</v>
+        <v>108.468841110654</v>
       </c>
       <c r="U28" t="n">
         <v>170.0757398730831</v>
@@ -36842,7 +36842,7 @@
         <v>73.55635456989245</v>
       </c>
       <c r="Y28" t="n">
-        <v>28.35444821007238</v>
+        <v>33.53464715053764</v>
       </c>
     </row>
     <row r="29">
@@ -36879,16 +36879,16 @@
         <v>83.35374249862829</v>
       </c>
       <c r="K29" t="n">
-        <v>648</v>
+        <v>177.4460351758794</v>
       </c>
       <c r="L29" t="n">
-        <v>648</v>
+        <v>220.1374974874373</v>
       </c>
       <c r="M29" t="n">
-        <v>173.3626654167357</v>
+        <v>484.0273427657024</v>
       </c>
       <c r="N29" t="n">
-        <v>648.0000000000038</v>
+        <v>650</v>
       </c>
       <c r="O29" t="n">
         <v>164.7897032902292</v>
@@ -36897,10 +36897,10 @@
         <v>200.3120706125849</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>593.6709819069124</v>
       </c>
       <c r="R29" t="n">
-        <v>4.088132750393465e-11</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -37064,7 +37064,7 @@
         <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>108.4688411106541</v>
+        <v>108.468841110654</v>
       </c>
       <c r="U31" t="n">
         <v>170.0757398730831</v>
@@ -37116,16 +37116,16 @@
         <v>83.35374249862829</v>
       </c>
       <c r="K32" t="n">
-        <v>648</v>
+        <v>231.6108754290191</v>
       </c>
       <c r="L32" t="n">
-        <v>227.6916835098239</v>
+        <v>650</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>650</v>
       </c>
       <c r="N32" t="n">
-        <v>648.0000000000033</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>164.7897032902292</v>
@@ -37253,7 +37253,7 @@
         <v>48.27475335195533</v>
       </c>
       <c r="D34" t="n">
-        <v>35.46378194444452</v>
+        <v>30.28358300397924</v>
       </c>
       <c r="E34" t="n">
         <v>40.01909516304346</v>
@@ -37301,7 +37301,7 @@
         <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>108.4688411106541</v>
+        <v>113.6490400511193</v>
       </c>
       <c r="U34" t="n">
         <v>170.0757398730831</v>
@@ -37353,19 +37353,19 @@
         <v>83.35374249862829</v>
       </c>
       <c r="K35" t="n">
-        <v>561</v>
+        <v>177.4460351758794</v>
       </c>
       <c r="L35" t="n">
-        <v>561</v>
+        <v>220.1374974874372</v>
       </c>
       <c r="M35" t="n">
-        <v>89.87781693189082</v>
+        <v>420.0435835183994</v>
       </c>
       <c r="N35" t="n">
-        <v>561.0000000000001</v>
+        <v>562</v>
       </c>
       <c r="O35" t="n">
-        <v>164.7897032902292</v>
+        <v>562</v>
       </c>
       <c r="P35" t="n">
         <v>200.3120706125849</v>
@@ -37429,7 +37429,7 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>193.5132771061857</v>
+        <v>195.7248986905059</v>
       </c>
       <c r="K36" t="n">
         <v>311.6274301124894</v>
@@ -37484,19 +37484,19 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0</v>
+        <v>57.88619966292134</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>72.27475335195533</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>59.46378194444452</v>
       </c>
       <c r="E37" t="n">
         <v>64.01909516304346</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>70.61714403225807</v>
       </c>
       <c r="G37" t="n">
         <v>100.581864863388</v>
@@ -37505,16 +37505,16 @@
         <v>121.7922509475617</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>187.184183724144</v>
       </c>
       <c r="J37" t="n">
-        <v>288.6293965744163</v>
+        <v>353.9707069017971</v>
       </c>
       <c r="K37" t="n">
         <v>129.178570461152</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>14.48250298976181</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -37538,22 +37538,22 @@
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>137.6490400511193</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>194.0757398730831</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>145.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>118.6271901612903</v>
+        <v>11.397136685873</v>
       </c>
       <c r="X37" t="n">
         <v>97.55635456989245</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>57.53464715053764</v>
       </c>
     </row>
     <row r="38">
@@ -37587,19 +37587,19 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>83.35374249862829</v>
+        <v>513.658479084785</v>
       </c>
       <c r="K38" t="n">
-        <v>561</v>
+        <v>177.4460351758794</v>
       </c>
       <c r="L38" t="n">
-        <v>561</v>
+        <v>220.1374974874373</v>
       </c>
       <c r="M38" t="n">
-        <v>561.0000000000038</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>89.87781693188715</v>
+        <v>386.9491436420136</v>
       </c>
       <c r="O38" t="n">
         <v>164.7897032902292</v>
@@ -37608,7 +37608,7 @@
         <v>200.3120706125849</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>562</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -37666,7 +37666,7 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>193.5132771061857</v>
+        <v>195.7248986905059</v>
       </c>
       <c r="K39" t="n">
         <v>311.6274301124894</v>
@@ -37721,16 +37721,16 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>57.88619966292134</v>
+        <v>0</v>
       </c>
       <c r="C40" t="n">
-        <v>72.27475335195533</v>
+        <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>59.46378194444452</v>
+        <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>64.01909516304346</v>
+        <v>0</v>
       </c>
       <c r="F40" t="n">
         <v>70.61714403225807</v>
@@ -37742,16 +37742,16 @@
         <v>121.7922509475617</v>
       </c>
       <c r="I40" t="n">
-        <v>91.0607339916543</v>
+        <v>187.184183724144</v>
       </c>
       <c r="J40" t="n">
-        <v>8.970706901797143</v>
+        <v>353.9707069017971</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>129.178570461152</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>14.48250298976183</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
@@ -37775,22 +37775,22 @@
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>137.6490400511193</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
         <v>194.0757398730831</v>
       </c>
       <c r="V40" t="n">
-        <v>145.8296897837838</v>
+        <v>107.4290384942943</v>
       </c>
       <c r="W40" t="n">
         <v>118.6271901612903</v>
       </c>
       <c r="X40" t="n">
-        <v>97.55635456989245</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>57.53464715053764</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -37827,16 +37827,16 @@
         <v>83.35374249862829</v>
       </c>
       <c r="K41" t="n">
-        <v>177.4460351758794</v>
+        <v>432.6999154040499</v>
       </c>
       <c r="L41" t="n">
-        <v>220.1374974874373</v>
+        <v>220.1374974874371</v>
       </c>
       <c r="M41" t="n">
-        <v>253.2942842685705</v>
+        <v>562</v>
       </c>
       <c r="N41" t="n">
-        <v>561.0000000000019</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>164.7897032902292</v>
@@ -37845,7 +37845,7 @@
         <v>200.3120706125849</v>
       </c>
       <c r="Q41" t="n">
-        <v>561.0000000000019</v>
+        <v>562</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -37903,7 +37903,7 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>193.5132771061783</v>
+        <v>195.7248986905059</v>
       </c>
       <c r="K42" t="n">
         <v>311.6274301124894</v>
@@ -37958,37 +37958,37 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0</v>
+        <v>29.92029596335265</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>67.27475335195533</v>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>54.46378194444452</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>59.01909516304346</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>65.61714403225807</v>
       </c>
       <c r="G43" t="n">
-        <v>100.581864863388</v>
+        <v>95.58186486338801</v>
       </c>
       <c r="H43" t="n">
-        <v>121.7922509475617</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>353.9707069017971</v>
+        <v>348.9707069017971</v>
       </c>
       <c r="K43" t="n">
-        <v>129.178570461152</v>
+        <v>124.178570461152</v>
       </c>
       <c r="L43" t="n">
-        <v>14.48250298976183</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
@@ -38012,22 +38012,22 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>137.6490400511193</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>194.0757398730831</v>
+        <v>189.0757398730831</v>
       </c>
       <c r="V43" t="n">
-        <v>145.8296897837838</v>
+        <v>140.8296897837838</v>
       </c>
       <c r="W43" t="n">
-        <v>118.6271901612903</v>
+        <v>113.6271901612903</v>
       </c>
       <c r="X43" t="n">
-        <v>81.75163641579326</v>
+        <v>92.55635456989245</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>52.53464715053764</v>
       </c>
     </row>
     <row r="44">
@@ -38064,16 +38064,16 @@
         <v>83.35374249862829</v>
       </c>
       <c r="K44" t="n">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="L44" t="n">
-        <v>561</v>
+        <v>562.0000000000001</v>
       </c>
       <c r="M44" t="n">
-        <v>561</v>
+        <v>90.83741289148684</v>
       </c>
       <c r="N44" t="n">
-        <v>89.87781693189082</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>164.7897032902292</v>
@@ -38082,7 +38082,7 @@
         <v>200.3120706125849</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>562</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -38158,7 +38158,7 @@
         <v>419.0391822801049</v>
       </c>
       <c r="P45" t="n">
-        <v>253.9797225529744</v>
+        <v>256.1913441372947</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -38195,37 +38195,37 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>57.88619966292134</v>
+        <v>52.88619966292134</v>
       </c>
       <c r="C46" t="n">
-        <v>72.27475335195533</v>
+        <v>67.27475335195533</v>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>54.46378194444452</v>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
+        <v>59.01909516304346</v>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>65.61714403225807</v>
       </c>
       <c r="G46" t="n">
-        <v>100.581864863388</v>
+        <v>95.58186486338801</v>
       </c>
       <c r="H46" t="n">
-        <v>121.7922509475617</v>
+        <v>116.7922509475617</v>
       </c>
       <c r="I46" t="n">
-        <v>187.184183724144</v>
+        <v>182.184183724144</v>
       </c>
       <c r="J46" t="n">
-        <v>8.970706901797143</v>
+        <v>348.9707069017971</v>
       </c>
       <c r="K46" t="n">
-        <v>129.178570461152</v>
+        <v>124.178570461152</v>
       </c>
       <c r="L46" t="n">
-        <v>14.48250298976181</v>
+        <v>9.482502989761826</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -38249,22 +38249,22 @@
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>137.6490400511193</v>
+        <v>132.6490400511193</v>
       </c>
       <c r="U46" t="n">
-        <v>194.0757398730831</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>145.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>72.94268811763288</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>97.55635456989245</v>
+        <v>72.01509297589396</v>
       </c>
       <c r="Y46" t="n">
-        <v>57.53464715053764</v>
+        <v>52.53464715053764</v>
       </c>
     </row>
   </sheetData>
